--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-15</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H2" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L2" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Bottom Of Your Boots</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-15</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>Dandelion</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G3" t="str">
-        <v>3:19</v>
+        <v>3:14</v>
       </c>
       <c r="H3" t="str">
-        <v>Ella Langley</v>
+        <v>DANNA</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L3" t="str">
-        <v>Bottom Of Your Boots - Ella Langley</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>RUNWAY</v>
+        <v>Bottom Of Your Boots</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/runway/1891472591</v>
+        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-15</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>RUNWAY - Single</v>
+        <v>Dandelion</v>
       </c>
       <c r="G4" t="str">
-        <v>2:51</v>
+        <v>3:19</v>
       </c>
       <c r="H4" t="str">
-        <v>Lady Gaga</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/runway/1891472590</v>
+        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
       </c>
       <c r="L4" t="str">
-        <v>RUNWAY - Lady Gaga</v>
+        <v>Bottom Of Your Boots - Ella Langley</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Back and Forth (feat. Missy Elliott)</v>
+        <v>RUNWAY</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
+        <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-15</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Kehlani</v>
+        <v>RUNWAY - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>3:34</v>
+        <v>2:51</v>
       </c>
       <c r="H5" t="str">
-        <v>Kehlani</v>
+        <v>Lady Gaga</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
+        <v>https://music.apple.com/us/album/runway/1891472590</v>
       </c>
       <c r="L5" t="str">
-        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
+        <v>RUNWAY - Lady Gaga</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Mr. Know It All</v>
+        <v>Back and Forth (feat. Missy Elliott)</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
+        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-15</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Mr. Know It All - Single</v>
+        <v>Kehlani</v>
       </c>
       <c r="G6" t="str">
-        <v>3:18</v>
+        <v>3:34</v>
       </c>
       <c r="H6" t="str">
-        <v>Teddy Swims</v>
+        <v>Kehlani</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
+        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
+        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
       </c>
       <c r="L6" t="str">
-        <v>Mr. Know It All - Teddy Swims</v>
+        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Bad Angel</v>
+        <v>Mr. Know It All</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
+        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-15</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Bad Angel - Single</v>
+        <v>Mr. Know It All - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>2:33</v>
+        <v>3:18</v>
       </c>
       <c r="H7" t="str">
-        <v>Anyma</v>
+        <v>Teddy Swims</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
+        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
       </c>
       <c r="L7" t="str">
-        <v>Bad Angel - Anyma</v>
+        <v>Mr. Know It All - Teddy Swims</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Step (feat. Swizz Beatz)</v>
+        <v>Bad Angel</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
+        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-15</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>10 Til' Midnight</v>
+        <v>Bad Angel - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>3:34</v>
+        <v>2:33</v>
       </c>
       <c r="H8" t="str">
-        <v>Snoop Dogg</v>
+        <v>Anyma</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
+        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
+        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
       </c>
       <c r="L8" t="str">
-        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
+        <v>Bad Angel - Anyma</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Sweet Hallelujah</v>
+        <v>Step (feat. Swizz Beatz)</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
+        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-15</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Sweet Hallelujah - Single</v>
+        <v>10 Til' Midnight</v>
       </c>
       <c r="G9" t="str">
-        <v>3:02</v>
+        <v>3:34</v>
       </c>
       <c r="H9" t="str">
-        <v>Royel Otis</v>
+        <v>Snoop Dogg</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
+        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
+        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
       </c>
       <c r="L9" t="str">
-        <v>Sweet Hallelujah - Royel Otis</v>
+        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Beauty Pageant</v>
+        <v>Sweet Hallelujah</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
+        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-15</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Cruel World</v>
+        <v>Sweet Hallelujah - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:15</v>
+        <v>3:02</v>
       </c>
       <c r="H10" t="str">
-        <v>Holly Humberstone</v>
+        <v>Royel Otis</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
+        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
       </c>
       <c r="L10" t="str">
-        <v>Beauty Pageant - Holly Humberstone</v>
+        <v>Sweet Hallelujah - Royel Otis</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>PINKY UP</v>
+        <v>Beauty Pageant</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-15</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>PINKY UP - Single</v>
+        <v>Cruel World</v>
       </c>
       <c r="G11" t="str">
-        <v>2:11</v>
+        <v>3:15</v>
       </c>
       <c r="H11" t="str">
-        <v>KATSEYE</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
       </c>
       <c r="L11" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>Beauty Pageant - Holly Humberstone</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>i just get worse</v>
+        <v>PINKY UP</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-15</v>
@@ -831,25 +831,25 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>i just get worse - Single</v>
+        <v>PINKY UP - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:25</v>
+        <v>2:11</v>
       </c>
       <c r="H12" t="str">
-        <v>Kevian Kraemer</v>
+        <v>KATSEYE</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
       </c>
       <c r="L12" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>PINKY UP - KATSEYE</v>
       </c>
     </row>
     <row r="13">
@@ -892,13 +892,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Ember</v>
+        <v>i just get worse</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-15</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G14" t="str">
         <v>3:25</v>
       </c>
       <c r="H14" t="str">
-        <v>Iceage</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L14" t="str">
-        <v>Ember - Iceage</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Turnaround</v>
+        <v>Ember</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-15</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>For Love of Grace &amp; the Hereafter</v>
       </c>
       <c r="G15" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H15" t="str">
-        <v>54 Ultra</v>
+        <v>Iceage</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/iceage/406846711</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/ember/1880484160</v>
       </c>
       <c r="L15" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>Ember - Iceage</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Turnaround</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-15</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H16" t="str">
-        <v>Labrinth</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L16" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Madwoman</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-15</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:59</v>
+        <v>3:05</v>
       </c>
       <c r="H17" t="str">
-        <v>Laufey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L17" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Madwoman</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-15</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G18" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H18" t="str">
-        <v>Hilary Duff</v>
+        <v>Laufey</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L18" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>One of Them</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-15</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>One of Them - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H19" t="str">
-        <v>DJ Khaled</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L19" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-15</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H20" t="str">
-        <v>Bossman Dlow</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L20" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>stuck</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-15</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>ghosted - EP</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G21" t="str">
-        <v>2:41</v>
+        <v>2:49</v>
       </c>
       <c r="H21" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L21" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>De Lejitos</v>
+        <v>stuck</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-15</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>De Lejitos - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G22" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H22" t="str">
-        <v>Jay Wheeler</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L22" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Echo</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-15</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Echo - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H23" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L23" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Where We Go</v>
+        <v>Echo</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-15</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Where We Go - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H24" t="str">
-        <v>Marshmello</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L24" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Where We Go</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-15</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Apambichao</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H25" t="str">
-        <v>Manuel Turizo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L25" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Of All People</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-15</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Apambichao</v>
       </c>
       <c r="G26" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H26" t="str">
-        <v>Foo Fighters</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L26" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Waves of You</v>
+        <v>Of All People</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-15</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Waves of You - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G27" t="str">
-        <v>3:15</v>
+        <v>2:34</v>
       </c>
       <c r="H27" t="str">
-        <v>After Hours</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L27" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-15</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H28" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L28" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-15</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H29" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L29" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-15</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G30" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H30" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L30" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-15</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H31" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L31" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-15</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H32" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L32" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-15</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>5:06</v>
+        <v>3:06</v>
       </c>
       <c r="H33" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L33" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-15</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G34" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L34" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-15</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G35" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H35" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L35" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-15</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G36" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H36" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L36" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-15</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H37" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L37" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Woman I Am</v>
+        <v>side slider</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-15</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>SE9</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G38" t="str">
-        <v>3:31</v>
+        <v>3:47</v>
       </c>
       <c r="H38" t="str">
-        <v>Skye Newman</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L38" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bubee</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-15</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Bubee - Single</v>
+        <v>SE9</v>
       </c>
       <c r="G39" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H39" t="str">
-        <v>ILLIT</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
       </c>
       <c r="L39" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Good Morning</v>
+        <v>Bubee</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-15</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>24</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G40" t="str">
         <v>3:02</v>
       </c>
       <c r="H40" t="str">
-        <v>Alexis Ffrench</v>
+        <v>ILLIT</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L40" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Positano</v>
+        <v>Good Morning</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-15</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>24</v>
       </c>
       <c r="G41" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H41" t="str">
-        <v>Stephan Moccio</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L41" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>sophie</v>
+        <v>Positano</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-15</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G42" t="str">
-        <v>2:36</v>
+        <v>3:27</v>
       </c>
       <c r="H42" t="str">
-        <v>kenzie</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L42" t="str">
-        <v>sophie - kenzie</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>kiss goodbye</v>
+        <v>sophie</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-15</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G43" t="str">
-        <v>2:43</v>
+        <v>2:36</v>
       </c>
       <c r="H43" t="str">
-        <v>The Two Lips</v>
+        <v>kenzie</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L43" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENTRÉGAME</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-15</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:08</v>
+        <v>2:43</v>
       </c>
       <c r="H44" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L44" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>EL SENTRITA</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-15</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>ETERNO</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G45" t="str">
-        <v>2:57</v>
+        <v>3:08</v>
       </c>
       <c r="H45" t="str">
-        <v>Calle 24</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L45" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-15</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>DAWN PATROL</v>
+        <v>ETERNO</v>
       </c>
       <c r="G46" t="str">
-        <v>2:39</v>
+        <v>2:57</v>
       </c>
       <c r="H46" t="str">
-        <v>PARTY WAVE</v>
+        <v>Calle 24</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L46" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Formation</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-15</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Formation - Single</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G47" t="str">
-        <v>2:36</v>
+        <v>2:39</v>
       </c>
       <c r="H47" t="str">
-        <v>Adekunle Gold</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L47" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Who Will You Follow</v>
+        <v>Formation</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-15</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Sanctuary</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>3:55</v>
+        <v>2:36</v>
       </c>
       <c r="H48" t="str">
-        <v>Evanescence</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L48" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>That's When You Know</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-15</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>3:55</v>
       </c>
       <c r="H49" t="str">
-        <v>Kygo</v>
+        <v>Evanescence</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L49" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Drinking Game</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-15</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Drinking Game - Single</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:50</v>
+        <v>3:13</v>
       </c>
       <c r="H50" t="str">
-        <v>Warren Zeiders</v>
+        <v>Kygo</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L50" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Anything But Me</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-15</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>In The Feeling</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>4:59</v>
+        <v>2:50</v>
       </c>
       <c r="H51" t="str">
-        <v>Owen Riegling</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L51" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>American Dream</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-15</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>American Dream - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G52" t="str">
-        <v>4:27</v>
+        <v>4:59</v>
       </c>
       <c r="H52" t="str">
-        <v>Alabama Shakes</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L52" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Already There</v>
+        <v>American Dream</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-15</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Victory Garden</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>4:27</v>
       </c>
       <c r="H53" t="str">
-        <v>Young the Giant</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L53" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Already There</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-15</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>KINDA HARD</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G54" t="str">
-        <v>2:47</v>
+        <v>3:50</v>
       </c>
       <c r="H54" t="str">
-        <v>Bilmuri</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L54" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alone For A Year</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-15</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Joy Next Door</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G55" t="str">
-        <v>3:22</v>
+        <v>2:47</v>
       </c>
       <c r="H55" t="str">
-        <v>The Maine</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L55" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bring Home My Man</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-15</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G56" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H56" t="str">
-        <v>Maya Hawke</v>
+        <v>The Maine</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L56" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SUPERMAN</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-15</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G57" t="str">
-        <v>3:24</v>
+        <v>4:22</v>
       </c>
       <c r="H57" t="str">
-        <v>South Arcade</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L57" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1989</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-15</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>1989 - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:34</v>
+        <v>3:24</v>
       </c>
       <c r="H58" t="str">
-        <v>Nightly</v>
+        <v>South Arcade</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L58" t="str">
-        <v>1989 - Nightly</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>waste your pain</v>
+        <v>1989</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-15</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>waste your pain - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:23</v>
+        <v>2:34</v>
       </c>
       <c r="H59" t="str">
-        <v>Cruz Beckham</v>
+        <v>Nightly</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L59" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Strangers</v>
+        <v>waste your pain</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-15</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:44</v>
+        <v>2:23</v>
       </c>
       <c r="H60" t="str">
-        <v>Tink</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L60" t="str">
-        <v>Strangers - Tink</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Strangers</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-15</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G61" t="str">
-        <v>2:45</v>
+        <v>2:44</v>
       </c>
       <c r="H61" t="str">
-        <v>Tiny Habits</v>
+        <v>Tink</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L61" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SAME SH!T</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-15</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:13</v>
+        <v>2:45</v>
       </c>
       <c r="H62" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L62" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-15</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>The End is Not the End</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:12</v>
+        <v>3:13</v>
       </c>
       <c r="H63" t="str">
-        <v>Atreyu</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L63" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Heal</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-15</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Heal - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G64" t="str">
-        <v>3:26</v>
+        <v>4:12</v>
       </c>
       <c r="H64" t="str">
-        <v>HAYLA</v>
+        <v>Atreyu</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L64" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Free</v>
+        <v>Heal</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-15</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:13</v>
+        <v>3:26</v>
       </c>
       <c r="H65" t="str">
-        <v>Simone Ashley</v>
+        <v>HAYLA</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L65" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Cállate</v>
+        <v>Free</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-15</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G66" t="str">
-        <v>1:59</v>
+        <v>4:13</v>
       </c>
       <c r="H66" t="str">
-        <v>Dua Saleh</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L66" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Raindrops</v>
+        <v>Cállate</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-15</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Raindrops - Single</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>1:59</v>
       </c>
       <c r="H67" t="str">
-        <v>Rick Astley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L67" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WORK OF ART</v>
+        <v>Raindrops</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-15</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>PRODIGY</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:27</v>
+        <v>3:34</v>
       </c>
       <c r="H68" t="str">
-        <v>Tkandz</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L68" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Scottie Pippen</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-15</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G69" t="str">
-        <v>2:34</v>
+        <v>2:27</v>
       </c>
       <c r="H69" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tkandz</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L69" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Damn Good Actress</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-15</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:49</v>
+        <v>2:34</v>
       </c>
       <c r="H70" t="str">
-        <v>Tiffany Stringer</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L70" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ricota</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-15</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Ricota - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:25</v>
+        <v>2:49</v>
       </c>
       <c r="H71" t="str">
-        <v>ZULAN</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L71" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kissing The Ground</v>
+        <v>Ricota</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-15</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:50</v>
+        <v>2:25</v>
       </c>
       <c r="H72" t="str">
-        <v>Nell Mescal</v>
+        <v>ZULAN</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L72" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Joy</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-15</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>All In Now</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:41</v>
+        <v>3:50</v>
       </c>
       <c r="H73" t="str">
-        <v>Dogstar</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L73" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Amor Bonito</v>
+        <v>Joy</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-15</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>All In Now</v>
       </c>
       <c r="G74" t="str">
-        <v>2:44</v>
+        <v>3:41</v>
       </c>
       <c r="H74" t="str">
-        <v>Kany García</v>
+        <v>Dogstar</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L74" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Patchwork</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-15</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Patchwork - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G75" t="str">
-        <v>3:07</v>
+        <v>2:44</v>
       </c>
       <c r="H75" t="str">
-        <v>Carlita</v>
+        <v>Kany García</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L75" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>She's A Devil</v>
+        <v>Patchwork</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-15</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:24</v>
+        <v>3:07</v>
       </c>
       <c r="H76" t="str">
-        <v>Layton Giordani</v>
+        <v>Carlita</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L76" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Do It All Alone</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-15</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:52</v>
+        <v>3:24</v>
       </c>
       <c r="H77" t="str">
-        <v>Rend Collective</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L77" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Time</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-15</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Time - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:20</v>
+        <v>2:52</v>
       </c>
       <c r="H78" t="str">
-        <v>David Leonard</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L78" t="str">
-        <v>Time - David Leonard</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Andamos Ready</v>
+        <v>Time</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-15</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:10</v>
+        <v>3:20</v>
       </c>
       <c r="H79" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>David Leonard</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L79" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Van y Vienen</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-15</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:46</v>
+        <v>3:10</v>
       </c>
       <c r="H80" t="str">
-        <v>El Fantasma</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L80" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No Vuelvas</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-15</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:46</v>
+        <v>2:46</v>
       </c>
       <c r="H81" t="str">
-        <v>Majo Aguilar</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L81" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>RUNNIN</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-15</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>RUNNIN - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:40</v>
+        <v>3:46</v>
       </c>
       <c r="H82" t="str">
-        <v>RUA YOUNG</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L82" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Talk You Through It</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-15</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:33</v>
+        <v>2:40</v>
       </c>
       <c r="H83" t="str">
-        <v>Kenyon Dixon</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L83" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Partners in Crime</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-15</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Born to Kill</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:50</v>
+        <v>3:33</v>
       </c>
       <c r="H84" t="str">
-        <v>Social Distortion</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L84" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Change your mind</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-15</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Change your mind - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>3:50</v>
       </c>
       <c r="H85" t="str">
-        <v>Casper Sage</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L85" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Change your mind</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-15</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H86" t="str">
-        <v>The Franklin Electric</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L86" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-15</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Train on the Island</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:17</v>
+        <v>3:29</v>
       </c>
       <c r="H87" t="str">
-        <v>Aldous Harding</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L87" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lover</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-15</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Lover - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:17</v>
       </c>
       <c r="H88" t="str">
-        <v>Juke Ross</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L88" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>pink moon</v>
+        <v>Lover</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-15</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>runo plum</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L89" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Summer</v>
+        <v>pink moon</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-15</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Summer - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G90" t="str">
         <v>3:21</v>
       </c>
       <c r="H90" t="str">
-        <v>Tasha</v>
+        <v>runo plum</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L90" t="str">
-        <v>Summer - Tasha</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Summer</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-15</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>Nara's Room</v>
+        <v>Tasha</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L91" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Fabienk</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-15</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Vol.II</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G92" t="str">
-        <v>6:31</v>
+        <v>4:20</v>
       </c>
       <c r="H92" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L92" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>My Girl</v>
+        <v>Fabienk</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-15</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Soren - EP</v>
+        <v>Vol.II</v>
       </c>
       <c r="G93" t="str">
-        <v>3:45</v>
+        <v>6:31</v>
       </c>
       <c r="H93" t="str">
-        <v>Orca</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L93" t="str">
-        <v>My Girl - Orca</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bone Structure</v>
+        <v>My Girl</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-15</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G94" t="str">
-        <v>3:01</v>
+        <v>3:45</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolder</v>
+        <v>Orca</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L94" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Turning Into Us</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-15</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:30</v>
+        <v>3:01</v>
       </c>
       <c r="H95" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Dolder</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L95" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-15</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:00</v>
+        <v>3:30</v>
       </c>
       <c r="H96" t="str">
-        <v>Osé</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L96" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Fright</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-15</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Fright - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:25</v>
+        <v>3:00</v>
       </c>
       <c r="H97" t="str">
-        <v>Creepy Nuts</v>
+        <v>Osé</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L97" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Smoking In Bed</v>
+        <v>Fright</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-15</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>3:24</v>
+        <v>2:25</v>
       </c>
       <c r="H98" t="str">
-        <v>The Bends</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L98" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Dissonant Void</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-15</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:47</v>
+        <v>3:24</v>
       </c>
       <c r="H99" t="str">
-        <v>At The Gates</v>
+        <v>The Bends</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L99" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-15</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G100" t="str">
-        <v>3:51</v>
+        <v>2:47</v>
       </c>
       <c r="H100" t="str">
-        <v>Melvins</v>
+        <v>At The Gates</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L100" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G101" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H101" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-04-15</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-04-15</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>4:46</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/runway/1891472591</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/ember/1880484164</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-15</v>
+        <v>2026-04-16</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1842,13 +1842,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Woman I Am</v>
+        <v>Bubee</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1890182800</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-16</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>SE9</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:31</v>
+        <v>3:02</v>
       </c>
       <c r="H39" t="str">
-        <v>Skye Newman</v>
+        <v>ILLIT</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1890182220</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L39" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Bubee</v>
+        <v>Good Morning</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-16</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Bubee - Single</v>
+        <v>24</v>
       </c>
       <c r="G40" t="str">
         <v>3:02</v>
       </c>
       <c r="H40" t="str">
-        <v>ILLIT</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L40" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Good Morning</v>
+        <v>Positano</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-16</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>24</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G41" t="str">
-        <v>3:02</v>
+        <v>3:27</v>
       </c>
       <c r="H41" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L41" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Positano</v>
+        <v>sophie</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-16</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G42" t="str">
-        <v>3:27</v>
+        <v>2:36</v>
       </c>
       <c r="H42" t="str">
-        <v>Stephan Moccio</v>
+        <v>kenzie</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L42" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>sophie</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-16</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>notes from the in between - EP</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>2:36</v>
+        <v>2:43</v>
       </c>
       <c r="H43" t="str">
-        <v>kenzie</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L43" t="str">
-        <v>sophie - kenzie</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>kiss goodbye</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-16</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G44" t="str">
-        <v>2:43</v>
+        <v>3:08</v>
       </c>
       <c r="H44" t="str">
-        <v>The Two Lips</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L44" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENTRÉGAME</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-16</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>ETERNO</v>
       </c>
       <c r="G45" t="str">
-        <v>3:08</v>
+        <v>2:57</v>
       </c>
       <c r="H45" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>Calle 24</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L45" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>EL SENTRITA</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-16</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>ETERNO</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G46" t="str">
-        <v>2:57</v>
+        <v>2:39</v>
       </c>
       <c r="H46" t="str">
-        <v>Calle 24</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L46" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>Formation</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-16</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>DAWN PATROL</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:39</v>
+        <v>2:36</v>
       </c>
       <c r="H47" t="str">
-        <v>PARTY WAVE</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L47" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Formation</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-16</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Formation - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G48" t="str">
-        <v>2:36</v>
+        <v>3:55</v>
       </c>
       <c r="H48" t="str">
-        <v>Adekunle Gold</v>
+        <v>Evanescence</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L48" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Who Will You Follow</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-16</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Sanctuary</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:55</v>
+        <v>3:13</v>
       </c>
       <c r="H49" t="str">
-        <v>Evanescence</v>
+        <v>Kygo</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L49" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>That's When You Know</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-16</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>3:13</v>
+        <v>2:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Kygo</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L50" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Drinking Game</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-16</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Drinking Game - Single</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G51" t="str">
-        <v>2:50</v>
+        <v>4:59</v>
       </c>
       <c r="H51" t="str">
-        <v>Warren Zeiders</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L51" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Anything But Me</v>
+        <v>American Dream</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-16</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>In The Feeling</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>4:59</v>
+        <v>4:27</v>
       </c>
       <c r="H52" t="str">
-        <v>Owen Riegling</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L52" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>American Dream</v>
+        <v>Already There</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-16</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>American Dream - Single</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G53" t="str">
-        <v>4:27</v>
+        <v>3:50</v>
       </c>
       <c r="H53" t="str">
-        <v>Alabama Shakes</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L53" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Already There</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-16</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Victory Garden</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G54" t="str">
-        <v>3:50</v>
+        <v>2:47</v>
       </c>
       <c r="H54" t="str">
-        <v>Young the Giant</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L54" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-16</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>KINDA HARD</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G55" t="str">
-        <v>2:47</v>
+        <v>3:22</v>
       </c>
       <c r="H55" t="str">
-        <v>Bilmuri</v>
+        <v>The Maine</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L55" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Alone For A Year</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-16</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>Joy Next Door</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G56" t="str">
-        <v>3:22</v>
+        <v>4:22</v>
       </c>
       <c r="H56" t="str">
-        <v>The Maine</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L56" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Bring Home My Man</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-16</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>4:22</v>
+        <v>3:24</v>
       </c>
       <c r="H57" t="str">
-        <v>Maya Hawke</v>
+        <v>South Arcade</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L57" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SUPERMAN</v>
+        <v>1989</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-16</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:24</v>
+        <v>2:34</v>
       </c>
       <c r="H58" t="str">
-        <v>South Arcade</v>
+        <v>Nightly</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L58" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>1989</v>
+        <v>waste your pain</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-16</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>1989 - Single</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:34</v>
+        <v>2:23</v>
       </c>
       <c r="H59" t="str">
-        <v>Nightly</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L59" t="str">
-        <v>1989 - Nightly</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>waste your pain</v>
+        <v>Strangers</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-16</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>waste your pain - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G60" t="str">
-        <v>2:23</v>
+        <v>2:44</v>
       </c>
       <c r="H60" t="str">
-        <v>Cruz Beckham</v>
+        <v>Tink</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L60" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Strangers</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-16</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:44</v>
+        <v>2:45</v>
       </c>
       <c r="H61" t="str">
-        <v>Tink</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L61" t="str">
-        <v>Strangers - Tink</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Right In Front Of Me</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-16</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:45</v>
+        <v>3:13</v>
       </c>
       <c r="H62" t="str">
-        <v>Tiny Habits</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L62" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SAME SH!T</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-16</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G63" t="str">
-        <v>3:13</v>
+        <v>4:12</v>
       </c>
       <c r="H63" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Atreyu</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L63" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Heal</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-16</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>The End is Not the End</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:12</v>
+        <v>3:26</v>
       </c>
       <c r="H64" t="str">
-        <v>Atreyu</v>
+        <v>HAYLA</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L64" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Heal</v>
+        <v>Free</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-16</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Heal - Single</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G65" t="str">
-        <v>3:26</v>
+        <v>4:13</v>
       </c>
       <c r="H65" t="str">
-        <v>HAYLA</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L65" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Free</v>
+        <v>Cállate</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-16</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G66" t="str">
-        <v>4:13</v>
+        <v>1:59</v>
       </c>
       <c r="H66" t="str">
-        <v>Simone Ashley</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L66" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Cállate</v>
+        <v>Raindrops</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-16</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>1:59</v>
+        <v>3:34</v>
       </c>
       <c r="H67" t="str">
-        <v>Dua Saleh</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L67" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Raindrops</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-16</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Raindrops - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G68" t="str">
-        <v>3:34</v>
+        <v>2:27</v>
       </c>
       <c r="H68" t="str">
-        <v>Rick Astley</v>
+        <v>Tkandz</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L68" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>WORK OF ART</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-16</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>PRODIGY</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:27</v>
+        <v>2:34</v>
       </c>
       <c r="H69" t="str">
-        <v>Tkandz</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L69" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Scottie Pippen</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-16</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:34</v>
+        <v>2:49</v>
       </c>
       <c r="H70" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L70" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Damn Good Actress</v>
+        <v>Ricota</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-16</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:49</v>
+        <v>2:25</v>
       </c>
       <c r="H71" t="str">
-        <v>Tiffany Stringer</v>
+        <v>ZULAN</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L71" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ricota</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-16</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Ricota - Single</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:25</v>
+        <v>3:50</v>
       </c>
       <c r="H72" t="str">
-        <v>ZULAN</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L72" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Kissing The Ground</v>
+        <v>Joy</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-16</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G73" t="str">
-        <v>3:50</v>
+        <v>3:41</v>
       </c>
       <c r="H73" t="str">
-        <v>Nell Mescal</v>
+        <v>Dogstar</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L73" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Joy</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-16</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>All In Now</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G74" t="str">
-        <v>3:41</v>
+        <v>2:44</v>
       </c>
       <c r="H74" t="str">
-        <v>Dogstar</v>
+        <v>Kany García</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L74" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Amor Bonito</v>
+        <v>Patchwork</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-16</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>2:44</v>
+        <v>3:07</v>
       </c>
       <c r="H75" t="str">
-        <v>Kany García</v>
+        <v>Carlita</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L75" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Patchwork</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-16</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Patchwork - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:07</v>
+        <v>3:24</v>
       </c>
       <c r="H76" t="str">
-        <v>Carlita</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L76" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>She's A Devil</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-16</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>She's A Devil - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:24</v>
+        <v>2:52</v>
       </c>
       <c r="H77" t="str">
-        <v>Layton Giordani</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L77" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Do It All Alone</v>
+        <v>Time</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-16</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:52</v>
+        <v>3:20</v>
       </c>
       <c r="H78" t="str">
-        <v>Rend Collective</v>
+        <v>David Leonard</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L78" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Time</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-16</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Time - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:20</v>
+        <v>3:10</v>
       </c>
       <c r="H79" t="str">
-        <v>David Leonard</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L79" t="str">
-        <v>Time - David Leonard</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Andamos Ready</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-16</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:10</v>
+        <v>2:46</v>
       </c>
       <c r="H80" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L80" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Van y Vienen</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-16</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:46</v>
+        <v>3:46</v>
       </c>
       <c r="H81" t="str">
-        <v>El Fantasma</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L81" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>No Vuelvas</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-16</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:46</v>
+        <v>2:40</v>
       </c>
       <c r="H82" t="str">
-        <v>Majo Aguilar</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L82" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>RUNNIN</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-16</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:40</v>
+        <v>3:33</v>
       </c>
       <c r="H83" t="str">
-        <v>RUA YOUNG</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L83" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Talk You Through It</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-16</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G84" t="str">
-        <v>3:33</v>
+        <v>3:50</v>
       </c>
       <c r="H84" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L84" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Partners in Crime</v>
+        <v>Change your mind</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-16</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Born to Kill</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:50</v>
+        <v>3:21</v>
       </c>
       <c r="H85" t="str">
-        <v>Social Distortion</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L85" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Change your mind</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-16</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Change your mind - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:21</v>
+        <v>3:29</v>
       </c>
       <c r="H86" t="str">
-        <v>Casper Sage</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L86" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-16</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G87" t="str">
-        <v>3:29</v>
+        <v>3:17</v>
       </c>
       <c r="H87" t="str">
-        <v>The Franklin Electric</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L87" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Lover</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-16</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Train on the Island</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:17</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Aldous Harding</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L88" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Lover</v>
+        <v>pink moon</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-16</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Lover - Single</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:21</v>
       </c>
       <c r="H89" t="str">
-        <v>Juke Ross</v>
+        <v>runo plum</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L89" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>pink moon</v>
+        <v>Summer</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-16</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G90" t="str">
         <v>3:21</v>
       </c>
       <c r="H90" t="str">
-        <v>runo plum</v>
+        <v>Tasha</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L90" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Summer</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-16</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Summer - Single</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>4:20</v>
       </c>
       <c r="H91" t="str">
-        <v>Tasha</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L91" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Lizzie mcguire</v>
+        <v>Fabienk</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-16</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Vol.II</v>
       </c>
       <c r="G92" t="str">
-        <v>4:20</v>
+        <v>6:31</v>
       </c>
       <c r="H92" t="str">
-        <v>Nara's Room</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L92" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Fabienk</v>
+        <v>My Girl</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-16</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Vol.II</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G93" t="str">
-        <v>6:31</v>
+        <v>3:45</v>
       </c>
       <c r="H93" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Orca</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L93" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>My Girl</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-16</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Soren - EP</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:45</v>
+        <v>3:01</v>
       </c>
       <c r="H94" t="str">
-        <v>Orca</v>
+        <v>Dolder</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L94" t="str">
-        <v>My Girl - Orca</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Bone Structure</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-16</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:01</v>
+        <v>3:30</v>
       </c>
       <c r="H95" t="str">
-        <v>Dolder</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L95" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Turning Into Us</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-16</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:30</v>
+        <v>3:00</v>
       </c>
       <c r="H96" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Osé</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L96" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Fright</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-16</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:00</v>
+        <v>2:25</v>
       </c>
       <c r="H97" t="str">
-        <v>Osé</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L97" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Fright</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-16</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Fright - Single</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:25</v>
+        <v>3:24</v>
       </c>
       <c r="H98" t="str">
-        <v>Creepy Nuts</v>
+        <v>The Bends</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L98" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Smoking In Bed</v>
+        <v>The Dissonant Void</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-16</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G99" t="str">
-        <v>3:24</v>
+        <v>2:47</v>
       </c>
       <c r="H99" t="str">
-        <v>The Bends</v>
+        <v>At The Gates</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
       </c>
       <c r="L99" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>The Dissonant Void - At The Gates</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>The Dissonant Void</v>
+        <v>Nine Days Of Rain</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-16</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Savage Imperial Death March</v>
       </c>
       <c r="G100" t="str">
-        <v>2:47</v>
+        <v>3:51</v>
       </c>
       <c r="H100" t="str">
-        <v>At The Gates</v>
+        <v>Melvins</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
       </c>
       <c r="L100" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Nine Days Of Rain - Melvins</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Invocation of the Dreamer</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-16</v>
@@ -4213,68 +4213,30 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Khemmis</v>
       </c>
       <c r="G101" t="str">
-        <v>3:51</v>
+        <v>4:46</v>
       </c>
       <c r="H101" t="str">
-        <v>Melvins</v>
+        <v>Khemmis</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
       <c r="L101" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Invocation of the Dreamer</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="G102" t="str">
-        <v>4:46</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
-      </c>
-      <c r="L102" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BIAF &lt;3</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-16</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G2" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H2" t="str">
-        <v>Young Miko</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L2" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Sick Of Love</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-16</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>The Afterparty</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:36</v>
+        <v>2:50</v>
       </c>
       <c r="H13" t="str">
-        <v>Lykke Li</v>
+        <v>Young Miko</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L13" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>i just get worse</v>
+        <v>Sick Of Love</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-16</v>
@@ -907,25 +907,25 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>i just get worse - Single</v>
+        <v>The Afterparty</v>
       </c>
       <c r="G14" t="str">
-        <v>3:25</v>
+        <v>3:36</v>
       </c>
       <c r="H14" t="str">
-        <v>Kevian Kraemer</v>
+        <v>Lykke Li</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
       </c>
       <c r="L14" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Sick Of Love - Lykke Li</v>
       </c>
     </row>
     <row r="15">
@@ -968,13 +968,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Turnaround</v>
+        <v>i just get worse</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-16</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:14</v>
+        <v>3:25</v>
       </c>
       <c r="H16" t="str">
-        <v>54 Ultra</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L16" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Turnaround</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-16</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Turnaround / I'm Hooked - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:05</v>
+        <v>3:14</v>
       </c>
       <c r="H17" t="str">
-        <v>Labrinth</v>
+        <v>54 Ultra</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
       </c>
       <c r="L17" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Turnaround - 54 Ultra</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Madwoman</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-16</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:59</v>
+        <v>3:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Laufey</v>
+        <v>Labrinth</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L18" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Madwoman</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-16</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>A Matter of Time: The Final Hour</v>
       </c>
       <c r="G19" t="str">
-        <v>3:33</v>
+        <v>3:59</v>
       </c>
       <c r="H19" t="str">
-        <v>Hilary Duff</v>
+        <v>Laufey</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
       </c>
       <c r="L19" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Madwoman - Laufey</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>One of Them</v>
+        <v>Come Clean (Mine)</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-16</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>One of Them - Single</v>
+        <v>Come Clean (Mine) - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:24</v>
+        <v>3:33</v>
       </c>
       <c r="H20" t="str">
-        <v>DJ Khaled</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
       </c>
       <c r="L20" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Come Clean (Mine) - Hilary Duff</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-16</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>One of Them - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>2:49</v>
+        <v>3:24</v>
       </c>
       <c r="H21" t="str">
-        <v>Bossman Dlow</v>
+        <v>DJ Khaled</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
       </c>
       <c r="L21" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>One of Them - DJ Khaled</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>stuck</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-16</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>ghosted - EP</v>
+        <v>Chicken Talkin Bastard</v>
       </c>
       <c r="G22" t="str">
-        <v>2:41</v>
+        <v>2:49</v>
       </c>
       <c r="H22" t="str">
-        <v>Saint Harison</v>
+        <v>Bossman Dlow</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
       </c>
       <c r="L22" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Chicken Talkin Bastard - Bossman Dlow</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>De Lejitos</v>
+        <v>stuck</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/stuck/1875303118</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-16</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>De Lejitos - Single</v>
+        <v>ghosted - EP</v>
       </c>
       <c r="G23" t="str">
-        <v>3:27</v>
+        <v>2:41</v>
       </c>
       <c r="H23" t="str">
-        <v>Jay Wheeler</v>
+        <v>Saint Harison</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/stuck/1875302904</v>
       </c>
       <c r="L23" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>stuck - Saint Harison</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Echo</v>
+        <v>De Lejitos</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-16</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Echo - Single</v>
+        <v>De Lejitos - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:39</v>
+        <v>3:27</v>
       </c>
       <c r="H24" t="str">
-        <v>The Chainsmokers</v>
+        <v>Jay Wheeler</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
       </c>
       <c r="L24" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>De Lejitos - Jay Wheeler</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Where We Go</v>
+        <v>Echo</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/echo/1891104992</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-16</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Where We Go - Single</v>
+        <v>Echo - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:16</v>
+        <v>3:39</v>
       </c>
       <c r="H25" t="str">
-        <v>Marshmello</v>
+        <v>The Chainsmokers</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/echo/1891104991</v>
       </c>
       <c r="L25" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>Echo - The Chainsmokers</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Where We Go</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-16</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Apambichao</v>
+        <v>Where We Go - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:41</v>
+        <v>3:16</v>
       </c>
       <c r="H26" t="str">
-        <v>Manuel Turizo</v>
+        <v>Marshmello</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
       </c>
       <c r="L26" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Where We Go - Marshmello</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Of All People</v>
+        <v>Te hacen falta dos</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-16</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Apambichao</v>
       </c>
       <c r="G27" t="str">
-        <v>2:34</v>
+        <v>2:41</v>
       </c>
       <c r="H27" t="str">
-        <v>Foo Fighters</v>
+        <v>Manuel Turizo</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
       </c>
       <c r="L27" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Te hacen falta dos - Manuel Turizo</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Waves of You</v>
+        <v>Of All People</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-16</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Waves of You - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G28" t="str">
-        <v>3:15</v>
+        <v>2:34</v>
       </c>
       <c r="H28" t="str">
-        <v>After Hours</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
       </c>
       <c r="L28" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Of All People - Foo Fighters</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>idea 1</v>
+        <v>Waves of You</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-16</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>idea 1 - Single</v>
+        <v>Waves of You - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>3:25</v>
+        <v>3:15</v>
       </c>
       <c r="H29" t="str">
-        <v>Kelela</v>
+        <v>After Hours</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
       </c>
       <c r="L29" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Waves of You - After Hours</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Attitude</v>
+        <v>idea 1</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-16</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Sweat</v>
+        <v>idea 1 - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:13</v>
+        <v>3:25</v>
       </c>
       <c r="H30" t="str">
-        <v>Melanie C</v>
+        <v>Kelela</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/kelela/549186342</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
       </c>
       <c r="L30" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>idea 1 - Kelela</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Attitude</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/attitude/1840517116</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-16</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>Sweat</v>
       </c>
       <c r="G31" t="str">
-        <v>2:54</v>
+        <v>3:13</v>
       </c>
       <c r="H31" t="str">
-        <v>Kylie Cantrall</v>
+        <v>Melanie C</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/attitude/1840516706</v>
       </c>
       <c r="L31" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Attitude - Melanie C</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Work</v>
+        <v>Carrie Bradshaw</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-16</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Work - Single</v>
+        <v>Carrie Bradshaw - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:51</v>
+        <v>2:54</v>
       </c>
       <c r="H32" t="str">
-        <v>Pitbull</v>
+        <v>Kylie Cantrall</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
       </c>
       <c r="L32" t="str">
-        <v>Work - Pitbull</v>
+        <v>Carrie Bradshaw - Kylie Cantrall</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Obvious</v>
+        <v>Work</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/work/1885916583</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-16</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Obvious - Single</v>
+        <v>Work - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H33" t="str">
-        <v>Chris Brown</v>
+        <v>Pitbull</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/work/1885916578</v>
       </c>
       <c r="L33" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Work - Pitbull</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>As Time Goes By</v>
+        <v>Obvious</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/obvious/1891759136</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-16</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>CINEMATIC</v>
+        <v>Obvious - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>5:06</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Josh Groban</v>
+        <v>Chris Brown</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/obvious/1891759134</v>
       </c>
       <c r="L34" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Obvious - Chris Brown</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>My Mess</v>
+        <v>As Time Goes By</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-16</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>CINEMATIC</v>
       </c>
       <c r="G35" t="str">
-        <v>3:11</v>
+        <v>5:06</v>
       </c>
       <c r="H35" t="str">
-        <v>Myles Smith</v>
+        <v>Josh Groban</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
       </c>
       <c r="L35" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>As Time Goes By - Josh Groban</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Going Shopping</v>
+        <v>My Mess</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-16</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Reality Awaits</v>
+        <v>My Mess, My Heart, My Life.</v>
       </c>
       <c r="G36" t="str">
-        <v>4:21</v>
+        <v>3:11</v>
       </c>
       <c r="H36" t="str">
-        <v>The Strokes</v>
+        <v>Myles Smith</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
       </c>
       <c r="L36" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>My Mess - Myles Smith</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Choka Choka</v>
+        <v>Going Shopping</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-16</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Reality Awaits</v>
       </c>
       <c r="G37" t="str">
-        <v>2:11</v>
+        <v>4:21</v>
       </c>
       <c r="H37" t="str">
-        <v>Anitta</v>
+        <v>The Strokes</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
       </c>
       <c r="L37" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Going Shopping - The Strokes</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>side slider</v>
+        <v>Choka Choka</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-16</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Choka Choka - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:47</v>
+        <v>2:11</v>
       </c>
       <c r="H38" t="str">
-        <v>Isaia Huron</v>
+        <v>Anitta</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
       </c>
       <c r="L38" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Choka Choka - Anitta</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bubee</v>
+        <v>side slider</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-16</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Bubee - Single</v>
+        <v>Mr. Lovebomb</v>
       </c>
       <c r="G39" t="str">
-        <v>3:02</v>
+        <v>3:47</v>
       </c>
       <c r="H39" t="str">
-        <v>ILLIT</v>
+        <v>Isaia Huron</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
       </c>
       <c r="L39" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>side slider - Isaia Huron</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Good Morning</v>
+        <v>Woman I Am</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/woman-i-am/1893733064</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-16</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>24</v>
+        <v>SE9</v>
       </c>
       <c r="G40" t="str">
-        <v>3:02</v>
+        <v>3:31</v>
       </c>
       <c r="H40" t="str">
-        <v>Alexis Ffrench</v>
+        <v>Skye Newman</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/woman-i-am/1893733056</v>
       </c>
       <c r="L40" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Woman I Am - Skye Newman</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Positano</v>
+        <v>Bubee</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/bubee/1885450942</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-16</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Bubee - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H41" t="str">
-        <v>Stephan Moccio</v>
+        <v>ILLIT</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/illit/1734551937</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/bubee/1885450328</v>
       </c>
       <c r="L41" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Bubee - ILLIT</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>sophie</v>
+        <v>Good Morning</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-16</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>notes from the in between - EP</v>
+        <v>24</v>
       </c>
       <c r="G42" t="str">
-        <v>2:36</v>
+        <v>3:02</v>
       </c>
       <c r="H42" t="str">
-        <v>kenzie</v>
+        <v>Alexis Ffrench</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
       </c>
       <c r="L42" t="str">
-        <v>sophie - kenzie</v>
+        <v>Good Morning - Alexis Ffrench</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>kiss goodbye</v>
+        <v>Positano</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/positano/1886736661</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-16</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>Scenes from a Velvet Room</v>
       </c>
       <c r="G43" t="str">
-        <v>2:43</v>
+        <v>3:27</v>
       </c>
       <c r="H43" t="str">
-        <v>The Two Lips</v>
+        <v>Stephan Moccio</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/positano/1886736650</v>
       </c>
       <c r="L43" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>Positano - Stephan Moccio</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENTRÉGAME</v>
+        <v>sophie</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/sophie/1887348036</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-16</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>notes from the in between - EP</v>
       </c>
       <c r="G44" t="str">
-        <v>3:08</v>
+        <v>2:36</v>
       </c>
       <c r="H44" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>kenzie</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/sophie/1887348032</v>
       </c>
       <c r="L44" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>sophie - kenzie</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>EL SENTRITA</v>
+        <v>kiss goodbye</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-16</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>ETERNO</v>
+        <v>kiss goodbye / brb - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:57</v>
+        <v>2:43</v>
       </c>
       <c r="H45" t="str">
-        <v>Calle 24</v>
+        <v>The Two Lips</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
       </c>
       <c r="L45" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>kiss goodbye - The Two Lips</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>ENTRÉGAME</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-16</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>DAWN PATROL</v>
+        <v>RADIO VENEZUELA</v>
       </c>
       <c r="G46" t="str">
-        <v>2:39</v>
+        <v>3:08</v>
       </c>
       <c r="H46" t="str">
-        <v>PARTY WAVE</v>
+        <v>Chino &amp; Nacho</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
       </c>
       <c r="L46" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>ENTRÉGAME - Chino &amp; Nacho</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Formation</v>
+        <v>EL SENTRITA</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-16</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Formation - Single</v>
+        <v>ETERNO</v>
       </c>
       <c r="G47" t="str">
-        <v>2:36</v>
+        <v>2:57</v>
       </c>
       <c r="H47" t="str">
-        <v>Adekunle Gold</v>
+        <v>Calle 24</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
       </c>
       <c r="L47" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>EL SENTRITA - Calle 24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Who Will You Follow</v>
+        <v>SOMETHING IN THE WATER</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-16</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Sanctuary</v>
+        <v>DAWN PATROL</v>
       </c>
       <c r="G48" t="str">
-        <v>3:55</v>
+        <v>2:39</v>
       </c>
       <c r="H48" t="str">
-        <v>Evanescence</v>
+        <v>PARTY WAVE</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
       </c>
       <c r="L48" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>That's When You Know</v>
+        <v>Formation</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/formation/1882714068</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-16</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>That's When You Know - Single</v>
+        <v>Formation - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>3:13</v>
+        <v>2:36</v>
       </c>
       <c r="H49" t="str">
-        <v>Kygo</v>
+        <v>Adekunle Gold</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/formation/1882714060</v>
       </c>
       <c r="L49" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Formation - Adekunle Gold</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Drinking Game</v>
+        <v>Who Will You Follow</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-16</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Drinking Game - Single</v>
+        <v>Sanctuary</v>
       </c>
       <c r="G50" t="str">
-        <v>2:50</v>
+        <v>3:55</v>
       </c>
       <c r="H50" t="str">
-        <v>Warren Zeiders</v>
+        <v>Evanescence</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
       </c>
       <c r="L50" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>Who Will You Follow - Evanescence</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Anything But Me</v>
+        <v>That's When You Know</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-16</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>In The Feeling</v>
+        <v>That's When You Know - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>4:59</v>
+        <v>3:13</v>
       </c>
       <c r="H51" t="str">
-        <v>Owen Riegling</v>
+        <v>Kygo</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
       </c>
       <c r="L51" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>That's When You Know - Kygo</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>American Dream</v>
+        <v>Drinking Game</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-16</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>American Dream - Single</v>
+        <v>Drinking Game - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>4:27</v>
+        <v>2:50</v>
       </c>
       <c r="H52" t="str">
-        <v>Alabama Shakes</v>
+        <v>Warren Zeiders</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
       </c>
       <c r="L52" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Drinking Game - Warren Zeiders</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Already There</v>
+        <v>Anything But Me</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-16</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Victory Garden</v>
+        <v>In The Feeling</v>
       </c>
       <c r="G53" t="str">
-        <v>3:50</v>
+        <v>4:59</v>
       </c>
       <c r="H53" t="str">
-        <v>Young the Giant</v>
+        <v>Owen Riegling</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
       </c>
       <c r="L53" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>Anything But Me - Owen Riegling</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>American Dream</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-16</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>KINDA HARD</v>
+        <v>American Dream - Single</v>
       </c>
       <c r="G54" t="str">
-        <v>2:47</v>
+        <v>4:27</v>
       </c>
       <c r="H54" t="str">
-        <v>Bilmuri</v>
+        <v>Alabama Shakes</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
       </c>
       <c r="L54" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>American Dream - Alabama Shakes</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Alone For A Year</v>
+        <v>Already There</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/already-there/1866700770</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-16</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Joy Next Door</v>
+        <v>Victory Garden</v>
       </c>
       <c r="G55" t="str">
-        <v>3:22</v>
+        <v>3:50</v>
       </c>
       <c r="H55" t="str">
-        <v>The Maine</v>
+        <v>Young the Giant</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/already-there/1866700309</v>
       </c>
       <c r="L55" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Already There - Young the Giant</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Bring Home My Man</v>
+        <v>ROCK BOTTOM</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-16</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>KINDA HARD</v>
       </c>
       <c r="G56" t="str">
-        <v>4:22</v>
+        <v>2:47</v>
       </c>
       <c r="H56" t="str">
-        <v>Maya Hawke</v>
+        <v>Bilmuri</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
       </c>
       <c r="L56" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>ROCK BOTTOM - Bilmuri</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SUPERMAN</v>
+        <v>Alone For A Year</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-16</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>Joy Next Door</v>
       </c>
       <c r="G57" t="str">
-        <v>3:24</v>
+        <v>3:22</v>
       </c>
       <c r="H57" t="str">
-        <v>South Arcade</v>
+        <v>The Maine</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
       </c>
       <c r="L57" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Alone For A Year - The Maine</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>1989</v>
+        <v>Bring Home My Man</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-16</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>1989 - Single</v>
+        <v>MAITREYA CORSO</v>
       </c>
       <c r="G58" t="str">
-        <v>2:34</v>
+        <v>4:22</v>
       </c>
       <c r="H58" t="str">
-        <v>Nightly</v>
+        <v>Maya Hawke</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
       </c>
       <c r="L58" t="str">
-        <v>1989 - Nightly</v>
+        <v>Bring Home My Man - Maya Hawke</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>waste your pain</v>
+        <v>SUPERMAN</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/superman/1890027996</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-16</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>waste your pain - Single</v>
+        <v>SUPERMAN - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:23</v>
+        <v>3:24</v>
       </c>
       <c r="H59" t="str">
-        <v>Cruz Beckham</v>
+        <v>South Arcade</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/superman/1890027995</v>
       </c>
       <c r="L59" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>SUPERMAN - South Arcade</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Strangers</v>
+        <v>1989</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/1989/1887250155</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-16</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>1989 - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:44</v>
+        <v>2:34</v>
       </c>
       <c r="H60" t="str">
-        <v>Tink</v>
+        <v>Nightly</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/nightly/352310972</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/1989/1887250154</v>
       </c>
       <c r="L60" t="str">
-        <v>Strangers - Tink</v>
+        <v>1989 - Nightly</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Right In Front Of Me</v>
+        <v>waste your pain</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-16</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>waste your pain - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:45</v>
+        <v>2:23</v>
       </c>
       <c r="H61" t="str">
-        <v>Tiny Habits</v>
+        <v>Cruz Beckham</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
       </c>
       <c r="L61" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>waste your pain - Cruz Beckham</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SAME SH!T</v>
+        <v>Strangers</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/strangers/1883252372</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-16</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>F**k, Marry, Kill</v>
       </c>
       <c r="G62" t="str">
-        <v>3:13</v>
+        <v>2:44</v>
       </c>
       <c r="H62" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Tink</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/tink/579974302</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/strangers/1883252371</v>
       </c>
       <c r="L62" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>Strangers - Tink</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Right In Front Of Me</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-16</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>The End is Not the End</v>
+        <v>Right In Front Of Me - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:12</v>
+        <v>2:45</v>
       </c>
       <c r="H63" t="str">
-        <v>Atreyu</v>
+        <v>Tiny Habits</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
       </c>
       <c r="L63" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Right In Front Of Me - Tiny Habits</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Heal</v>
+        <v>SAME SH!T</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-16</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Heal - Single</v>
+        <v>SAME SH!T - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H64" t="str">
-        <v>HAYLA</v>
+        <v>Isaiah Rashad</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
       </c>
       <c r="L64" t="str">
-        <v>Heal - HAYLA</v>
+        <v>SAME SH!T - Isaiah Rashad</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Free</v>
+        <v>Children of Light (feat. Max Cavalera)</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-16</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>The End is Not the End</v>
       </c>
       <c r="G65" t="str">
-        <v>4:13</v>
+        <v>4:12</v>
       </c>
       <c r="H65" t="str">
-        <v>Simone Ashley</v>
+        <v>Atreyu</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
       </c>
       <c r="L65" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Cállate</v>
+        <v>Heal</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/heal/1884661632</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-16</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>Heal - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>1:59</v>
+        <v>3:26</v>
       </c>
       <c r="H66" t="str">
-        <v>Dua Saleh</v>
+        <v>HAYLA</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/heal/1884661625</v>
       </c>
       <c r="L66" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Heal - HAYLA</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Raindrops</v>
+        <v>Free</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/free/1886600087</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-16</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Raindrops - Single</v>
+        <v>Songs I Wrote In New York - EP</v>
       </c>
       <c r="G67" t="str">
-        <v>3:34</v>
+        <v>4:13</v>
       </c>
       <c r="H67" t="str">
-        <v>Rick Astley</v>
+        <v>Simone Ashley</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/free/1886600085</v>
       </c>
       <c r="L67" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Free - Simone Ashley</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>WORK OF ART</v>
+        <v>Cállate</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-16</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>PRODIGY</v>
+        <v>Of Earth &amp; Wires</v>
       </c>
       <c r="G68" t="str">
-        <v>2:27</v>
+        <v>1:59</v>
       </c>
       <c r="H68" t="str">
-        <v>Tkandz</v>
+        <v>Dua Saleh</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
       </c>
       <c r="L68" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>Cállate - Dua Saleh</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Scottie Pippen</v>
+        <v>Raindrops</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-16</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>Raindrops - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>2:34</v>
+        <v>3:34</v>
       </c>
       <c r="H69" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Rick Astley</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
       </c>
       <c r="L69" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>Raindrops - Rick Astley</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Damn Good Actress</v>
+        <v>WORK OF ART</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-16</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PRODIGY</v>
       </c>
       <c r="G70" t="str">
-        <v>2:49</v>
+        <v>2:27</v>
       </c>
       <c r="H70" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Tkandz</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
       </c>
       <c r="L70" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>WORK OF ART - Tkandz</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Ricota</v>
+        <v>Scottie Pippen</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-16</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Ricota - Single</v>
+        <v>Scottie Pippen - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:25</v>
+        <v>2:34</v>
       </c>
       <c r="H71" t="str">
-        <v>ZULAN</v>
+        <v>SUNSHINE BENZI</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
       </c>
       <c r="L71" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>Scottie Pippen - SUNSHINE BENZI</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Kissing The Ground</v>
+        <v>Damn Good Actress</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-16</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Damn Good Actress - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:50</v>
+        <v>2:49</v>
       </c>
       <c r="H72" t="str">
-        <v>Nell Mescal</v>
+        <v>Tiffany Stringer</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
       </c>
       <c r="L72" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>Damn Good Actress - Tiffany Stringer</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Joy</v>
+        <v>Ricota</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/ricota/1889387735</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-16</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>All In Now</v>
+        <v>Ricota - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:41</v>
+        <v>2:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Dogstar</v>
+        <v>ZULAN</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/ricota/1889387732</v>
       </c>
       <c r="L73" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Ricota - ZULAN</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Amor Bonito</v>
+        <v>Kissing The Ground</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-16</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Kissing The Ground - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:44</v>
+        <v>3:50</v>
       </c>
       <c r="H74" t="str">
-        <v>Kany García</v>
+        <v>Nell Mescal</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
       </c>
       <c r="L74" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Kissing The Ground - Nell Mescal</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Patchwork</v>
+        <v>Joy</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/joy/1877978274</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-16</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Patchwork - Single</v>
+        <v>All In Now</v>
       </c>
       <c r="G75" t="str">
-        <v>3:07</v>
+        <v>3:41</v>
       </c>
       <c r="H75" t="str">
-        <v>Carlita</v>
+        <v>Dogstar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/joy/1877978262</v>
       </c>
       <c r="L75" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>Joy - Dogstar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>She's A Devil</v>
+        <v>Amor Bonito</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-16</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>She's A Devil - Single</v>
+        <v>PUERTA ABIERTA</v>
       </c>
       <c r="G76" t="str">
-        <v>3:24</v>
+        <v>2:44</v>
       </c>
       <c r="H76" t="str">
-        <v>Layton Giordani</v>
+        <v>Kany García</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
       </c>
       <c r="L76" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>Amor Bonito - Kany García</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Do It All Alone</v>
+        <v>Patchwork</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-16</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Patchwork - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:52</v>
+        <v>3:07</v>
       </c>
       <c r="H77" t="str">
-        <v>Rend Collective</v>
+        <v>Carlita</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/carlita/599607197</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
       </c>
       <c r="L77" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Patchwork - Carlita</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Time</v>
+        <v>She's A Devil</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-16</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Time - Single</v>
+        <v>She's A Devil - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:20</v>
+        <v>3:24</v>
       </c>
       <c r="H78" t="str">
-        <v>David Leonard</v>
+        <v>Layton Giordani</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
       </c>
       <c r="L78" t="str">
-        <v>Time - David Leonard</v>
+        <v>She's A Devil - Layton Giordani</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Andamos Ready</v>
+        <v>Do It All Alone</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-16</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Do It All Alone - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:10</v>
+        <v>2:52</v>
       </c>
       <c r="H79" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Rend Collective</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
       </c>
       <c r="L79" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Do It All Alone - Rend Collective</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Van y Vienen</v>
+        <v>Time</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/time/1880476913</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-16</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>Time - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:46</v>
+        <v>3:20</v>
       </c>
       <c r="H80" t="str">
-        <v>El Fantasma</v>
+        <v>David Leonard</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/time/1880476790</v>
       </c>
       <c r="L80" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Time - David Leonard</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>No Vuelvas</v>
+        <v>Andamos Ready</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-16</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>Andamos Ready - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H81" t="str">
-        <v>Majo Aguilar</v>
+        <v>Los Tucanes de Tijuana</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
       </c>
       <c r="L81" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>Andamos Ready - Los Tucanes de Tijuana</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>RUNNIN</v>
+        <v>Van y Vienen</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-16</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Van y Vienen - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:40</v>
+        <v>2:46</v>
       </c>
       <c r="H82" t="str">
-        <v>RUA YOUNG</v>
+        <v>El Fantasma</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
       </c>
       <c r="L82" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Van y Vienen - El Fantasma</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Talk You Through It</v>
+        <v>No Vuelvas</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-16</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>No Vuelvas - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:33</v>
+        <v>3:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Majo Aguilar</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
       </c>
       <c r="L83" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>No Vuelvas - Majo Aguilar</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Partners in Crime</v>
+        <v>RUNNIN</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/runnin/1886581872</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-16</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Born to Kill</v>
+        <v>RUNNIN - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>3:50</v>
+        <v>2:40</v>
       </c>
       <c r="H84" t="str">
-        <v>Social Distortion</v>
+        <v>RUA YOUNG</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/runnin/1886581868</v>
       </c>
       <c r="L84" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>RUNNIN - RUA YOUNG</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Change your mind</v>
+        <v>Talk You Through It</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-16</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Change your mind - Single</v>
+        <v>Talk You Through It - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:21</v>
+        <v>3:33</v>
       </c>
       <c r="H85" t="str">
-        <v>Casper Sage</v>
+        <v>Kenyon Dixon</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
       </c>
       <c r="L85" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>Talk You Through It - Kenyon Dixon</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Partners in Crime</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-16</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>Born to Kill</v>
       </c>
       <c r="G86" t="str">
-        <v>3:29</v>
+        <v>3:50</v>
       </c>
       <c r="H86" t="str">
-        <v>The Franklin Electric</v>
+        <v>Social Distortion</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
       </c>
       <c r="L86" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Partners in Crime - Social Distortion</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Change your mind</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-16</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Train on the Island</v>
+        <v>Change your mind - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H87" t="str">
-        <v>Aldous Harding</v>
+        <v>Casper Sage</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
       </c>
       <c r="L87" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Change your mind - Casper Sage</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Lover</v>
+        <v>Bones to Ashes, Dark to Light</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-16</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Lover - Single</v>
+        <v>Bones to Ashes, Dark to Light - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:29</v>
       </c>
       <c r="H88" t="str">
-        <v>Juke Ross</v>
+        <v>The Franklin Electric</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
       </c>
       <c r="L88" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>pink moon</v>
+        <v>Venus in the Zinnia</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-16</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Train on the Island</v>
       </c>
       <c r="G89" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H89" t="str">
-        <v>runo plum</v>
+        <v>Aldous Harding</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
       </c>
       <c r="L89" t="str">
-        <v>pink moon - runo plum</v>
+        <v>Venus in the Zinnia - Aldous Harding</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Summer</v>
+        <v>Lover</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/lover/1878758405</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-16</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Summer - Single</v>
+        <v>Lover - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:21</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Tasha</v>
+        <v>Juke Ross</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/lover/1878758400</v>
       </c>
       <c r="L90" t="str">
-        <v>Summer - Tasha</v>
+        <v>Lover - Juke Ross</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Lizzie mcguire</v>
+        <v>pink moon</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-16</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>Bloom Again - EP</v>
       </c>
       <c r="G91" t="str">
-        <v>4:20</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>Nara's Room</v>
+        <v>runo plum</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
       </c>
       <c r="L91" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>pink moon - runo plum</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Fabienk</v>
+        <v>Summer</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/summer/1884646207</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-16</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Vol.II</v>
+        <v>Summer - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>6:31</v>
+        <v>3:21</v>
       </c>
       <c r="H92" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Tasha</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/summer/1884645989</v>
       </c>
       <c r="L92" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Summer - Tasha</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>My Girl</v>
+        <v>Lizzie mcguire</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-16</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Soren - EP</v>
+        <v>Tearless, thoughtless</v>
       </c>
       <c r="G93" t="str">
-        <v>3:45</v>
+        <v>4:20</v>
       </c>
       <c r="H93" t="str">
-        <v>Orca</v>
+        <v>Nara's Room</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
       </c>
       <c r="L93" t="str">
-        <v>My Girl - Orca</v>
+        <v>Lizzie mcguire - Nara's Room</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bone Structure</v>
+        <v>Fabienk</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-16</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Bone Structure - Single</v>
+        <v>Vol.II</v>
       </c>
       <c r="G94" t="str">
-        <v>3:01</v>
+        <v>6:31</v>
       </c>
       <c r="H94" t="str">
-        <v>Dolder</v>
+        <v>Angine de Poitrine</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
       </c>
       <c r="L94" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>Fabienk - Angine de Poitrine</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Turning Into Us</v>
+        <v>My Girl</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-16</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>Soren - EP</v>
       </c>
       <c r="G95" t="str">
-        <v>3:30</v>
+        <v>3:45</v>
       </c>
       <c r="H95" t="str">
-        <v>Rhys Rutherford</v>
+        <v>Orca</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/orca/1741045781</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
       </c>
       <c r="L95" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>My Girl - Orca</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>Bone Structure</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-16</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>Bone Structure - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:00</v>
+        <v>3:01</v>
       </c>
       <c r="H96" t="str">
-        <v>Osé</v>
+        <v>Dolder</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
       </c>
       <c r="L96" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>Bone Structure - Dolder</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Fright</v>
+        <v>Turning Into Us</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-16</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Fright - Single</v>
+        <v>Turning Into Us - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H97" t="str">
-        <v>Creepy Nuts</v>
+        <v>Rhys Rutherford</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
       </c>
       <c r="L97" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Turning Into Us - Rhys Rutherford</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Smoking In Bed</v>
+        <v>Bother Me (feat. Victony)</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-16</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>Bother Me (feat. Victony) - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>3:24</v>
+        <v>3:00</v>
       </c>
       <c r="H98" t="str">
-        <v>The Bends</v>
+        <v>Osé</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
       </c>
       <c r="L98" t="str">
-        <v>Smoking In Bed - The Bends</v>
+        <v>Bother Me (feat. Victony) - Osé</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Dissonant Void</v>
+        <v>Fright</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+        <v>https://music.apple.com/us/song/fright/1890396431</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-16</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Fright - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:47</v>
+        <v>2:25</v>
       </c>
       <c r="H99" t="str">
-        <v>At The Gates</v>
+        <v>Creepy Nuts</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+        <v>https://music.apple.com/us/album/fright/1890396429</v>
       </c>
       <c r="L99" t="str">
-        <v>The Dissonant Void - At The Gates</v>
+        <v>Fright - Creepy Nuts</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nine Days Of Rain</v>
+        <v>Smoking In Bed</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-16</v>
@@ -4175,68 +4175,144 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Savage Imperial Death March</v>
+        <v>Smoking In Bed - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>3:51</v>
+        <v>3:24</v>
       </c>
       <c r="H100" t="str">
-        <v>Melvins</v>
+        <v>The Bends</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
+        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
       </c>
       <c r="L100" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
+        <v>Smoking In Bed - The Bends</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>The Dissonant Void</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G101" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H101" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
+      </c>
+      <c r="L101" t="str">
+        <v>The Dissonant Void - At The Gates</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Nine Days Of Rain</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>Savage Imperial Death March</v>
+      </c>
+      <c r="G102" t="str">
+        <v>3:51</v>
+      </c>
+      <c r="H102" t="str">
+        <v>Melvins</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/melvins/737433</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Nine Days Of Rain - Melvins</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Invocation of the Dreamer</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D103" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G103" t="str">
         <v>4:46</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H103" t="str">
         <v>Khemmis</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L103" t="str">
         <v>Invocation of the Dreamer - Khemmis</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L100"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,3883 +436,3769 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>drop dead</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>The Nightlife</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G2" t="str">
-        <v>3:32</v>
+        <v>3:44</v>
       </c>
       <c r="H2" t="str">
-        <v>Honey Dijon</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L2" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>First Light</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G3" t="str">
-        <v>3:14</v>
+        <v>3:24</v>
       </c>
       <c r="H3" t="str">
-        <v>DANNA</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L3" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Bottom Of Your Boots</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/bottom-of-your-boots/1869436848</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>Dandelion</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G4" t="str">
-        <v>3:19</v>
+        <v>2:50</v>
       </c>
       <c r="H4" t="str">
-        <v>Ella Langley</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/ella-langley/1384373733</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/bottom-of-your-boots/1869436835</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L4" t="str">
-        <v>Bottom Of Your Boots - Ella Langley</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>RUNWAY</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/runway/1891472591</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>RUNWAY - Single</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G5" t="str">
-        <v>2:51</v>
+        <v>2:36</v>
       </c>
       <c r="H5" t="str">
-        <v>Lady Gaga</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/lady-gaga/277293880</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/runway/1891472590</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L5" t="str">
-        <v>RUNWAY - Lady Gaga</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Back and Forth (feat. Missy Elliott)</v>
+        <v>Rackies</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/back-and-forth-feat-missy-elliott/1885055415</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Kehlani</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G6" t="str">
-        <v>3:34</v>
+        <v>2:53</v>
       </c>
       <c r="H6" t="str">
-        <v>Kehlani</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/kehlani/690126399</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/back-and-forth-feat-missy-elliott/1885055310</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L6" t="str">
-        <v>Back and Forth (feat. Missy Elliott) - Kehlani</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Mr. Know It All</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/mr-know-it-all/1889361602</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Mr. Know It All - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G7" t="str">
-        <v>3:18</v>
+        <v>3:33</v>
       </c>
       <c r="H7" t="str">
-        <v>Teddy Swims</v>
+        <v>Tyla</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/teddy-swims/1462541757</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/mr-know-it-all/1889361601</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L7" t="str">
-        <v>Mr. Know It All - Teddy Swims</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Bad Angel</v>
+        <v>Potential</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/bad-angel/1889611957</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Bad Angel - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>2:33</v>
+        <v>4:02</v>
       </c>
       <c r="H8" t="str">
-        <v>Anyma</v>
+        <v>sombr</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/anyma/1505813449</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/bad-angel/1889611955</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L8" t="str">
-        <v>Bad Angel - Anyma</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Step (feat. Swizz Beatz)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/step-feat-swizz-beatz/1886977955</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>10 Til' Midnight</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:34</v>
+        <v>3:04</v>
       </c>
       <c r="H9" t="str">
-        <v>Snoop Dogg</v>
+        <v>Maluma</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/snoop-dogg/21769</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/step-feat-swizz-beatz/1886977935</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L9" t="str">
-        <v>Step (feat. Swizz Beatz) - Snoop Dogg</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Sweet Hallelujah</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/sweet-hallelujah/1886800532</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Sweet Hallelujah - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G10" t="str">
-        <v>3:02</v>
+        <v>3:32</v>
       </c>
       <c r="H10" t="str">
-        <v>Royel Otis</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/royel-otis/1537647213</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/sweet-hallelujah/1886800353</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L10" t="str">
-        <v>Sweet Hallelujah - Royel Otis</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Beauty Pageant</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/beauty-pageant/1859630301</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>Cruel World</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:15</v>
+        <v>2:50</v>
       </c>
       <c r="H11" t="str">
-        <v>Holly Humberstone</v>
+        <v>Young Miko</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/holly-humberstone/1495433177</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/beauty-pageant/1859629846</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L11" t="str">
-        <v>Beauty Pageant - Holly Humberstone</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>PINKY UP</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/pinky-up/1888235066</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>PINKY UP - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G12" t="str">
-        <v>2:11</v>
+        <v>3:14</v>
       </c>
       <c r="H12" t="str">
-        <v>KATSEYE</v>
+        <v>DANNA</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/katseye/1754284416</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/pinky-up/1888235065</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L12" t="str">
-        <v>PINKY UP - KATSEYE</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>BIAF &lt;3</v>
+        <v>i just get worse</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:50</v>
+        <v>3:25</v>
       </c>
       <c r="H13" t="str">
-        <v>Young Miko</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L13" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Sick Of Love</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/sick-of-love/1857952499</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>The Afterparty</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G14" t="str">
-        <v>3:36</v>
+        <v>3:23</v>
       </c>
       <c r="H14" t="str">
-        <v>Lykke Li</v>
+        <v>John Summit</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/lykke-li/263435943</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/sick-of-love/1857952252</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L14" t="str">
-        <v>Sick Of Love - Lykke Li</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Ember</v>
+        <v>Side Effects</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/ember/1880484164</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>For Love of Grace &amp; the Hereafter</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G15" t="str">
-        <v>3:25</v>
+        <v>3:17</v>
       </c>
       <c r="H15" t="str">
-        <v>Iceage</v>
+        <v>ZAYN</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/iceage/406846711</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/ember/1880484160</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L15" t="str">
-        <v>Ember - Iceage</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>i just get worse</v>
+        <v>Numb</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>i just get worse - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:25</v>
+        <v>2:34</v>
       </c>
       <c r="H16" t="str">
-        <v>Kevian Kraemer</v>
+        <v>JT</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L16" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Turnaround</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/turnaround/1885084566</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Turnaround / I'm Hooked - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:14</v>
+        <v>3:05</v>
       </c>
       <c r="H17" t="str">
-        <v>54 Ultra</v>
+        <v>Labrinth</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/54-ultra/1521471420</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/turnaround/1885084282</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L17" t="str">
-        <v>Turnaround - 54 Ultra</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:05</v>
+        <v>2:47</v>
       </c>
       <c r="H18" t="str">
-        <v>Labrinth</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L18" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Madwoman</v>
+        <v>My Way</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/madwoman/1873116853</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>A Matter of Time: The Final Hour</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:59</v>
+        <v>4:02</v>
       </c>
       <c r="H19" t="str">
-        <v>Laufey</v>
+        <v>Riley Green</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/laufey/1504424880</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/madwoman/1873116455</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L19" t="str">
-        <v>Madwoman - Laufey</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Come Clean (Mine)</v>
+        <v>Ache</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/come-clean-mine/1889962796</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Come Clean (Mine) - Single</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>3:33</v>
+        <v>4:25</v>
       </c>
       <c r="H20" t="str">
-        <v>Hilary Duff</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/come-clean-mine/1889962541</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L20" t="str">
-        <v>Come Clean (Mine) - Hilary Duff</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>One of Them</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/one-of-them/1891015806</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>One of Them - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G21" t="str">
-        <v>3:24</v>
+        <v>4:09</v>
       </c>
       <c r="H21" t="str">
-        <v>DJ Khaled</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/dj-khaled/157749142</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/one-of-them/1891015797</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L21" t="str">
-        <v>One of Them - DJ Khaled</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/chicken-talkin-bastard/1889672894</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E22" t="str">
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Chicken Talkin Bastard</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>2:49</v>
+        <v>2:13</v>
       </c>
       <c r="H22" t="str">
-        <v>Bossman Dlow</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/bossman-dlow/1474308236</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/chicken-talkin-bastard/1889672893</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L22" t="str">
-        <v>Chicken Talkin Bastard - Bossman Dlow</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>stuck</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/stuck/1875303118</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E23" t="str">
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>ghosted - EP</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G23" t="str">
-        <v>2:41</v>
+        <v>3:57</v>
       </c>
       <c r="H23" t="str">
-        <v>Saint Harison</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/saint-harison/1639595302</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/stuck/1875302904</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L23" t="str">
-        <v>stuck - Saint Harison</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>De Lejitos</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/de-lejitos/1887715567</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E24" t="str">
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>De Lejitos - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:27</v>
+        <v>4:21</v>
       </c>
       <c r="H24" t="str">
-        <v>Jay Wheeler</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/jay-wheeler/164376380</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/de-lejitos/1887715566</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L24" t="str">
-        <v>De Lejitos - Jay Wheeler</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Echo</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/echo/1891104992</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E25" t="str">
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Echo - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:39</v>
+        <v>3:26</v>
       </c>
       <c r="H25" t="str">
-        <v>The Chainsmokers</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/the-chainsmokers/580391756</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/echo/1891104991</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L25" t="str">
-        <v>Echo - The Chainsmokers</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Where We Go</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/where-we-go/1889655589</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E26" t="str">
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Where We Go - Single</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:16</v>
+        <v>2:22</v>
       </c>
       <c r="H26" t="str">
-        <v>Marshmello</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/marshmello/980795202</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/where-we-go/1889655580</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L26" t="str">
-        <v>Where We Go - Marshmello</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Te hacen falta dos</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/te-hacen-falta-dos/1881764327</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E27" t="str">
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Apambichao</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G27" t="str">
-        <v>2:41</v>
+        <v>2:34</v>
       </c>
       <c r="H27" t="str">
-        <v>Manuel Turizo</v>
+        <v>MUNA</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/manuel-turizo/1186116587</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/te-hacen-falta-dos/1881763954</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L27" t="str">
-        <v>Te hacen falta dos - Manuel Turizo</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Of All People</v>
+        <v>Superbloom</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/of-all-people/1877913732</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E28" t="str">
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Superbloom</v>
       </c>
       <c r="G28" t="str">
-        <v>2:34</v>
+        <v>4:11</v>
       </c>
       <c r="H28" t="str">
-        <v>Foo Fighters</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/of-all-people/1877913489</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L28" t="str">
-        <v>Of All People - Foo Fighters</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Waves of You</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/waves-of-you/1890508898</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Waves of You - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G29" t="str">
-        <v>3:15</v>
+        <v>1:40</v>
       </c>
       <c r="H29" t="str">
-        <v>After Hours</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/after-hours/1890531257</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/waves-of-you/1890508897</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L29" t="str">
-        <v>Waves of You - After Hours</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>idea 1</v>
+        <v>Make You Move</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/idea-1/1884060944</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>idea 1 - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G30" t="str">
-        <v>3:25</v>
+        <v>2:24</v>
       </c>
       <c r="H30" t="str">
-        <v>Kelela</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/kelela/549186342</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/idea-1/1884060943</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L30" t="str">
-        <v>idea 1 - Kelela</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Attitude</v>
+        <v>FERRARI</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/attitude/1840517116</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Sweat</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>3:13</v>
+        <v>2:14</v>
       </c>
       <c r="H31" t="str">
-        <v>Melanie C</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/melanie-c/653819</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/attitude/1840516706</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L31" t="str">
-        <v>Attitude - Melanie C</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Carrie Bradshaw</v>
+        <v>Stick With You</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/carrie-bradshaw/1889945356</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E32" t="str">
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Carrie Bradshaw - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G32" t="str">
-        <v>2:54</v>
+        <v>2:33</v>
       </c>
       <c r="H32" t="str">
-        <v>Kylie Cantrall</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/kylie-cantrall/1459186568</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/carrie-bradshaw/1889945355</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L32" t="str">
-        <v>Carrie Bradshaw - Kylie Cantrall</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Work</v>
+        <v>KGB</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/work/1885916583</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E33" t="str">
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Work - Single</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:51</v>
+        <v>2:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Pitbull</v>
+        <v>Adela</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/pitbull/27044968</v>
+        <v>https://music.apple.com/us/artist/adela/1423152831</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/work/1885916578</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L33" t="str">
-        <v>Work - Pitbull</v>
+        <v>KGB - Adela</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Obvious</v>
+        <v>Holly!</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/obvious/1891759136</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E34" t="str">
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Obvious - Single</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>3:10</v>
       </c>
       <c r="H34" t="str">
-        <v>Chris Brown</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/chris-brown/95705522</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/obvious/1891759134</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L34" t="str">
-        <v>Obvious - Chris Brown</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>As Time Goes By</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/as-time-goes-by/1880847909</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E35" t="str">
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>CINEMATIC</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G35" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H35" t="str">
-        <v>Josh Groban</v>
+        <v>6LACK</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/josh-groban/170344</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/as-time-goes-by/1880847908</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L35" t="str">
-        <v>As Time Goes By - Josh Groban</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>My Mess</v>
+        <v>Move Time</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/my-mess/1886119370</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>My Mess, My Heart, My Life.</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:11</v>
+        <v>3:39</v>
       </c>
       <c r="H36" t="str">
-        <v>Myles Smith</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/myles-smith/1249499491</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/my-mess/1886119367</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L36" t="str">
-        <v>My Mess - Myles Smith</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Going Shopping</v>
+        <v>I Want You</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/going-shopping/1891161450</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E37" t="str">
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Reality Awaits</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G37" t="str">
-        <v>4:21</v>
+        <v>3:10</v>
       </c>
       <c r="H37" t="str">
-        <v>The Strokes</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/the-strokes/560289</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/going-shopping/1891161441</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L37" t="str">
-        <v>Going Shopping - The Strokes</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Choka Choka</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/choka-choka/1891400226</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Choka Choka - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>2:11</v>
+        <v>3:11</v>
       </c>
       <c r="H38" t="str">
-        <v>Anitta</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/choka-choka/1891400123</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L38" t="str">
-        <v>Choka Choka - Anitta</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>side slider</v>
+        <v>Ring</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/side-slider/1884983636</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Mr. Lovebomb</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:47</v>
+        <v>3:21</v>
       </c>
       <c r="H39" t="str">
-        <v>Isaia Huron</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/isaia-huron/1490954483</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/side-slider/1884983213</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L39" t="str">
-        <v>side slider - Isaia Huron</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Woman I Am</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/woman-i-am/1893733064</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>SE9</v>
+        <v>Wild</v>
       </c>
       <c r="G40" t="str">
-        <v>3:31</v>
+        <v>3:24</v>
       </c>
       <c r="H40" t="str">
-        <v>Skye Newman</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/skye-newman/1799174381</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/woman-i-am/1893733056</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L40" t="str">
-        <v>Woman I Am - Skye Newman</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bubee</v>
+        <v>Stay Love</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/bubee/1885450942</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Bubee - Single</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G41" t="str">
-        <v>3:02</v>
+        <v>3:26</v>
       </c>
       <c r="H41" t="str">
-        <v>ILLIT</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/illit/1734551937</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/bubee/1885450328</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L41" t="str">
-        <v>Bubee - ILLIT</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Good Morning</v>
+        <v>Love Me</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/good-morning/1887166609</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>24</v>
+        <v>Dear God</v>
       </c>
       <c r="G42" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H42" t="str">
-        <v>Alexis Ffrench</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/alexis-ffrench/342515428</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/good-morning/1887166427</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L42" t="str">
-        <v>Good Morning - Alexis Ffrench</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Positano</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/positano/1886736661</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Scenes from a Velvet Room</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H43" t="str">
-        <v>Stephan Moccio</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/stephan-moccio/941440</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/positano/1886736650</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L43" t="str">
-        <v>Positano - Stephan Moccio</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>sophie</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/sophie/1887348036</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>notes from the in between - EP</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G44" t="str">
-        <v>2:36</v>
+        <v>3:52</v>
       </c>
       <c r="H44" t="str">
-        <v>kenzie</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/kenzie/1472031971</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/sophie/1887348032</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L44" t="str">
-        <v>sophie - kenzie</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kiss goodbye</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/kiss-goodbye/1889685407</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>kiss goodbye / brb - Single</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>2:43</v>
+        <v>3:08</v>
       </c>
       <c r="H45" t="str">
-        <v>The Two Lips</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/the-two-lips/1821008741</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/kiss-goodbye/1889685404</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L45" t="str">
-        <v>kiss goodbye - The Two Lips</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENTRÉGAME</v>
+        <v>Desgraça</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/entr%C3%A9game/1887410456</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>RADIO VENEZUELA</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G46" t="str">
-        <v>3:08</v>
+        <v>2:50</v>
       </c>
       <c r="H46" t="str">
-        <v>Chino &amp; Nacho</v>
+        <v>Anitta</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/chino-nacho/344579832</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/entr%C3%A9game/1887409818</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L46" t="str">
-        <v>ENTRÉGAME - Chino &amp; Nacho</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>EL SENTRITA</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/el-sentrita/1891769916</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>ETERNO</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G47" t="str">
-        <v>2:57</v>
+        <v>2:44</v>
       </c>
       <c r="H47" t="str">
-        <v>Calle 24</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/calle-24/1550107106</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/el-sentrita/1891769892</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L47" t="str">
-        <v>EL SENTRITA - Calle 24</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SOMETHING IN THE WATER</v>
+        <v>Dansons</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/something-in-the-water/1887768842</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>DAWN PATROL</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:39</v>
+        <v>3:26</v>
       </c>
       <c r="H48" t="str">
-        <v>PARTY WAVE</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/party-wave/1890006227</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/something-in-the-water/1887768606</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L48" t="str">
-        <v>SOMETHING IN THE WATER - PARTY WAVE</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Formation</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/formation/1882714068</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Formation - Single</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:36</v>
+        <v>2:57</v>
       </c>
       <c r="H49" t="str">
-        <v>Adekunle Gold</v>
+        <v>Trousdale</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/adekunle-gold/1035126760</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/formation/1882714060</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L49" t="str">
-        <v>Formation - Adekunle Gold</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Who Will You Follow</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/who-will-you-follow/1891104594</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Sanctuary</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G50" t="str">
-        <v>3:55</v>
+        <v>5:21</v>
       </c>
       <c r="H50" t="str">
-        <v>Evanescence</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/evanescence/42102393</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/who-will-you-follow/1891104460</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L50" t="str">
-        <v>Who Will You Follow - Evanescence</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>That's When You Know</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/thats-when-you-know/1890152583</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>That's When You Know - Single</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G51" t="str">
-        <v>3:13</v>
+        <v>2:49</v>
       </c>
       <c r="H51" t="str">
-        <v>Kygo</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/thats-when-you-know/1890152580</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L51" t="str">
-        <v>That's When You Know - Kygo</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Drinking Game</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/drinking-game/1889994437</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Drinking Game - Single</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G52" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H52" t="str">
-        <v>Warren Zeiders</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/warren-zeiders/1545729343</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/drinking-game/1889994435</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L52" t="str">
-        <v>Drinking Game - Warren Zeiders</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Anything But Me</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/anything-but-me/1874068213</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>In The Feeling</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G53" t="str">
-        <v>4:59</v>
+        <v>7:56</v>
       </c>
       <c r="H53" t="str">
-        <v>Owen Riegling</v>
+        <v>TOMORA</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/owen-riegling/1471251438</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/anything-but-me/1874067488</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L53" t="str">
-        <v>Anything But Me - Owen Riegling</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>American Dream</v>
+        <v>Everything U</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/american-dream/1889674399</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>American Dream - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G54" t="str">
-        <v>4:27</v>
+        <v>3:30</v>
       </c>
       <c r="H54" t="str">
-        <v>Alabama Shakes</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/alabama-shakes/498509884</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/american-dream/1889674398</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L54" t="str">
-        <v>American Dream - Alabama Shakes</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Already There</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/already-there/1866700770</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Victory Garden</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G55" t="str">
-        <v>3:50</v>
+        <v>4:21</v>
       </c>
       <c r="H55" t="str">
-        <v>Young the Giant</v>
+        <v>ZERB</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/young-the-giant/394582977</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/already-there/1866700309</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L55" t="str">
-        <v>Already There - Young the Giant</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ROCK BOTTOM</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/rock-bottom/1871578110</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>KINDA HARD</v>
+        <v>soft pop</v>
       </c>
       <c r="G56" t="str">
-        <v>2:47</v>
+        <v>3:02</v>
       </c>
       <c r="H56" t="str">
-        <v>Bilmuri</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/bilmuri/1072442999</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/rock-bottom/1871578103</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L56" t="str">
-        <v>ROCK BOTTOM - Bilmuri</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Alone For A Year</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/alone-for-a-year/1874354217</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Joy Next Door</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H57" t="str">
-        <v>The Maine</v>
+        <v>Subtronics</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/the-maine/268579357</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/alone-for-a-year/1874354034</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L57" t="str">
-        <v>Alone For A Year - The Maine</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Bring Home My Man</v>
+        <v>Track 3</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/bring-home-my-man/1878649634</v>
+        <v>https://music.apple.com/us/song/track-3/1889992071</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>MAITREYA CORSO</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G58" t="str">
-        <v>4:22</v>
+        <v>2:56</v>
       </c>
       <c r="H58" t="str">
-        <v>Maya Hawke</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/maya-hawke/1473393677</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/bring-home-my-man/1878649394</v>
+        <v>https://music.apple.com/us/album/track-3/1889992065</v>
       </c>
       <c r="L58" t="str">
-        <v>Bring Home My Man - Maya Hawke</v>
+        <v>Track 3 - rjtheweirdo</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SUPERMAN</v>
+        <v>Outside</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/superman/1890027996</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>SUPERMAN - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:24</v>
+        <v>3:15</v>
       </c>
       <c r="H59" t="str">
-        <v>South Arcade</v>
+        <v>Inayah</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/south-arcade/1614415981</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/superman/1890027995</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L59" t="str">
-        <v>SUPERMAN - South Arcade</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>1989</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/1989/1887250155</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>1989 - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:34</v>
+        <v>2:25</v>
       </c>
       <c r="H60" t="str">
-        <v>Nightly</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/nightly/352310972</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/1989/1887250154</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L60" t="str">
-        <v>1989 - Nightly</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>waste your pain</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/waste-your-pain/1887908088</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>waste your pain - Single</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:23</v>
+        <v>3:12</v>
       </c>
       <c r="H61" t="str">
-        <v>Cruz Beckham</v>
+        <v>Max McNown</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/cruz-beckham/1182571263</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/waste-your-pain/1887908087</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L61" t="str">
-        <v>waste your pain - Cruz Beckham</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Strangers</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/strangers/1883252372</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>F**k, Marry, Kill</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G62" t="str">
-        <v>2:44</v>
+        <v>4:19</v>
       </c>
       <c r="H62" t="str">
-        <v>Tink</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/tink/579974302</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/strangers/1883252371</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L62" t="str">
-        <v>Strangers - Tink</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Right In Front Of Me</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/right-in-front-of-me/1886205894</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E63" t="str">
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Right In Front Of Me - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:45</v>
+        <v>3:14</v>
       </c>
       <c r="H63" t="str">
-        <v>Tiny Habits</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/tiny-habits/1643949763</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/right-in-front-of-me/1886205537</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L63" t="str">
-        <v>Right In Front Of Me - Tiny Habits</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SAME SH!T</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/same-sh-t/1888333272</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E64" t="str">
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>SAME SH!T - Single</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:13</v>
+        <v>3:26</v>
       </c>
       <c r="H64" t="str">
-        <v>Isaiah Rashad</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/isaiah-rashad/605391263</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/same-sh-t/1888333271</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L64" t="str">
-        <v>SAME SH!T - Isaiah Rashad</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Children of Light (feat. Max Cavalera)</v>
+        <v>Deep Water</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/children-of-light-feat-max-cavalera/1873286318</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E65" t="str">
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>The End is Not the End</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G65" t="str">
-        <v>4:12</v>
+        <v>2:33</v>
       </c>
       <c r="H65" t="str">
-        <v>Atreyu</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/atreyu/6095061</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/children-of-light-feat-max-cavalera/1873285466</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L65" t="str">
-        <v>Children of Light (feat. Max Cavalera) - Atreyu</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Heal</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/heal/1884661632</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E66" t="str">
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Heal - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G66" t="str">
-        <v>3:26</v>
+        <v>3:13</v>
       </c>
       <c r="H66" t="str">
-        <v>HAYLA</v>
+        <v>ERNEST</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/hayla/1489979989</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/heal/1884661625</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L66" t="str">
-        <v>Heal - HAYLA</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Free</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/free/1886600087</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Songs I Wrote In New York - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>4:13</v>
+        <v>1:58</v>
       </c>
       <c r="H67" t="str">
-        <v>Simone Ashley</v>
+        <v>Marca MP</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/simone-ashley/1888142588</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/free/1886600085</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L67" t="str">
-        <v>Free - Simone Ashley</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Cállate</v>
+        <v>Price of Love</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/ca-llate/1868826996</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Of Earth &amp; Wires</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G68" t="str">
-        <v>1:59</v>
+        <v>3:29</v>
       </c>
       <c r="H68" t="str">
-        <v>Dua Saleh</v>
+        <v>Benny G</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/dua-saleh/1442780979</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/ca-llate/1868826829</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L68" t="str">
-        <v>Cállate - Dua Saleh</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Raindrops</v>
+        <v>Las Flores</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/raindrops/1888238250</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Raindrops - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:34</v>
+        <v>2:59</v>
       </c>
       <c r="H69" t="str">
-        <v>Rick Astley</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/rick-astley/669771</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/raindrops/1888238243</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L69" t="str">
-        <v>Raindrops - Rick Astley</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>WORK OF ART</v>
+        <v>To The Moon</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/work-of-art/1891439319</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E70" t="str">
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>PRODIGY</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>2:27</v>
+        <v>3:42</v>
       </c>
       <c r="H70" t="str">
-        <v>Tkandz</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/tkandz/1596651878</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/work-of-art/1891439309</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L70" t="str">
-        <v>WORK OF ART - Tkandz</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Scottie Pippen</v>
+        <v>MATCHA</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/scottie-pippen/1890022533</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E71" t="str">
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Scottie Pippen - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G71" t="str">
-        <v>2:34</v>
+        <v>2:36</v>
       </c>
       <c r="H71" t="str">
-        <v>SUNSHINE BENZI</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/sunshine-benzi/1884937174</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/scottie-pippen/1890022532</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L71" t="str">
-        <v>Scottie Pippen - SUNSHINE BENZI</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Damn Good Actress</v>
+        <v>PROWLER</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/damn-good-actress/1888228994</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Damn Good Actress - Single</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:49</v>
+        <v>2:45</v>
       </c>
       <c r="H72" t="str">
-        <v>Tiffany Stringer</v>
+        <v>Waterparks</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/tiffany-stringer/559628818</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/damn-good-actress/1888228993</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L72" t="str">
-        <v>Damn Good Actress - Tiffany Stringer</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Ricota</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/ricota/1889387735</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>Ricota - Single</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G73" t="str">
-        <v>2:25</v>
+        <v>3:14</v>
       </c>
       <c r="H73" t="str">
-        <v>ZULAN</v>
+        <v>Wage War</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/zulan/1807249833</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/ricota/1889387732</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L73" t="str">
-        <v>Ricota - ZULAN</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Kissing The Ground</v>
+        <v>how far down</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/kissing-the-ground/1888473785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Kissing The Ground - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G74" t="str">
-        <v>3:50</v>
+        <v>2:59</v>
       </c>
       <c r="H74" t="str">
-        <v>Nell Mescal</v>
+        <v>Camylio</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/nell-mescal/1495475912</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/kissing-the-ground/1888473303</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L74" t="str">
-        <v>Kissing The Ground - Nell Mescal</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Joy</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/joy/1877978274</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E75" t="str">
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>All In Now</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:41</v>
+        <v>2:26</v>
       </c>
       <c r="H75" t="str">
-        <v>Dogstar</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/dogstar/306221427</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/joy/1877978262</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L75" t="str">
-        <v>Joy - Dogstar</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Amor Bonito</v>
+        <v>Spin</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/amor-bonito/1880238581</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E76" t="str">
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>PUERTA ABIERTA</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>2:44</v>
+        <v>4:15</v>
       </c>
       <c r="H76" t="str">
-        <v>Kany García</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/kany-garc%C3%ADa/251432197</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/amor-bonito/1880238437</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L76" t="str">
-        <v>Amor Bonito - Kany García</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Patchwork</v>
+        <v>MILAN</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/patchwork/1886702082</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E77" t="str">
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Patchwork - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>3:07</v>
+        <v>2:16</v>
       </c>
       <c r="H77" t="str">
-        <v>Carlita</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/carlita/599607197</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/patchwork/1886702081</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L77" t="str">
-        <v>Patchwork - Carlita</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>She's A Devil</v>
+        <v>SHABA</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/shes-a-devil/1890195202</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E78" t="str">
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>She's A Devil - Single</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>3:24</v>
+        <v>2:01</v>
       </c>
       <c r="H78" t="str">
-        <v>Layton Giordani</v>
+        <v>SPINALL</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/layton-giordani/748431694</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/shes-a-devil/1890195198</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L78" t="str">
-        <v>She's A Devil - Layton Giordani</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Do It All Alone</v>
+        <v>Forever</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/do-it-all-alone/1887356036</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E79" t="str">
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Do It All Alone - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G79" t="str">
-        <v>2:52</v>
+        <v>3:38</v>
       </c>
       <c r="H79" t="str">
-        <v>Rend Collective</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/rend-collective/775030640</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/do-it-all-alone/1887355945</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L79" t="str">
-        <v>Do It All Alone - Rend Collective</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Time</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/time/1880476913</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E80" t="str">
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Time - Single</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:20</v>
+        <v>2:46</v>
       </c>
       <c r="H80" t="str">
-        <v>David Leonard</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/david-leonard/1447310166</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/time/1880476790</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L80" t="str">
-        <v>Time - David Leonard</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Andamos Ready</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/andamos-ready/1883135067</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E81" t="str">
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Andamos Ready - Single</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G81" t="str">
-        <v>3:10</v>
+        <v>2:57</v>
       </c>
       <c r="H81" t="str">
-        <v>Los Tucanes de Tijuana</v>
+        <v>Terror</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/los-tucanes-de-tijuana/90197</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/andamos-ready/1883135066</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L81" t="str">
-        <v>Andamos Ready - Los Tucanes de Tijuana</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Van y Vienen</v>
+        <v>Confused</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/van-y-vienen/1889235209</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E82" t="str">
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Van y Vienen - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G82" t="str">
-        <v>2:46</v>
+        <v>2:56</v>
       </c>
       <c r="H82" t="str">
-        <v>El Fantasma</v>
+        <v>cortex</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/el-fantasma/1245916228</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/van-y-vienen/1889235201</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L82" t="str">
-        <v>Van y Vienen - El Fantasma</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>No Vuelvas</v>
+        <v>On The Low</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/no-vuelvas/1888677229</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E83" t="str">
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>No Vuelvas - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>3:46</v>
+        <v>3:29</v>
       </c>
       <c r="H83" t="str">
-        <v>Majo Aguilar</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/majo-aguilar/1472659171</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/no-vuelvas/1888677228</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L83" t="str">
-        <v>No Vuelvas - Majo Aguilar</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>RUNNIN</v>
+        <v>Wannabe</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/runnin/1886581872</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E84" t="str">
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>RUNNIN - Single</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:40</v>
+        <v>2:30</v>
       </c>
       <c r="H84" t="str">
-        <v>RUA YOUNG</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/rua-young/1782603897</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/runnin/1886581868</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L84" t="str">
-        <v>RUNNIN - RUA YOUNG</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Talk You Through It</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/talk-you-through-it/1889279398</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Talk You Through It - Single</v>
+        <v>Middle Child</v>
       </c>
       <c r="G85" t="str">
-        <v>3:33</v>
+        <v>3:32</v>
       </c>
       <c r="H85" t="str">
-        <v>Kenyon Dixon</v>
+        <v>Amma</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/kenyon-dixon/432966456</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/talk-you-through-it/1889279392</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L85" t="str">
-        <v>Talk You Through It - Kenyon Dixon</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Partners in Crime</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/partners-in-crime/1873280361</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E86" t="str">
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Born to Kill</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G86" t="str">
-        <v>3:50</v>
+        <v>3:24</v>
       </c>
       <c r="H86" t="str">
-        <v>Social Distortion</v>
+        <v>Venom</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/social-distortion/543473</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/partners-in-crime/1873280355</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L86" t="str">
-        <v>Partners in Crime - Social Distortion</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Change your mind</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/change-your-mind/1886571624</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E87" t="str">
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Change your mind - Single</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:21</v>
+        <v>3:22</v>
       </c>
       <c r="H87" t="str">
-        <v>Casper Sage</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/casper-sage/1460817970</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/change-your-mind/1886571623</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L87" t="str">
-        <v>Change your mind - Casper Sage</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Bones to Ashes, Dark to Light</v>
+        <v>Taylor</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/bones-to-ashes-dark-to-light/1885581311</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E88" t="str">
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Bones to Ashes, Dark to Light - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G88" t="str">
-        <v>3:29</v>
+        <v>4:15</v>
       </c>
       <c r="H88" t="str">
-        <v>The Franklin Electric</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/the-franklin-electric/579427453</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/bones-to-ashes-dark-to-light/1885581310</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L88" t="str">
-        <v>Bones to Ashes, Dark to Light - The Franklin Electric</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Venus in the Zinnia</v>
+        <v>Yours</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/venus-in-the-zinnia/1876846403</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E89" t="str">
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Train on the Island</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>3:17</v>
+        <v>4:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Aldous Harding</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/aldous-harding/896764341</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/venus-in-the-zinnia/1876846303</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L89" t="str">
-        <v>Venus in the Zinnia - Aldous Harding</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Lover</v>
+        <v>Pepper</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/lover/1878758405</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Lover - Single</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>4:54</v>
       </c>
       <c r="H90" t="str">
-        <v>Juke Ross</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/juke-ross/1112539089</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/lover/1878758400</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L90" t="str">
-        <v>Lover - Juke Ross</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>pink moon</v>
+        <v>No Driver</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/pink-moon/1878228442</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Bloom Again - EP</v>
+        <v>Roses</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>3:48</v>
       </c>
       <c r="H91" t="str">
-        <v>runo plum</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/runo-plum/1571991360</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/pink-moon/1878228434</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L91" t="str">
-        <v>pink moon - runo plum</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Summer</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/summer/1884646207</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Summer - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:21</v>
+        <v>3:13</v>
       </c>
       <c r="H92" t="str">
-        <v>Tasha</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/tasha/1413936117</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/summer/1884645989</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L92" t="str">
-        <v>Summer - Tasha</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Lizzie mcguire</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/lizzie-mcguire/1873123794</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Tearless, thoughtless</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>4:20</v>
+        <v>2:18</v>
       </c>
       <c r="H93" t="str">
-        <v>Nara's Room</v>
+        <v>H.LLS</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/naras-room/1556457239</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/lizzie-mcguire/1873123366</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L93" t="str">
-        <v>Lizzie mcguire - Nara's Room</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Fabienk</v>
+        <v>Powder</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/fabienk/1876355939</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Vol.II</v>
+        <v>Powder</v>
       </c>
       <c r="G94" t="str">
-        <v>6:31</v>
+        <v>4:41</v>
       </c>
       <c r="H94" t="str">
-        <v>Angine de Poitrine</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/angine-de-poitrine/1750092191</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/fabienk/1876355936</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L94" t="str">
-        <v>Fabienk - Angine de Poitrine</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>My Girl</v>
+        <v>Knuckle</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/my-girl/1888266119</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Soren - EP</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>3:45</v>
+        <v>2:20</v>
       </c>
       <c r="H95" t="str">
-        <v>Orca</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/orca/1741045781</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/my-girl/1888266118</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L95" t="str">
-        <v>My Girl - Orca</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bone Structure</v>
+        <v>For The Ride</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/bone-structure/1889250911</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Bone Structure - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>3:01</v>
+        <v>2:43</v>
       </c>
       <c r="H96" t="str">
-        <v>Dolder</v>
+        <v>Snakehips</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/dolder/1841805181</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/bone-structure/1889250905</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L96" t="str">
-        <v>Bone Structure - Dolder</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Turning Into Us</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/turning-into-us/1886600375</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Turning Into Us - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>3:30</v>
+        <v>2:19</v>
       </c>
       <c r="H97" t="str">
-        <v>Rhys Rutherford</v>
+        <v>daydreamers</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/rhys-rutherford/1368721814</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/turning-into-us/1886600374</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L97" t="str">
-        <v>Turning Into Us - Rhys Rutherford</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Bother Me (feat. Victony)</v>
+        <v>WYD</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/bother-me-feat-victony/1889266488</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Bother Me (feat. Victony) - Single</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>3:00</v>
+        <v>2:36</v>
       </c>
       <c r="H98" t="str">
-        <v>Osé</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/os%C3%A9/1494379253</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/bother-me-feat-victony/1889266486</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L98" t="str">
-        <v>Bother Me (feat. Victony) - Osé</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Fright</v>
+        <v>Dig Your Own Grave</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/fright/1890396431</v>
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Fright - Single</v>
+        <v>Strike and Kill</v>
       </c>
       <c r="G99" t="str">
-        <v>2:25</v>
+        <v>4:29</v>
       </c>
       <c r="H99" t="str">
-        <v>Creepy Nuts</v>
+        <v>DevilDriver</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/creepy-nuts/678140651</v>
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/fright/1890396429</v>
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
       </c>
       <c r="L99" t="str">
-        <v>Fright - Creepy Nuts</v>
+        <v>Dig Your Own Grave - DevilDriver</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Smoking In Bed</v>
+        <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/smoking-in-bed/1888340669</v>
+        <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-16</v>
+        <v>2026-04-17</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Smoking In Bed - Single</v>
+        <v>The Dead Ones</v>
       </c>
       <c r="G100" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H100" t="str">
-        <v>The Bends</v>
+        <v>The Last Ten Seconds of Life</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/the-bends/1781943253</v>
+        <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/smoking-in-bed/1888340666</v>
+        <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
       <c r="L100" t="str">
-        <v>Smoking In Bed - The Bends</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>The Dissonant Void</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/the-dissonant-void/1873364812</v>
-      </c>
-      <c r="D101" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>The Ghost of a Future Dead</v>
-      </c>
-      <c r="G101" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H101" t="str">
-        <v>At The Gates</v>
-      </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
-      </c>
-      <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/the-dissonant-void/1873364809</v>
-      </c>
-      <c r="L101" t="str">
-        <v>The Dissonant Void - At The Gates</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Nine Days Of Rain</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/nine-days-of-rain/1866957694</v>
-      </c>
-      <c r="D102" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>Savage Imperial Death March</v>
-      </c>
-      <c r="G102" t="str">
-        <v>3:51</v>
-      </c>
-      <c r="H102" t="str">
-        <v>Melvins</v>
-      </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/melvins/737433</v>
-      </c>
-      <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/nine-days-of-rain/1866957685</v>
-      </c>
-      <c r="L102" t="str">
-        <v>Nine Days Of Rain - Melvins</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Invocation of the Dreamer</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/invocation-of-the-dreamer/1885856105</v>
-      </c>
-      <c r="D103" t="str">
-        <v>2026-04-16</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="G103" t="str">
-        <v>4:46</v>
-      </c>
-      <c r="H103" t="str">
-        <v>Khemmis</v>
-      </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/khemmis/1004631193</v>
-      </c>
-      <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/invocation-of-the-dreamer/1885856096</v>
-      </c>
-      <c r="L103" t="str">
-        <v>Invocation of the Dreamer - Khemmis</v>
+        <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -1635,19 +1635,19 @@
         <v>2:37</v>
       </c>
       <c r="H33" t="str">
-        <v>Adela</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/adela/1423152831</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K33" t="str">
         <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L33" t="str">
-        <v>KGB - Adela</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="34">
@@ -2564,13 +2564,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Track 3</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/track-3/1889992071</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-17</v>
@@ -2594,10 +2594,10 @@
         <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/track-3/1889992065</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L58" t="str">
-        <v>Track 3 - rjtheweirdo</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="59">

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1576,13 +1576,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-17</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H32" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L32" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-17</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G33" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H33" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L33" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-17</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H34" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L34" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-17</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G35" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H35" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L35" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-17</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G36" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H36" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L36" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-17</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H37" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L37" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-17</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G38" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H38" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L38" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-17</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H39" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L39" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-17</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H40" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L40" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-17</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G41" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H41" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L41" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-17</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G42" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H42" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L42" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-17</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G43" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H43" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L43" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-17</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G44" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H44" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L44" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-17</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G45" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H45" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L45" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-17</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H46" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L46" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-17</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G47" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H47" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L47" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-17</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G48" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H48" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L48" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-17</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L49" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-17</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H50" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L50" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-17</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G51" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H51" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L51" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-17</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G52" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H52" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L52" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-17</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G53" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H53" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L53" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-17</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G54" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H54" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L54" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-17</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G55" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H55" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L55" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-17</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G56" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H56" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L56" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-17</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G57" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H57" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L57" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-17</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H58" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L58" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-17</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G59" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H59" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L59" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-17</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H60" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L60" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-17</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H61" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L61" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-17</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H62" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L62" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-17</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G63" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H63" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L63" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-17</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H64" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L64" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-17</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H65" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L65" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-17</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G66" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H66" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L66" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-17</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G67" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H67" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L67" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-17</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H68" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L68" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-17</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G69" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H69" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L69" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-17</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H70" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L70" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-17</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H71" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L71" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-17</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G72" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H72" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L72" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-17</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H73" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L73" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-17</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G74" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H74" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L74" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-17</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G75" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H75" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L75" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-17</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H76" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L76" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-17</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H77" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L77" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-17</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H78" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L78" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-17</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H79" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L79" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-17</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G80" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H80" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L80" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-17</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H81" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L81" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-17</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G82" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H82" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L82" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-17</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G83" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H83" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L83" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-17</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H84" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L84" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-17</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H85" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L85" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-17</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G86" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H86" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L86" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-17</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G87" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H87" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L87" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-17</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H88" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L88" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-17</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G89" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H89" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L89" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-17</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H90" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L90" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-17</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H91" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L91" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-17</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G92" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H92" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L92" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-17</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H93" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L93" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-17</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H94" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L94" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-17</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G95" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H95" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L95" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-17</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H96" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L96" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-17</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H97" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L97" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-17</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H98" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L98" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-17</v>
@@ -4137,68 +4137,106 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H99" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L99" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B100" t="str">
+        <v/>
+      </c>
+      <c r="C100" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D100" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G100" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H100" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I100" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J100" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K100" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L100" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D100" t="str">
-        <v>2026-04-17</v>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
+      <c r="D101" t="str">
+        <v>2026-04-17</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G101" t="str">
         <v>3:32</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H101" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I100" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J100" t="str">
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K100" t="str">
+      <c r="K101" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L100" t="str">
+      <c r="L101" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-17</v>
+        <v>2026-04-18</v>
       </c>
       <c r="E101" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -474,13 +474,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>First Light</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-18</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>First Light - Single</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G3" t="str">
-        <v>3:24</v>
+        <v>5:03</v>
       </c>
       <c r="H3" t="str">
-        <v>Lana Del Rey</v>
+        <v>Madonna</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L3" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Focu 'Ranni</v>
+        <v>First Light</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-18</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G4" t="str">
-        <v>2:50</v>
+        <v>3:24</v>
       </c>
       <c r="H4" t="str">
-        <v>ROSALÍA</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L4" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-18</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>Middle of Nowhere</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G5" t="str">
-        <v>2:36</v>
+        <v>2:50</v>
       </c>
       <c r="H5" t="str">
-        <v>Kacey Musgraves</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L5" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Rackies</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-18</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G6" t="str">
-        <v>2:53</v>
+        <v>2:36</v>
       </c>
       <c r="H6" t="str">
-        <v>Sexyy Red</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L6" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>Rackies</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-18</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G7" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H7" t="str">
-        <v>Tyla</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L7" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Potential</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-18</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>Potential - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G8" t="str">
-        <v>4:02</v>
+        <v>3:33</v>
       </c>
       <c r="H8" t="str">
-        <v>sombr</v>
+        <v>Tyla</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L8" t="str">
-        <v>Potential - sombr</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Pa' la seca</v>
+        <v>Potential</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-18</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>3:04</v>
+        <v>4:02</v>
       </c>
       <c r="H9" t="str">
-        <v>Maluma</v>
+        <v>sombr</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L9" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-18</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>The Nightlife</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H10" t="str">
-        <v>Honey Dijon</v>
+        <v>Maluma</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L10" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>BIAF &lt;3</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-18</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G11" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H11" t="str">
-        <v>Young Miko</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L11" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-18</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G12" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H12" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L12" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>i just get worse</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-18</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>i just get worse - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G13" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H13" t="str">
-        <v>Kevian Kraemer</v>
+        <v>DANNA</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L13" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>i just get worse</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-18</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H14" t="str">
-        <v>John Summit</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L14" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Side Effects</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-18</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>KONNAKOL</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G15" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H15" t="str">
-        <v>ZAYN</v>
+        <v>John Summit</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L15" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Numb</v>
+        <v>Side Effects</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-18</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>Numb - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G16" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H16" t="str">
-        <v>JT</v>
+        <v>ZAYN</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L16" t="str">
-        <v>Numb - JT</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Numb</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-18</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G17" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H17" t="str">
-        <v>Labrinth</v>
+        <v>JT</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L17" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-18</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H18" t="str">
-        <v>Miley Cyrus</v>
+        <v>Labrinth</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L18" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>My Way</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-18</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>My Way - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>4:02</v>
+        <v>2:47</v>
       </c>
       <c r="H19" t="str">
-        <v>Riley Green</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L19" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ache</v>
+        <v>My Way</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-18</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Bloom - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H20" t="str">
-        <v>Not for Radio</v>
+        <v>Riley Green</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L20" t="str">
-        <v>Ache - Not for Radio</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Cut Ties</v>
+        <v>Ache</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-18</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>4:09</v>
+        <v>4:25</v>
       </c>
       <c r="H21" t="str">
-        <v>Anne Hathaway</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L21" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-18</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G22" t="str">
-        <v>2:13</v>
+        <v>4:09</v>
       </c>
       <c r="H22" t="str">
-        <v>Slayyyter</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L22" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-18</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Nine Inch Noize</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>3:57</v>
+        <v>2:13</v>
       </c>
       <c r="H23" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L23" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Boots on the Ground</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-18</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G24" t="str">
-        <v>4:21</v>
+        <v>3:57</v>
       </c>
       <c r="H24" t="str">
-        <v>Massive Attack</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L24" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-18</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H25" t="str">
-        <v>Demi Lovato</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L25" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>I CONDEMN</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-18</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H26" t="str">
-        <v>The Kid LAROI</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L26" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Wannabeher</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-18</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Dancing On The Wall</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H27" t="str">
-        <v>MUNA</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L27" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Superbloom</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-18</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Superbloom</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G28" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H28" t="str">
-        <v>Jessie Ware</v>
+        <v>MUNA</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L28" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Chairwoman Park</v>
+        <v>Superbloom</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-18</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G29" t="str">
-        <v>1:40</v>
+        <v>4:11</v>
       </c>
       <c r="H29" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L29" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Make You Move</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-18</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Make You Move - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G30" t="str">
-        <v>2:24</v>
+        <v>1:40</v>
       </c>
       <c r="H30" t="str">
-        <v>Dillon Francis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L30" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>FERRARI</v>
+        <v>Make You Move</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-18</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>FERRARI - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G31" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H31" t="str">
-        <v>Clave Especial</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L31" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Por Ella</v>
+        <v>FERRARI</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-18</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H32" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L32" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-18</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H33" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L33" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-18</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G34" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H34" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L34" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-18</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H35" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L35" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-18</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G36" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H36" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L36" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-18</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G37" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H37" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L37" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-18</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G38" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H38" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L38" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-18</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G39" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H39" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L39" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-18</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H40" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L40" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-18</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H41" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L41" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-18</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G42" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H42" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L42" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-18</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G43" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H43" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L43" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-18</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G44" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H44" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L44" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-18</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G45" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H45" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L45" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-18</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G46" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H46" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L46" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-18</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H47" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L47" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-18</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G48" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H48" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L48" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-18</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G49" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H49" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L49" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-18</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G50" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H50" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L50" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-18</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H51" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L51" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-18</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G52" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H52" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L52" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-18</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G53" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L53" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-18</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G54" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H54" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L54" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-18</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G55" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H55" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L55" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-18</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G56" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H56" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L56" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-18</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G57" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H57" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L57" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-18</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G58" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H58" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L58" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-18</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H59" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L59" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-18</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G60" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H60" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L60" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-18</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H61" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L61" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-18</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H62" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L62" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-18</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H63" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L63" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-18</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G64" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H64" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L64" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-18</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H65" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L65" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-18</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H66" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L66" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-18</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G67" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H67" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L67" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-18</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G68" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H68" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L68" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-18</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G69" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H69" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L69" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-18</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G70" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H70" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L70" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-18</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H71" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L71" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-18</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H72" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L72" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-18</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G73" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H73" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L73" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-18</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H74" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L74" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-18</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G75" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H75" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L75" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-18</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G76" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H76" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L76" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-18</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G77" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H77" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L77" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-18</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H78" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L78" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-18</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H79" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L79" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-18</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H80" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L80" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-18</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G81" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H81" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L81" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-18</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H82" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L82" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-18</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G83" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H83" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L83" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-18</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G84" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H84" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L84" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-18</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G85" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H85" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L85" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-18</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H86" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L86" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-18</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G87" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H87" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L87" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-18</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G88" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H88" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L88" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-18</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G89" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H89" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L89" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-18</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G90" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H90" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L90" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-18</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H91" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L91" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-18</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H92" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L92" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-18</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G93" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H93" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L93" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-18</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H94" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L94" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-18</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H95" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L95" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-18</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G96" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H96" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L96" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-18</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H97" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L97" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-18</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H98" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L98" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-18</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H99" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L99" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-18</v>
@@ -4175,68 +4175,106 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H100" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L100" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B101" t="str">
+        <v/>
+      </c>
+      <c r="C101" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D101" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G101" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H101" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I101" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J101" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K101" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L101" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D101" t="str">
-        <v>2026-04-18</v>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
+      <c r="D102" t="str">
+        <v>2026-04-18</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G102" t="str">
         <v>3:32</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H102" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I101" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J101" t="str">
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K101" t="str">
+      <c r="K102" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L101" t="str">
+      <c r="L102" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-18</v>
+        <v>2026-04-19</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-20</v>
       </c>
       <c r="E102" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>drop dead</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-20</v>
@@ -451,36 +451,36 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>you seem pretty sad for a girl so in love</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G2" t="str">
-        <v>3:44</v>
+        <v>4:32</v>
       </c>
       <c r="H2" t="str">
-        <v>Olivia Rodrigo</v>
+        <v>Beck</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L2" t="str">
-        <v>drop dead - Olivia Rodrigo</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>I Feel So Free</v>
+        <v>drop dead</v>
       </c>
       <c r="B3" t="str">
         <v/>
       </c>
       <c r="C3" t="str">
-        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
+        <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-20</v>
@@ -489,36 +489,36 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>CONFESSIONS II</v>
+        <v>you seem pretty sad for a girl so in love</v>
       </c>
       <c r="G3" t="str">
-        <v>5:03</v>
+        <v>3:44</v>
       </c>
       <c r="H3" t="str">
-        <v>Madonna</v>
+        <v>Olivia Rodrigo</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
-        <v>https://music.apple.com/us/artist/madonna/20044</v>
+        <v>https://music.apple.com/us/artist/olivia-rodrigo/979458609</v>
       </c>
       <c r="K3" t="str">
-        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
+        <v>https://music.apple.com/us/album/drop-dead/1889992111</v>
       </c>
       <c r="L3" t="str">
-        <v>I Feel So Free - Madonna</v>
+        <v>drop dead - Olivia Rodrigo</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>First Light</v>
+        <v>I Feel So Free</v>
       </c>
       <c r="B4" t="str">
         <v/>
       </c>
       <c r="C4" t="str">
-        <v>https://music.apple.com/us/song/first-light/1893438278</v>
+        <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-20</v>
@@ -527,36 +527,36 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>First Light - Single</v>
+        <v>CONFESSIONS II</v>
       </c>
       <c r="G4" t="str">
-        <v>3:24</v>
+        <v>5:03</v>
       </c>
       <c r="H4" t="str">
-        <v>Lana Del Rey</v>
+        <v>Madonna</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/madonna/20044</v>
       </c>
       <c r="K4" t="str">
-        <v>https://music.apple.com/us/album/first-light/1893438114</v>
+        <v>https://music.apple.com/us/album/i-feel-so-free/1892545087</v>
       </c>
       <c r="L4" t="str">
-        <v>First Light - Lana Del Rey</v>
+        <v>I Feel So Free - Madonna</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Focu 'Ranni</v>
+        <v>First Light</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
+        <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-20</v>
@@ -565,36 +565,36 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>LUX (Complete Works)</v>
+        <v>First Light - Single</v>
       </c>
       <c r="G5" t="str">
-        <v>2:50</v>
+        <v>3:24</v>
       </c>
       <c r="H5" t="str">
-        <v>ROSALÍA</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
-        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K5" t="str">
-        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
+        <v>https://music.apple.com/us/album/first-light/1893438114</v>
       </c>
       <c r="L5" t="str">
-        <v>Focu 'Ranni - ROSALÍA</v>
+        <v>First Light - Lana Del Rey</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Middle of Nowhere</v>
+        <v>Focu 'Ranni</v>
       </c>
       <c r="B6" t="str">
         <v/>
       </c>
       <c r="C6" t="str">
-        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
+        <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-20</v>
@@ -603,36 +603,36 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>Middle of Nowhere</v>
+        <v>LUX (Complete Works)</v>
       </c>
       <c r="G6" t="str">
-        <v>2:36</v>
+        <v>2:50</v>
       </c>
       <c r="H6" t="str">
-        <v>Kacey Musgraves</v>
+        <v>ROSALÍA</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
-        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
+        <v>https://music.apple.com/us/artist/rosal%C3%ADa/313845115</v>
       </c>
       <c r="K6" t="str">
-        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
+        <v>https://music.apple.com/us/album/focu-ranni/1893474283</v>
       </c>
       <c r="L6" t="str">
-        <v>Middle of Nowhere - Kacey Musgraves</v>
+        <v>Focu 'Ranni - ROSALÍA</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Rackies</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="B7" t="str">
         <v/>
       </c>
       <c r="C7" t="str">
-        <v>https://music.apple.com/us/song/rackies/1893499659</v>
+        <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-20</v>
@@ -641,36 +641,36 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>Yo Favorite Trappa Favorite Rappa</v>
+        <v>Middle of Nowhere</v>
       </c>
       <c r="G7" t="str">
-        <v>2:53</v>
+        <v>2:36</v>
       </c>
       <c r="H7" t="str">
-        <v>Sexyy Red</v>
+        <v>Kacey Musgraves</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
-        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
+        <v>https://music.apple.com/us/artist/kacey-musgraves/466044182</v>
       </c>
       <c r="K7" t="str">
-        <v>https://music.apple.com/us/album/rackies/1893499525</v>
+        <v>https://music.apple.com/us/album/middle-of-nowhere/1883176984</v>
       </c>
       <c r="L7" t="str">
-        <v>Rackies - Sexyy Red</v>
+        <v>Middle of Nowhere - Kacey Musgraves</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
+        <v>Rackies</v>
       </c>
       <c r="B8" t="str">
         <v/>
       </c>
       <c r="C8" t="str">
-        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
+        <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-20</v>
@@ -679,36 +679,36 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
+        <v>Yo Favorite Trappa Favorite Rappa</v>
       </c>
       <c r="G8" t="str">
-        <v>3:33</v>
+        <v>2:53</v>
       </c>
       <c r="H8" t="str">
-        <v>Tyla</v>
+        <v>Sexyy Red</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
-        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
+        <v>https://music.apple.com/us/artist/sexyy-red/1409330762</v>
       </c>
       <c r="K8" t="str">
-        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
+        <v>https://music.apple.com/us/album/rackies/1893499525</v>
       </c>
       <c r="L8" t="str">
-        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
+        <v>Rackies - Sexyy Red</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Potential</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson)</v>
       </c>
       <c r="B9" t="str">
         <v/>
       </c>
       <c r="C9" t="str">
-        <v>https://music.apple.com/us/song/potential/1892512227</v>
+        <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-20</v>
@@ -717,36 +717,36 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>Potential - Single</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Single</v>
       </c>
       <c r="G9" t="str">
-        <v>4:02</v>
+        <v>3:33</v>
       </c>
       <c r="H9" t="str">
-        <v>sombr</v>
+        <v>Tyla</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
-        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
+        <v>https://music.apple.com/us/artist/tyla/1552925732</v>
       </c>
       <c r="K9" t="str">
-        <v>https://music.apple.com/us/album/potential/1892512217</v>
+        <v>https://music.apple.com/us/album/she-did-it-again-feat-zara-larsson/1893706104</v>
       </c>
       <c r="L9" t="str">
-        <v>Potential - sombr</v>
+        <v>SHE DID IT AGAIN (feat. Zara Larsson) - Tyla</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Pa' la seca</v>
+        <v>Potential</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
+        <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-20</v>
@@ -755,36 +755,36 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>Pa' la seca - Single</v>
+        <v>Potential - Single</v>
       </c>
       <c r="G10" t="str">
-        <v>3:04</v>
+        <v>4:02</v>
       </c>
       <c r="H10" t="str">
-        <v>Maluma</v>
+        <v>sombr</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
-        <v>https://music.apple.com/us/artist/maluma/448916501</v>
+        <v>https://music.apple.com/us/artist/sombr/1589842503</v>
       </c>
       <c r="K10" t="str">
-        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
+        <v>https://music.apple.com/us/album/potential/1892512217</v>
       </c>
       <c r="L10" t="str">
-        <v>Pa' la seca - Maluma</v>
+        <v>Potential - sombr</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan)</v>
+        <v>Pa' la seca</v>
       </c>
       <c r="B11" t="str">
         <v/>
       </c>
       <c r="C11" t="str">
-        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
+        <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-20</v>
@@ -793,36 +793,36 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>The Nightlife</v>
+        <v>Pa' la seca - Single</v>
       </c>
       <c r="G11" t="str">
-        <v>3:32</v>
+        <v>3:04</v>
       </c>
       <c r="H11" t="str">
-        <v>Honey Dijon</v>
+        <v>Maluma</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
-        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
+        <v>https://music.apple.com/us/artist/maluma/448916501</v>
       </c>
       <c r="K11" t="str">
-        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
+        <v>https://music.apple.com/us/album/pa-la-seca/1891872224</v>
       </c>
       <c r="L11" t="str">
-        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
+        <v>Pa' la seca - Maluma</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>BIAF &lt;3</v>
+        <v>New Wave Groove (feat. Rochelle Jordan)</v>
       </c>
       <c r="B12" t="str">
         <v/>
       </c>
       <c r="C12" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-20</v>
@@ -831,36 +831,36 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>The Nightlife</v>
       </c>
       <c r="G12" t="str">
-        <v>2:50</v>
+        <v>3:32</v>
       </c>
       <c r="H12" t="str">
-        <v>Young Miko</v>
+        <v>Honey Dijon</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/honey-dijon/355901599</v>
       </c>
       <c r="K12" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/new-wave-groove-feat-rochelle-jordan/1878415566</v>
       </c>
       <c r="L12" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>New Wave Groove (feat. Rochelle Jordan) - Honey Dijon</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-20</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H13" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L13" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>i just get worse</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-20</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>i just get worse - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G14" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H14" t="str">
-        <v>Kevian Kraemer</v>
+        <v>DANNA</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L14" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>i just get worse</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-20</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G15" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H15" t="str">
-        <v>John Summit</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L15" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Side Effects</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-20</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>KONNAKOL</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G16" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H16" t="str">
-        <v>ZAYN</v>
+        <v>John Summit</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L16" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Numb</v>
+        <v>Side Effects</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-20</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>Numb - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G17" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H17" t="str">
-        <v>JT</v>
+        <v>ZAYN</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L17" t="str">
-        <v>Numb - JT</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Numb</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-20</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G18" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H18" t="str">
-        <v>Labrinth</v>
+        <v>JT</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L18" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-20</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H19" t="str">
-        <v>Miley Cyrus</v>
+        <v>Labrinth</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L19" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>My Way</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-20</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>My Way - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>4:02</v>
+        <v>2:47</v>
       </c>
       <c r="H20" t="str">
-        <v>Riley Green</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L20" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Ache</v>
+        <v>My Way</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-20</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>Bloom - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H21" t="str">
-        <v>Not for Radio</v>
+        <v>Riley Green</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L21" t="str">
-        <v>Ache - Not for Radio</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Cut Ties</v>
+        <v>Ache</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-20</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>4:09</v>
+        <v>4:25</v>
       </c>
       <c r="H22" t="str">
-        <v>Anne Hathaway</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L22" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-20</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G23" t="str">
-        <v>2:13</v>
+        <v>4:09</v>
       </c>
       <c r="H23" t="str">
-        <v>Slayyyter</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L23" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-20</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>Nine Inch Noize</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G24" t="str">
-        <v>3:57</v>
+        <v>2:13</v>
       </c>
       <c r="H24" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L24" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Boots on the Ground</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-20</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G25" t="str">
-        <v>4:21</v>
+        <v>3:57</v>
       </c>
       <c r="H25" t="str">
-        <v>Massive Attack</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L25" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-20</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G26" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H26" t="str">
-        <v>Demi Lovato</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L26" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>I CONDEMN</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-20</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H27" t="str">
-        <v>The Kid LAROI</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L27" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Wannabeher</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-20</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>Dancing On The Wall</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H28" t="str">
-        <v>MUNA</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L28" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Superbloom</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-20</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Superbloom</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G29" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H29" t="str">
-        <v>Jessie Ware</v>
+        <v>MUNA</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L29" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Chairwoman Park</v>
+        <v>Superbloom</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-20</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G30" t="str">
-        <v>1:40</v>
+        <v>4:11</v>
       </c>
       <c r="H30" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L30" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Make You Move</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-20</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>Make You Move - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G31" t="str">
-        <v>2:24</v>
+        <v>1:40</v>
       </c>
       <c r="H31" t="str">
-        <v>Dillon Francis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L31" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>FERRARI</v>
+        <v>Make You Move</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-20</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>FERRARI - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G32" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H32" t="str">
-        <v>Clave Especial</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L32" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Por Ella</v>
+        <v>FERRARI</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-20</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H33" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L33" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-20</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H34" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L34" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-20</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G35" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H35" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L35" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-20</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G36" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H36" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L36" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-20</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G37" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H37" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L37" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-20</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G38" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H38" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L38" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-20</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G39" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H39" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L39" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-20</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G40" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H40" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L40" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-20</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G41" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H41" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L41" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-20</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H42" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L42" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-20</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G43" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H43" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L43" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-20</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G44" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H44" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L44" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-20</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G45" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H45" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L45" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-20</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G46" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H46" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L46" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-20</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G47" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H47" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L47" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-20</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G48" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H48" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L48" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-20</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G49" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H49" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L49" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-20</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G50" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H50" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L50" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-20</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G51" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H51" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L51" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-20</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H52" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L52" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-20</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H53" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L53" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-20</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G54" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L54" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-20</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G55" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H55" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L55" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-20</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G56" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H56" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L56" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-20</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G57" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H57" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L57" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-20</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G58" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H58" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L58" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-20</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G59" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H59" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L59" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-20</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G60" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H60" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L60" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-20</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G61" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H61" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L61" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-20</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G62" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H62" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L62" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-20</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H63" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L63" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-20</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H64" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L64" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-20</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G65" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H65" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L65" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-20</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G66" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H66" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L66" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-20</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H67" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L67" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-20</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G68" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H68" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L68" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-20</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G69" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H69" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L69" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-20</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G70" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L70" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-20</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G71" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H71" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L71" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-20</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G72" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H72" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L72" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-20</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H73" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L73" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-20</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G74" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H74" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L74" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-20</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G75" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H75" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L75" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-20</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G76" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H76" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L76" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-20</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G77" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H77" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L77" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-20</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G78" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H78" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L78" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-20</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H79" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L79" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-20</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H80" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L80" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-20</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H81" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L81" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-20</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G82" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H82" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L82" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-20</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G83" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H83" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L83" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-20</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G84" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H84" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L84" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-20</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G85" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H85" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L85" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-20</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G86" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H86" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L86" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-20</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H87" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L87" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-20</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G88" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H88" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L88" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-20</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G89" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H89" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L89" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-20</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G90" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H90" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L90" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-20</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G91" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H91" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L91" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-20</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G92" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H92" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L92" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-20</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H93" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L93" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-20</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G94" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H94" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L94" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-20</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G95" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H95" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L95" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-20</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H96" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L96" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-20</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G97" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H97" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L97" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-20</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G98" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H98" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L98" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-20</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H99" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L99" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-20</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H100" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L100" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-20</v>
@@ -4213,68 +4213,106 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H101" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L101" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B102" t="str">
+        <v/>
+      </c>
+      <c r="C102" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D102" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G102" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H102" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I102" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J102" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K102" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D102" t="str">
-        <v>2026-04-20</v>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
+      <c r="D103" t="str">
+        <v>2026-04-20</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G103" t="str">
         <v>3:32</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H103" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I102" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J102" t="str">
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K102" t="str">
+      <c r="K103" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L102" t="str">
+      <c r="L103" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -445,7 +445,7 @@
         <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -483,7 +483,7 @@
         <v>https://music.apple.com/us/song/drop-dead/1889992113</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -521,7 +521,7 @@
         <v>https://music.apple.com/us/song/i-feel-so-free/1892545101</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -559,7 +559,7 @@
         <v>https://music.apple.com/us/song/first-light/1893438278</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>https://music.apple.com/us/song/focu-ranni/6762232889</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -635,7 +635,7 @@
         <v>https://music.apple.com/us/song/middle-of-nowhere/1883177257</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -673,7 +673,7 @@
         <v>https://music.apple.com/us/song/rackies/1893499659</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -711,7 +711,7 @@
         <v>https://music.apple.com/us/song/she-did-it-again-feat-zara-larsson/1893706107</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -749,7 +749,7 @@
         <v>https://music.apple.com/us/song/potential/1892512227</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -787,7 +787,7 @@
         <v>https://music.apple.com/us/song/pa-la-seca/1891872226</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -825,7 +825,7 @@
         <v>https://music.apple.com/us/song/new-wave-groove-feat-rochelle-jordan/1878416325</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -901,7 +901,7 @@
         <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -939,7 +939,7 @@
         <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -977,7 +977,7 @@
         <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1015,7 +1015,7 @@
         <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1053,7 +1053,7 @@
         <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1091,7 +1091,7 @@
         <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1129,7 +1129,7 @@
         <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1205,7 +1205,7 @@
         <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1243,7 +1243,7 @@
         <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1281,7 +1281,7 @@
         <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1319,7 +1319,7 @@
         <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1357,7 +1357,7 @@
         <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1395,7 +1395,7 @@
         <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1433,7 +1433,7 @@
         <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1471,7 +1471,7 @@
         <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1509,7 +1509,7 @@
         <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1547,7 +1547,7 @@
         <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1585,7 +1585,7 @@
         <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1623,7 +1623,7 @@
         <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1661,7 +1661,7 @@
         <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1699,7 +1699,7 @@
         <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1737,7 +1737,7 @@
         <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1775,7 +1775,7 @@
         <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1813,7 +1813,7 @@
         <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1851,7 +1851,7 @@
         <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1889,7 +1889,7 @@
         <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1965,7 +1965,7 @@
         <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -2003,7 +2003,7 @@
         <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -2041,7 +2041,7 @@
         <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -2079,7 +2079,7 @@
         <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -2117,7 +2117,7 @@
         <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -2155,7 +2155,7 @@
         <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2193,7 +2193,7 @@
         <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2231,7 +2231,7 @@
         <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2269,7 +2269,7 @@
         <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2307,7 +2307,7 @@
         <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2345,7 +2345,7 @@
         <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2383,7 +2383,7 @@
         <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2421,7 +2421,7 @@
         <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2459,7 +2459,7 @@
         <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2497,7 +2497,7 @@
         <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2535,7 +2535,7 @@
         <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2573,7 +2573,7 @@
         <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2611,7 +2611,7 @@
         <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2649,7 +2649,7 @@
         <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2687,7 +2687,7 @@
         <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2725,7 +2725,7 @@
         <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2763,7 +2763,7 @@
         <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2801,7 +2801,7 @@
         <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2839,7 +2839,7 @@
         <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2877,7 +2877,7 @@
         <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2915,7 +2915,7 @@
         <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2953,7 +2953,7 @@
         <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2991,7 +2991,7 @@
         <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -3029,7 +3029,7 @@
         <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3067,7 +3067,7 @@
         <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3105,7 +3105,7 @@
         <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -3143,7 +3143,7 @@
         <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -3181,7 +3181,7 @@
         <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -3219,7 +3219,7 @@
         <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3295,7 +3295,7 @@
         <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3333,7 +3333,7 @@
         <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3371,7 +3371,7 @@
         <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3409,7 +3409,7 @@
         <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3447,7 +3447,7 @@
         <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3485,7 +3485,7 @@
         <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3523,7 +3523,7 @@
         <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3561,7 +3561,7 @@
         <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3599,7 +3599,7 @@
         <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3637,7 +3637,7 @@
         <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3675,7 +3675,7 @@
         <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3713,7 +3713,7 @@
         <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3751,7 +3751,7 @@
         <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3789,7 +3789,7 @@
         <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3827,7 +3827,7 @@
         <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3865,7 +3865,7 @@
         <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3903,7 +3903,7 @@
         <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -3941,7 +3941,7 @@
         <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -3979,7 +3979,7 @@
         <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -4017,7 +4017,7 @@
         <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -4055,7 +4055,7 @@
         <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -4093,7 +4093,7 @@
         <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -4131,7 +4131,7 @@
         <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E99" t="str">
         <v/>
@@ -4169,7 +4169,7 @@
         <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -4207,7 +4207,7 @@
         <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -4245,7 +4245,7 @@
         <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E102" t="str">
         <v/>
@@ -4283,7 +4283,7 @@
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-04-20</v>
+        <v>2026-04-21</v>
       </c>
       <c r="E103" t="str">
         <v/>

--- a/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
+++ b/data/tags/מוזיקה לועזית חדשה/sites/apple-music-playlist/2026-04-week03/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ride Lonesome</v>
+        <v>Better</v>
       </c>
       <c r="B2" t="str">
         <v/>
       </c>
       <c r="C2" t="str">
-        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
+        <v>https://music.apple.com/us/song/better/1885858065</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-21</v>
@@ -451,25 +451,25 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Ride Lonesome - Single</v>
+        <v>U</v>
       </c>
       <c r="G2" t="str">
-        <v>4:32</v>
+        <v>3:50</v>
       </c>
       <c r="H2" t="str">
-        <v>Beck</v>
+        <v>Baauer</v>
       </c>
       <c r="I2" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
-        <v>https://music.apple.com/us/artist/beck/312095</v>
+        <v>https://music.apple.com/us/artist/baauer/526199085</v>
       </c>
       <c r="K2" t="str">
-        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
+        <v>https://music.apple.com/us/album/better/1885857722</v>
       </c>
       <c r="L2" t="str">
-        <v>Ride Lonesome - Beck</v>
+        <v>Better - Baauer</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>BIAF &lt;3</v>
+        <v>Ride Lonesome</v>
       </c>
       <c r="B13" t="str">
         <v/>
       </c>
       <c r="C13" t="str">
-        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
+        <v>https://music.apple.com/us/song/ride-lonesome/1893159447</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-21</v>
@@ -869,36 +869,36 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>BIAF &lt;3 - Single</v>
+        <v>Ride Lonesome - Single</v>
       </c>
       <c r="G13" t="str">
-        <v>2:50</v>
+        <v>4:32</v>
       </c>
       <c r="H13" t="str">
-        <v>Young Miko</v>
+        <v>Beck</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J13" t="str">
-        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
+        <v>https://music.apple.com/us/artist/beck/312095</v>
       </c>
       <c r="K13" t="str">
-        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
+        <v>https://music.apple.com/us/album/ride-lonesome/1893159445</v>
       </c>
       <c r="L13" t="str">
-        <v>BIAF &lt;3 - Young Miko</v>
+        <v>Ride Lonesome - Beck</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>YOU COULD BE THAT BOY</v>
+        <v>BIAF &lt;3</v>
       </c>
       <c r="B14" t="str">
         <v/>
       </c>
       <c r="C14" t="str">
-        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
+        <v>https://music.apple.com/us/song/biaf-3/1889968627</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-21</v>
@@ -907,36 +907,36 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>LUCID DREAMS - EP</v>
+        <v>BIAF &lt;3 - Single</v>
       </c>
       <c r="G14" t="str">
-        <v>3:14</v>
+        <v>2:50</v>
       </c>
       <c r="H14" t="str">
-        <v>DANNA</v>
+        <v>Young Miko</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J14" t="str">
-        <v>https://music.apple.com/us/artist/danna/1891412909</v>
+        <v>https://music.apple.com/us/artist/young-miko/1576521417</v>
       </c>
       <c r="K14" t="str">
-        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
+        <v>https://music.apple.com/us/album/biaf-3/1889968626</v>
       </c>
       <c r="L14" t="str">
-        <v>YOU COULD BE THAT BOY - DANNA</v>
+        <v>BIAF &lt;3 - Young Miko</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>i just get worse</v>
+        <v>YOU COULD BE THAT BOY</v>
       </c>
       <c r="B15" t="str">
         <v/>
       </c>
       <c r="C15" t="str">
-        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
+        <v>https://music.apple.com/us/song/you-could-be-that-boy/1889943415</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-21</v>
@@ -945,36 +945,36 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>i just get worse - Single</v>
+        <v>LUCID DREAMS - EP</v>
       </c>
       <c r="G15" t="str">
-        <v>3:25</v>
+        <v>3:14</v>
       </c>
       <c r="H15" t="str">
-        <v>Kevian Kraemer</v>
+        <v>DANNA</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J15" t="str">
-        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
+        <v>https://music.apple.com/us/artist/danna/1891412909</v>
       </c>
       <c r="K15" t="str">
-        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
+        <v>https://music.apple.com/us/album/you-could-be-that-boy/1889943408</v>
       </c>
       <c r="L15" t="str">
-        <v>i just get worse - Kevian Kraemer</v>
+        <v>YOU COULD BE THAT BOY - DANNA</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SHADES OF BLUE</v>
+        <v>i just get worse</v>
       </c>
       <c r="B16" t="str">
         <v/>
       </c>
       <c r="C16" t="str">
-        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
+        <v>https://music.apple.com/us/song/i-just-get-worse/1892487409</v>
       </c>
       <c r="D16" t="str">
         <v>2026-04-21</v>
@@ -983,36 +983,36 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>CTRL ESCAPE</v>
+        <v>i just get worse - Single</v>
       </c>
       <c r="G16" t="str">
-        <v>3:23</v>
+        <v>3:25</v>
       </c>
       <c r="H16" t="str">
-        <v>John Summit</v>
+        <v>Kevian Kraemer</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J16" t="str">
-        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
+        <v>https://music.apple.com/us/artist/kevian-kraemer/1594747842</v>
       </c>
       <c r="K16" t="str">
-        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
+        <v>https://music.apple.com/us/album/i-just-get-worse/1892487408</v>
       </c>
       <c r="L16" t="str">
-        <v>SHADES OF BLUE - John Summit</v>
+        <v>i just get worse - Kevian Kraemer</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Side Effects</v>
+        <v>SHADES OF BLUE</v>
       </c>
       <c r="B17" t="str">
         <v/>
       </c>
       <c r="C17" t="str">
-        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
+        <v>https://music.apple.com/us/song/shades-of-blue/1874015488</v>
       </c>
       <c r="D17" t="str">
         <v>2026-04-21</v>
@@ -1021,36 +1021,36 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>KONNAKOL</v>
+        <v>CTRL ESCAPE</v>
       </c>
       <c r="G17" t="str">
-        <v>3:17</v>
+        <v>3:23</v>
       </c>
       <c r="H17" t="str">
-        <v>ZAYN</v>
+        <v>John Summit</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J17" t="str">
-        <v>https://music.apple.com/us/artist/zayn/973181994</v>
+        <v>https://music.apple.com/us/artist/john-summit/1387587503</v>
       </c>
       <c r="K17" t="str">
-        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
+        <v>https://music.apple.com/us/album/shades-of-blue/1874015470</v>
       </c>
       <c r="L17" t="str">
-        <v>Side Effects - ZAYN</v>
+        <v>SHADES OF BLUE - John Summit</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Numb</v>
+        <v>Side Effects</v>
       </c>
       <c r="B18" t="str">
         <v/>
       </c>
       <c r="C18" t="str">
-        <v>https://music.apple.com/us/song/numb/1889655586</v>
+        <v>https://music.apple.com/us/song/side-effects/1872664200</v>
       </c>
       <c r="D18" t="str">
         <v>2026-04-21</v>
@@ -1059,36 +1059,36 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>Numb - Single</v>
+        <v>KONNAKOL</v>
       </c>
       <c r="G18" t="str">
-        <v>2:34</v>
+        <v>3:17</v>
       </c>
       <c r="H18" t="str">
-        <v>JT</v>
+        <v>ZAYN</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J18" t="str">
-        <v>https://music.apple.com/us/artist/jt/1590403119</v>
+        <v>https://music.apple.com/us/artist/zayn/973181994</v>
       </c>
       <c r="K18" t="str">
-        <v>https://music.apple.com/us/album/numb/1889655585</v>
+        <v>https://music.apple.com/us/album/side-effects/1872663947</v>
       </c>
       <c r="L18" t="str">
-        <v>Numb - JT</v>
+        <v>Side Effects - ZAYN</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SHUT YOUR DAMN 95.7892</v>
+        <v>Numb</v>
       </c>
       <c r="B19" t="str">
         <v/>
       </c>
       <c r="C19" t="str">
-        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
+        <v>https://music.apple.com/us/song/numb/1889655586</v>
       </c>
       <c r="D19" t="str">
         <v>2026-04-21</v>
@@ -1097,36 +1097,36 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Single</v>
+        <v>Numb - Single</v>
       </c>
       <c r="G19" t="str">
-        <v>3:05</v>
+        <v>2:34</v>
       </c>
       <c r="H19" t="str">
-        <v>Labrinth</v>
+        <v>JT</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J19" t="str">
-        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
+        <v>https://music.apple.com/us/artist/jt/1590403119</v>
       </c>
       <c r="K19" t="str">
-        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
+        <v>https://music.apple.com/us/album/numb/1889655585</v>
       </c>
       <c r="L19" t="str">
-        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
+        <v>Numb - JT</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
+        <v>SHUT YOUR DAMN 95.7892</v>
       </c>
       <c r="B20" t="str">
         <v/>
       </c>
       <c r="C20" t="str">
-        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
+        <v>https://music.apple.com/us/song/shut-your-damn-95-7892/1892735836</v>
       </c>
       <c r="D20" t="str">
         <v>2026-04-21</v>
@@ -1135,36 +1135,36 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
+        <v>SHUT YOUR DAMN 95.7892 - Single</v>
       </c>
       <c r="G20" t="str">
-        <v>2:47</v>
+        <v>3:05</v>
       </c>
       <c r="H20" t="str">
-        <v>Miley Cyrus</v>
+        <v>Labrinth</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J20" t="str">
-        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
+        <v>https://music.apple.com/us/artist/labrinth/205732582</v>
       </c>
       <c r="K20" t="str">
-        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
+        <v>https://music.apple.com/us/album/shut-your-damn-95-7892/1892735835</v>
       </c>
       <c r="L20" t="str">
-        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
+        <v>SHUT YOUR DAMN 95.7892 - Labrinth</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>My Way</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special")</v>
       </c>
       <c r="B21" t="str">
         <v/>
       </c>
       <c r="C21" t="str">
-        <v>https://music.apple.com/us/song/my-way/1892083308</v>
+        <v>https://music.apple.com/us/song/younger-you-from-the-hannah-montana-20th-anniversary/6762304737</v>
       </c>
       <c r="D21" t="str">
         <v>2026-04-21</v>
@@ -1173,36 +1173,36 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>My Way - Single</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Single</v>
       </c>
       <c r="G21" t="str">
-        <v>4:02</v>
+        <v>2:47</v>
       </c>
       <c r="H21" t="str">
-        <v>Riley Green</v>
+        <v>Miley Cyrus</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J21" t="str">
-        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
+        <v>https://music.apple.com/us/artist/miley-cyrus/137057909</v>
       </c>
       <c r="K21" t="str">
-        <v>https://music.apple.com/us/album/my-way/1892083036</v>
+        <v>https://music.apple.com/us/album/younger-you-from-the-hannah-montana-20th-anniversary/1893731618</v>
       </c>
       <c r="L21" t="str">
-        <v>My Way - Riley Green</v>
+        <v>Younger You (From the "Hannah Montana 20th Anniversary Special") - Miley Cyrus</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ache</v>
+        <v>My Way</v>
       </c>
       <c r="B22" t="str">
         <v/>
       </c>
       <c r="C22" t="str">
-        <v>https://music.apple.com/us/song/ache/1892180581</v>
+        <v>https://music.apple.com/us/song/my-way/1892083308</v>
       </c>
       <c r="D22" t="str">
         <v>2026-04-21</v>
@@ -1211,36 +1211,36 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>Bloom - Single</v>
+        <v>My Way - Single</v>
       </c>
       <c r="G22" t="str">
-        <v>4:25</v>
+        <v>4:02</v>
       </c>
       <c r="H22" t="str">
-        <v>Not for Radio</v>
+        <v>Riley Green</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J22" t="str">
-        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
+        <v>https://music.apple.com/us/artist/riley-green/662432971</v>
       </c>
       <c r="K22" t="str">
-        <v>https://music.apple.com/us/album/ache/1892180567</v>
+        <v>https://music.apple.com/us/album/my-way/1892083036</v>
       </c>
       <c r="L22" t="str">
-        <v>Ache - Not for Radio</v>
+        <v>My Way - Riley Green</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Cut Ties</v>
+        <v>Ache</v>
       </c>
       <c r="B23" t="str">
         <v/>
       </c>
       <c r="C23" t="str">
-        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
+        <v>https://music.apple.com/us/song/ache/1892180581</v>
       </c>
       <c r="D23" t="str">
         <v>2026-04-21</v>
@@ -1249,36 +1249,36 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>Mother Mary: Greatest Hits</v>
+        <v>Bloom - Single</v>
       </c>
       <c r="G23" t="str">
-        <v>4:09</v>
+        <v>4:25</v>
       </c>
       <c r="H23" t="str">
-        <v>Anne Hathaway</v>
+        <v>Not for Radio</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J23" t="str">
-        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
+        <v>https://music.apple.com/us/artist/not-for-radio/1834193679</v>
       </c>
       <c r="K23" t="str">
-        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
+        <v>https://music.apple.com/us/album/ache/1892180567</v>
       </c>
       <c r="L23" t="str">
-        <v>Cut Ties - Anne Hathaway</v>
+        <v>Ache - Not for Radio</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>BROKE BITCH FREE$TYLE</v>
+        <v>Cut Ties</v>
       </c>
       <c r="B24" t="str">
         <v/>
       </c>
       <c r="C24" t="str">
-        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
+        <v>https://music.apple.com/us/song/cut-ties/1887564838</v>
       </c>
       <c r="D24" t="str">
         <v>2026-04-21</v>
@@ -1287,36 +1287,36 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>BROKE BITCH FREE$TYLE - Single</v>
+        <v>Mother Mary: Greatest Hits</v>
       </c>
       <c r="G24" t="str">
-        <v>2:13</v>
+        <v>4:09</v>
       </c>
       <c r="H24" t="str">
-        <v>Slayyyter</v>
+        <v>Anne Hathaway</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J24" t="str">
-        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
+        <v>https://music.apple.com/us/artist/anne-hathaway/3260249</v>
       </c>
       <c r="K24" t="str">
-        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
+        <v>https://music.apple.com/us/album/cut-ties/1887564390</v>
       </c>
       <c r="L24" t="str">
-        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
+        <v>Cut Ties - Anne Hathaway</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Heresy (Nine Inch Noize Version)</v>
+        <v>BROKE BITCH FREE$TYLE</v>
       </c>
       <c r="B25" t="str">
         <v/>
       </c>
       <c r="C25" t="str">
-        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
+        <v>https://music.apple.com/us/song/broke-bitch-free%24tyle/1892137762</v>
       </c>
       <c r="D25" t="str">
         <v>2026-04-21</v>
@@ -1325,36 +1325,36 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>Nine Inch Noize</v>
+        <v>BROKE BITCH FREE$TYLE - Single</v>
       </c>
       <c r="G25" t="str">
-        <v>3:57</v>
+        <v>2:13</v>
       </c>
       <c r="H25" t="str">
-        <v>Nine Inch Nails</v>
+        <v>Slayyyter</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J25" t="str">
-        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
+        <v>https://music.apple.com/us/artist/slayyyter/1424342162</v>
       </c>
       <c r="K25" t="str">
-        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
+        <v>https://music.apple.com/us/album/broke-bitch-free%24tyle/1892137611</v>
       </c>
       <c r="L25" t="str">
-        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
+        <v>BROKE BITCH FREE$TYLE - Slayyyter</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Boots on the Ground</v>
+        <v>Heresy (Nine Inch Noize Version)</v>
       </c>
       <c r="B26" t="str">
         <v/>
       </c>
       <c r="C26" t="str">
-        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
+        <v>https://music.apple.com/us/song/heresy-nine-inch-noize-version/1893171325</v>
       </c>
       <c r="D26" t="str">
         <v>2026-04-21</v>
@@ -1363,36 +1363,36 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>Boots on the Ground - Single</v>
+        <v>Nine Inch Noize</v>
       </c>
       <c r="G26" t="str">
-        <v>4:21</v>
+        <v>3:57</v>
       </c>
       <c r="H26" t="str">
-        <v>Massive Attack</v>
+        <v>Nine Inch Nails</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J26" t="str">
-        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
+        <v>https://music.apple.com/us/artist/nine-inch-nails/107917</v>
       </c>
       <c r="K26" t="str">
-        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
+        <v>https://music.apple.com/us/album/heresy-nine-inch-noize-version/1893171321</v>
       </c>
       <c r="L26" t="str">
-        <v>Boots on the Ground - Massive Attack</v>
+        <v>Heresy (Nine Inch Noize Version) - Nine Inch Nails</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Low Rise Jeans</v>
+        <v>Boots on the Ground</v>
       </c>
       <c r="B27" t="str">
         <v/>
       </c>
       <c r="C27" t="str">
-        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
+        <v>https://music.apple.com/us/song/boots-on-the-ground/1886123358</v>
       </c>
       <c r="D27" t="str">
         <v>2026-04-21</v>
@@ -1401,36 +1401,36 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>Low Rise Jeans - Single</v>
+        <v>Boots on the Ground - Single</v>
       </c>
       <c r="G27" t="str">
-        <v>3:26</v>
+        <v>4:21</v>
       </c>
       <c r="H27" t="str">
-        <v>Demi Lovato</v>
+        <v>Massive Attack</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J27" t="str">
-        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
+        <v>https://music.apple.com/us/artist/massive-attack/526404</v>
       </c>
       <c r="K27" t="str">
-        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
+        <v>https://music.apple.com/us/album/boots-on-the-ground/1886123355</v>
       </c>
       <c r="L27" t="str">
-        <v>Low Rise Jeans - Demi Lovato</v>
+        <v>Boots on the Ground - Massive Attack</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>I CONDEMN</v>
+        <v>Low Rise Jeans</v>
       </c>
       <c r="B28" t="str">
         <v/>
       </c>
       <c r="C28" t="str">
-        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
+        <v>https://music.apple.com/us/song/low-rise-jeans/1891868786</v>
       </c>
       <c r="D28" t="str">
         <v>2026-04-21</v>
@@ -1439,36 +1439,36 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>I CONDEMN - Single</v>
+        <v>Low Rise Jeans - Single</v>
       </c>
       <c r="G28" t="str">
-        <v>2:22</v>
+        <v>3:26</v>
       </c>
       <c r="H28" t="str">
-        <v>The Kid LAROI</v>
+        <v>Demi Lovato</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J28" t="str">
-        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
+        <v>https://music.apple.com/us/artist/demi-lovato/280215821</v>
       </c>
       <c r="K28" t="str">
-        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
+        <v>https://music.apple.com/us/album/low-rise-jeans/1891868785</v>
       </c>
       <c r="L28" t="str">
-        <v>I CONDEMN - The Kid LAROI</v>
+        <v>Low Rise Jeans - Demi Lovato</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Wannabeher</v>
+        <v>I CONDEMN</v>
       </c>
       <c r="B29" t="str">
         <v/>
       </c>
       <c r="C29" t="str">
-        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
+        <v>https://music.apple.com/us/song/i-condemn/1893399674</v>
       </c>
       <c r="D29" t="str">
         <v>2026-04-21</v>
@@ -1477,36 +1477,36 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>Dancing On The Wall</v>
+        <v>I CONDEMN - Single</v>
       </c>
       <c r="G29" t="str">
-        <v>2:34</v>
+        <v>2:22</v>
       </c>
       <c r="H29" t="str">
-        <v>MUNA</v>
+        <v>The Kid LAROI</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J29" t="str">
-        <v>https://music.apple.com/us/artist/muna/1042111883</v>
+        <v>https://music.apple.com/us/artist/the-kid-laroi/1435848034</v>
       </c>
       <c r="K29" t="str">
-        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
+        <v>https://music.apple.com/us/album/i-condemn/1893399673</v>
       </c>
       <c r="L29" t="str">
-        <v>Wannabeher - MUNA</v>
+        <v>I CONDEMN - The Kid LAROI</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Superbloom</v>
+        <v>Wannabeher</v>
       </c>
       <c r="B30" t="str">
         <v/>
       </c>
       <c r="C30" t="str">
-        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
+        <v>https://music.apple.com/us/song/wannabeher/1870703320</v>
       </c>
       <c r="D30" t="str">
         <v>2026-04-21</v>
@@ -1515,36 +1515,36 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>Superbloom</v>
+        <v>Dancing On The Wall</v>
       </c>
       <c r="G30" t="str">
-        <v>4:11</v>
+        <v>2:34</v>
       </c>
       <c r="H30" t="str">
-        <v>Jessie Ware</v>
+        <v>MUNA</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J30" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/muna/1042111883</v>
       </c>
       <c r="K30" t="str">
-        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
+        <v>https://music.apple.com/us/album/wannabeher/1870702692</v>
       </c>
       <c r="L30" t="str">
-        <v>Superbloom - Jessie Ware</v>
+        <v>Wannabeher - MUNA</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Chairwoman Park</v>
+        <v>Superbloom</v>
       </c>
       <c r="B31" t="str">
         <v/>
       </c>
       <c r="C31" t="str">
-        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
+        <v>https://music.apple.com/us/song/superbloom/1869414264</v>
       </c>
       <c r="D31" t="str">
         <v>2026-04-21</v>
@@ -1553,36 +1553,36 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>BEEF Season 2 (Original Soundtrack)</v>
+        <v>Superbloom</v>
       </c>
       <c r="G31" t="str">
-        <v>1:40</v>
+        <v>4:11</v>
       </c>
       <c r="H31" t="str">
-        <v>Finneas O’Connell</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J31" t="str">
-        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K31" t="str">
-        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
+        <v>https://music.apple.com/us/album/superbloom/1869414259</v>
       </c>
       <c r="L31" t="str">
-        <v>Chairwoman Park - Finneas O’Connell</v>
+        <v>Superbloom - Jessie Ware</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Make You Move</v>
+        <v>Chairwoman Park</v>
       </c>
       <c r="B32" t="str">
         <v/>
       </c>
       <c r="C32" t="str">
-        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
+        <v>https://music.apple.com/us/song/chairwoman-park/1887303614</v>
       </c>
       <c r="D32" t="str">
         <v>2026-04-21</v>
@@ -1591,36 +1591,36 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>Make You Move - Single</v>
+        <v>BEEF Season 2 (Original Soundtrack)</v>
       </c>
       <c r="G32" t="str">
-        <v>2:24</v>
+        <v>1:40</v>
       </c>
       <c r="H32" t="str">
-        <v>Dillon Francis</v>
+        <v>Finneas O’Connell</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J32" t="str">
-        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
+        <v>https://music.apple.com/us/artist/finneas-oconnell/1460027590</v>
       </c>
       <c r="K32" t="str">
-        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
+        <v>https://music.apple.com/us/album/chairwoman-park/1887303502</v>
       </c>
       <c r="L32" t="str">
-        <v>Make You Move - Dillon Francis</v>
+        <v>Chairwoman Park - Finneas O’Connell</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>FERRARI</v>
+        <v>Make You Move</v>
       </c>
       <c r="B33" t="str">
         <v/>
       </c>
       <c r="C33" t="str">
-        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
+        <v>https://music.apple.com/us/song/make-you-move/1888335707</v>
       </c>
       <c r="D33" t="str">
         <v>2026-04-21</v>
@@ -1629,36 +1629,36 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>FERRARI - Single</v>
+        <v>Make You Move - Single</v>
       </c>
       <c r="G33" t="str">
-        <v>2:14</v>
+        <v>2:24</v>
       </c>
       <c r="H33" t="str">
-        <v>Clave Especial</v>
+        <v>Dillon Francis</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J33" t="str">
-        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
+        <v>https://music.apple.com/us/artist/dillon-francis/366828522</v>
       </c>
       <c r="K33" t="str">
-        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
+        <v>https://music.apple.com/us/album/make-you-move/1888335706</v>
       </c>
       <c r="L33" t="str">
-        <v>FERRARI - Clave Especial</v>
+        <v>Make You Move - Dillon Francis</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Por Ella</v>
+        <v>FERRARI</v>
       </c>
       <c r="B34" t="str">
         <v/>
       </c>
       <c r="C34" t="str">
-        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
+        <v>https://music.apple.com/us/song/ferrari/1892533214</v>
       </c>
       <c r="D34" t="str">
         <v>2026-04-21</v>
@@ -1667,36 +1667,36 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
+        <v>FERRARI - Single</v>
       </c>
       <c r="G34" t="str">
-        <v>3:01</v>
+        <v>2:14</v>
       </c>
       <c r="H34" t="str">
-        <v>Los Ángeles Azules</v>
+        <v>Clave Especial</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J34" t="str">
-        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
+        <v>https://music.apple.com/us/artist/clave-especial/1569749622</v>
       </c>
       <c r="K34" t="str">
-        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
+        <v>https://music.apple.com/us/album/ferrari/1892533212</v>
       </c>
       <c r="L34" t="str">
-        <v>Por Ella - Los Ángeles Azules</v>
+        <v>FERRARI - Clave Especial</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Stick With You</v>
+        <v>Por Ella</v>
       </c>
       <c r="B35" t="str">
         <v/>
       </c>
       <c r="C35" t="str">
-        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
+        <v>https://music.apple.com/us/song/por-ella/1893448802</v>
       </c>
       <c r="D35" t="str">
         <v>2026-04-21</v>
@@ -1705,36 +1705,36 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
+        <v>Por Ella (FIFA World Cup 2026™) - Single</v>
       </c>
       <c r="G35" t="str">
-        <v>2:33</v>
+        <v>3:01</v>
       </c>
       <c r="H35" t="str">
-        <v>TOMORROW X TOGETHER</v>
+        <v>Los Ángeles Azules</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J35" t="str">
-        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
+        <v>https://music.apple.com/us/artist/los-%C3%A1ngeles-azules/3500477</v>
       </c>
       <c r="K35" t="str">
-        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
+        <v>https://music.apple.com/us/album/por-ella/1893448800</v>
       </c>
       <c r="L35" t="str">
-        <v>Stick With You - TOMORROW X TOGETHER</v>
+        <v>Por Ella - Los Ángeles Azules</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>KGB</v>
+        <v>Stick With You</v>
       </c>
       <c r="B36" t="str">
         <v/>
       </c>
       <c r="C36" t="str">
-        <v>https://music.apple.com/us/song/kgb/1888356648</v>
+        <v>https://music.apple.com/us/song/stick-with-you/1886536332</v>
       </c>
       <c r="D36" t="str">
         <v>2026-04-21</v>
@@ -1743,36 +1743,36 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>KGB - Single</v>
+        <v>7TH YEAR: A Moment of Stillness in the Thorns - EP</v>
       </c>
       <c r="G36" t="str">
-        <v>2:37</v>
+        <v>2:33</v>
       </c>
       <c r="H36" t="str">
-        <v>ADÉLA</v>
+        <v>TOMORROW X TOGETHER</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J36" t="str">
-        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
+        <v>https://music.apple.com/us/artist/tomorrow-x-together/1454642552</v>
       </c>
       <c r="K36" t="str">
-        <v>https://music.apple.com/us/album/kgb/1888356589</v>
+        <v>https://music.apple.com/us/album/stick-with-you/1886536327</v>
       </c>
       <c r="L36" t="str">
-        <v>KGB - ADÉLA</v>
+        <v>Stick With You - TOMORROW X TOGETHER</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Holly!</v>
+        <v>KGB</v>
       </c>
       <c r="B37" t="str">
         <v/>
       </c>
       <c r="C37" t="str">
-        <v>https://music.apple.com/us/song/holly/1887616413</v>
+        <v>https://music.apple.com/us/song/kgb/1888356648</v>
       </c>
       <c r="D37" t="str">
         <v>2026-04-21</v>
@@ -1781,36 +1781,36 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>NeverAlways (Vol. 2)</v>
+        <v>KGB - Single</v>
       </c>
       <c r="G37" t="str">
-        <v>3:10</v>
+        <v>2:37</v>
       </c>
       <c r="H37" t="str">
-        <v>The Band CAMINO</v>
+        <v>ADÉLA</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J37" t="str">
-        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
+        <v>https://music.apple.com/us/artist/ad%C3%A9la/1765924916</v>
       </c>
       <c r="K37" t="str">
-        <v>https://music.apple.com/us/album/holly/1887616173</v>
+        <v>https://music.apple.com/us/album/kgb/1888356589</v>
       </c>
       <c r="L37" t="str">
-        <v>Holly! - The Band CAMINO</v>
+        <v>KGB - ADÉLA</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sunday Again</v>
+        <v>Holly!</v>
       </c>
       <c r="B38" t="str">
         <v/>
       </c>
       <c r="C38" t="str">
-        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
+        <v>https://music.apple.com/us/song/holly/1887616413</v>
       </c>
       <c r="D38" t="str">
         <v>2026-04-21</v>
@@ -1819,36 +1819,36 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>Love is the New Gangsta</v>
+        <v>NeverAlways (Vol. 2)</v>
       </c>
       <c r="G38" t="str">
-        <v>3:40</v>
+        <v>3:10</v>
       </c>
       <c r="H38" t="str">
-        <v>6LACK</v>
+        <v>The Band CAMINO</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J38" t="str">
-        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
+        <v>https://music.apple.com/us/artist/the-band-camino/1097752725</v>
       </c>
       <c r="K38" t="str">
-        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
+        <v>https://music.apple.com/us/album/holly/1887616173</v>
       </c>
       <c r="L38" t="str">
-        <v>Sunday Again - 6LACK</v>
+        <v>Holly! - The Band CAMINO</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Move Time</v>
+        <v>Sunday Again</v>
       </c>
       <c r="B39" t="str">
         <v/>
       </c>
       <c r="C39" t="str">
-        <v>https://music.apple.com/us/song/move-time/1884662146</v>
+        <v>https://music.apple.com/us/song/sunday-again/1884792302</v>
       </c>
       <c r="D39" t="str">
         <v>2026-04-21</v>
@@ -1857,36 +1857,36 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>Move Time - Single</v>
+        <v>Love is the New Gangsta</v>
       </c>
       <c r="G39" t="str">
-        <v>3:39</v>
+        <v>3:40</v>
       </c>
       <c r="H39" t="str">
-        <v>MJ Cole</v>
+        <v>6LACK</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J39" t="str">
-        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
+        <v>https://music.apple.com/us/artist/6lack/1016633280</v>
       </c>
       <c r="K39" t="str">
-        <v>https://music.apple.com/us/album/move-time/1884662145</v>
+        <v>https://music.apple.com/us/album/sunday-again/1884792154</v>
       </c>
       <c r="L39" t="str">
-        <v>Move Time - MJ Cole</v>
+        <v>Sunday Again - 6LACK</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>I Want You</v>
+        <v>Move Time</v>
       </c>
       <c r="B40" t="str">
         <v/>
       </c>
       <c r="C40" t="str">
-        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
+        <v>https://music.apple.com/us/song/move-time/1884662146</v>
       </c>
       <c r="D40" t="str">
         <v>2026-04-21</v>
@@ -1895,36 +1895,36 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>Banks Of The Trinity</v>
+        <v>Move Time - Single</v>
       </c>
       <c r="G40" t="str">
-        <v>3:10</v>
+        <v>3:39</v>
       </c>
       <c r="H40" t="str">
-        <v>Cody Johnson</v>
+        <v>MJ Cole</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J40" t="str">
-        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
+        <v>https://music.apple.com/us/artist/mj-cole/405892</v>
       </c>
       <c r="K40" t="str">
-        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
+        <v>https://music.apple.com/us/album/move-time/1884662145</v>
       </c>
       <c r="L40" t="str">
-        <v>I Want You - Cody Johnson</v>
+        <v>Move Time - MJ Cole</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Straddle Me</v>
+        <v>I Want You</v>
       </c>
       <c r="B41" t="str">
         <v/>
       </c>
       <c r="C41" t="str">
-        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
+        <v>https://music.apple.com/us/song/i-want-you/1892466281</v>
       </c>
       <c r="D41" t="str">
         <v>2026-04-21</v>
@@ -1933,36 +1933,36 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>Straddle Me - Single</v>
+        <v>Banks Of The Trinity</v>
       </c>
       <c r="G41" t="str">
-        <v>3:11</v>
+        <v>3:10</v>
       </c>
       <c r="H41" t="str">
-        <v>Mike Clark Jr</v>
+        <v>Cody Johnson</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J41" t="str">
-        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
+        <v>https://music.apple.com/us/artist/cody-johnson/331459657</v>
       </c>
       <c r="K41" t="str">
-        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
+        <v>https://music.apple.com/us/album/i-want-you/1892465981</v>
       </c>
       <c r="L41" t="str">
-        <v>Straddle Me - Mike Clark Jr</v>
+        <v>I Want You - Cody Johnson</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Ring</v>
+        <v>Straddle Me</v>
       </c>
       <c r="B42" t="str">
         <v/>
       </c>
       <c r="C42" t="str">
-        <v>https://music.apple.com/us/song/ring/1890334908</v>
+        <v>https://music.apple.com/us/song/straddle-me/1891380773</v>
       </c>
       <c r="D42" t="str">
         <v>2026-04-21</v>
@@ -1971,36 +1971,36 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>Ring - Single</v>
+        <v>Straddle Me - Single</v>
       </c>
       <c r="G42" t="str">
-        <v>3:21</v>
+        <v>3:11</v>
       </c>
       <c r="H42" t="str">
-        <v>Queen Naija</v>
+        <v>Mike Clark Jr</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J42" t="str">
-        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
+        <v>https://music.apple.com/us/artist/mike-clark-jr/1689302017</v>
       </c>
       <c r="K42" t="str">
-        <v>https://music.apple.com/us/album/ring/1890334572</v>
+        <v>https://music.apple.com/us/album/straddle-me/1891380764</v>
       </c>
       <c r="L42" t="str">
-        <v>Ring - Queen Naija</v>
+        <v>Straddle Me - Mike Clark Jr</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Lines In The Carpet</v>
+        <v>Ring</v>
       </c>
       <c r="B43" t="str">
         <v/>
       </c>
       <c r="C43" t="str">
-        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
+        <v>https://music.apple.com/us/song/ring/1890334908</v>
       </c>
       <c r="D43" t="str">
         <v>2026-04-21</v>
@@ -2009,36 +2009,36 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>Wild</v>
+        <v>Ring - Single</v>
       </c>
       <c r="G43" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H43" t="str">
-        <v>Ashley McBryde</v>
+        <v>Queen Naija</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J43" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/queen-naija/1392861271</v>
       </c>
       <c r="K43" t="str">
-        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
+        <v>https://music.apple.com/us/album/ring/1890334572</v>
       </c>
       <c r="L43" t="str">
-        <v>Lines In The Carpet - Ashley McBryde</v>
+        <v>Ring - Queen Naija</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Stay Love</v>
+        <v>Lines In The Carpet</v>
       </c>
       <c r="B44" t="str">
         <v/>
       </c>
       <c r="C44" t="str">
-        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
+        <v>https://music.apple.com/us/song/lines-in-the-carpet/1885047093</v>
       </c>
       <c r="D44" t="str">
         <v>2026-04-21</v>
@@ -2047,36 +2047,36 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>Survive - EP</v>
+        <v>Wild</v>
       </c>
       <c r="G44" t="str">
-        <v>3:26</v>
+        <v>3:24</v>
       </c>
       <c r="H44" t="str">
-        <v>Lewis Capaldi</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J44" t="str">
-        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K44" t="str">
-        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
+        <v>https://music.apple.com/us/album/lines-in-the-carpet/1885046822</v>
       </c>
       <c r="L44" t="str">
-        <v>Stay Love - Lewis Capaldi</v>
+        <v>Lines In The Carpet - Ashley McBryde</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Love Me</v>
+        <v>Stay Love</v>
       </c>
       <c r="B45" t="str">
         <v/>
       </c>
       <c r="C45" t="str">
-        <v>https://music.apple.com/us/song/love-me/1878237810</v>
+        <v>https://music.apple.com/us/song/stay-love/1891664212</v>
       </c>
       <c r="D45" t="str">
         <v>2026-04-21</v>
@@ -2085,36 +2085,36 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>Dear God</v>
+        <v>Survive - EP</v>
       </c>
       <c r="G45" t="str">
-        <v>4:23</v>
+        <v>3:26</v>
       </c>
       <c r="H45" t="str">
-        <v>The Pretty Reckless</v>
+        <v>Lewis Capaldi</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J45" t="str">
-        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
+        <v>https://music.apple.com/us/artist/lewis-capaldi/1213405916</v>
       </c>
       <c r="K45" t="str">
-        <v>https://music.apple.com/us/album/love-me/1878237662</v>
+        <v>https://music.apple.com/us/album/stay-love/1891663823</v>
       </c>
       <c r="L45" t="str">
-        <v>Love Me - The Pretty Reckless</v>
+        <v>Stay Love - Lewis Capaldi</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Seconds Before The Sunrise</v>
+        <v>Love Me</v>
       </c>
       <c r="B46" t="str">
         <v/>
       </c>
       <c r="C46" t="str">
-        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
+        <v>https://music.apple.com/us/song/love-me/1878237810</v>
       </c>
       <c r="D46" t="str">
         <v>2026-04-21</v>
@@ -2123,36 +2123,36 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>Seconds Before The Sunrise - Single</v>
+        <v>Dear God</v>
       </c>
       <c r="G46" t="str">
-        <v>3:02</v>
+        <v>4:23</v>
       </c>
       <c r="H46" t="str">
-        <v>Dean Lewis</v>
+        <v>The Pretty Reckless</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J46" t="str">
-        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
+        <v>https://music.apple.com/us/artist/the-pretty-reckless/363203347</v>
       </c>
       <c r="K46" t="str">
-        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
+        <v>https://music.apple.com/us/album/love-me/1878237662</v>
       </c>
       <c r="L46" t="str">
-        <v>Seconds Before The Sunrise - Dean Lewis</v>
+        <v>Love Me - The Pretty Reckless</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Balboa Park</v>
+        <v>Seconds Before The Sunrise</v>
       </c>
       <c r="B47" t="str">
         <v/>
       </c>
       <c r="C47" t="str">
-        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
+        <v>https://music.apple.com/us/song/seconds-before-the-sunrise/1886165987</v>
       </c>
       <c r="D47" t="str">
         <v>2026-04-21</v>
@@ -2161,36 +2161,36 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>Let It Die Here</v>
+        <v>Seconds Before The Sunrise - Single</v>
       </c>
       <c r="G47" t="str">
-        <v>3:52</v>
+        <v>3:02</v>
       </c>
       <c r="H47" t="str">
-        <v>Linda Perry</v>
+        <v>Dean Lewis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J47" t="str">
-        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
+        <v>https://music.apple.com/us/artist/dean-lewis/779085108</v>
       </c>
       <c r="K47" t="str">
-        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
+        <v>https://music.apple.com/us/album/seconds-before-the-sunrise/1886165713</v>
       </c>
       <c r="L47" t="str">
-        <v>Balboa Park - Linda Perry</v>
+        <v>Seconds Before The Sunrise - Dean Lewis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The One You Loved</v>
+        <v>Balboa Park</v>
       </c>
       <c r="B48" t="str">
         <v/>
       </c>
       <c r="C48" t="str">
-        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
+        <v>https://music.apple.com/us/song/balboa-park/1864389784</v>
       </c>
       <c r="D48" t="str">
         <v>2026-04-21</v>
@@ -2199,36 +2199,36 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>The One You Loved - Single</v>
+        <v>Let It Die Here</v>
       </c>
       <c r="G48" t="str">
-        <v>3:08</v>
+        <v>3:52</v>
       </c>
       <c r="H48" t="str">
-        <v>Kenya Grace</v>
+        <v>Linda Perry</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J48" t="str">
-        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
+        <v>https://music.apple.com/us/artist/linda-perry/316041</v>
       </c>
       <c r="K48" t="str">
-        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
+        <v>https://music.apple.com/us/album/balboa-park/1864389779</v>
       </c>
       <c r="L48" t="str">
-        <v>The One You Loved - Kenya Grace</v>
+        <v>Balboa Park - Linda Perry</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Desgraça</v>
+        <v>The One You Loved</v>
       </c>
       <c r="B49" t="str">
         <v/>
       </c>
       <c r="C49" t="str">
-        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
+        <v>https://music.apple.com/us/song/the-one-you-loved/1891833986</v>
       </c>
       <c r="D49" t="str">
         <v>2026-04-21</v>
@@ -2237,36 +2237,36 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>EQUILIBRIVM</v>
+        <v>The One You Loved - Single</v>
       </c>
       <c r="G49" t="str">
-        <v>2:50</v>
+        <v>3:08</v>
       </c>
       <c r="H49" t="str">
-        <v>Anitta</v>
+        <v>Kenya Grace</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J49" t="str">
-        <v>https://music.apple.com/us/artist/anitta/597214610</v>
+        <v>https://music.apple.com/us/artist/kenya-grace/1476584041</v>
       </c>
       <c r="K49" t="str">
-        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
+        <v>https://music.apple.com/us/album/the-one-you-loved/1891833876</v>
       </c>
       <c r="L49" t="str">
-        <v>Desgraça - Anitta</v>
+        <v>The One You Loved - Kenya Grace</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>CHUCK THE MONEY</v>
+        <v>Desgraça</v>
       </c>
       <c r="B50" t="str">
         <v/>
       </c>
       <c r="C50" t="str">
-        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
+        <v>https://music.apple.com/us/song/desgra%C3%A7a/1893225298</v>
       </c>
       <c r="D50" t="str">
         <v>2026-04-21</v>
@@ -2275,36 +2275,36 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>LOVE, LOVE, LOVE</v>
+        <v>EQUILIBRIVM</v>
       </c>
       <c r="G50" t="str">
-        <v>2:44</v>
+        <v>2:50</v>
       </c>
       <c r="H50" t="str">
-        <v>Stephen Sanchez</v>
+        <v>Anitta</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J50" t="str">
-        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
+        <v>https://music.apple.com/us/artist/anitta/597214610</v>
       </c>
       <c r="K50" t="str">
-        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
+        <v>https://music.apple.com/us/album/desgra%C3%A7a/1893225297</v>
       </c>
       <c r="L50" t="str">
-        <v>CHUCK THE MONEY - Stephen Sanchez</v>
+        <v>Desgraça - Anitta</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Dansons</v>
+        <v>CHUCK THE MONEY</v>
       </c>
       <c r="B51" t="str">
         <v/>
       </c>
       <c r="C51" t="str">
-        <v>https://music.apple.com/us/song/dansons/1892460437</v>
+        <v>https://music.apple.com/us/song/chuck-the-money/1880198198</v>
       </c>
       <c r="D51" t="str">
         <v>2026-04-21</v>
@@ -2313,36 +2313,36 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>Dansons - Single</v>
+        <v>LOVE, LOVE, LOVE</v>
       </c>
       <c r="G51" t="str">
-        <v>3:26</v>
+        <v>2:44</v>
       </c>
       <c r="H51" t="str">
-        <v>Céline Dion</v>
+        <v>Stephen Sanchez</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J51" t="str">
-        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
+        <v>https://music.apple.com/us/artist/stephen-sanchez/1276541872</v>
       </c>
       <c r="K51" t="str">
-        <v>https://music.apple.com/us/album/dansons/1892460429</v>
+        <v>https://music.apple.com/us/album/chuck-the-money/1880197844</v>
       </c>
       <c r="L51" t="str">
-        <v>Dansons - Céline Dion</v>
+        <v>CHUCK THE MONEY - Stephen Sanchez</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Death Grip (feat. HAFFWAY)</v>
+        <v>Dansons</v>
       </c>
       <c r="B52" t="str">
         <v/>
       </c>
       <c r="C52" t="str">
-        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
+        <v>https://music.apple.com/us/song/dansons/1892460437</v>
       </c>
       <c r="D52" t="str">
         <v>2026-04-21</v>
@@ -2351,36 +2351,36 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Single</v>
+        <v>Dansons - Single</v>
       </c>
       <c r="G52" t="str">
-        <v>2:57</v>
+        <v>3:26</v>
       </c>
       <c r="H52" t="str">
-        <v>Trousdale</v>
+        <v>Céline Dion</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J52" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/c%C3%A9line-dion/63729</v>
       </c>
       <c r="K52" t="str">
-        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
+        <v>https://music.apple.com/us/album/dansons/1892460429</v>
       </c>
       <c r="L52" t="str">
-        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
+        <v>Dansons - Céline Dion</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version)</v>
+        <v>Death Grip (feat. HAFFWAY)</v>
       </c>
       <c r="B53" t="str">
         <v/>
       </c>
       <c r="C53" t="str">
-        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
+        <v>https://music.apple.com/us/song/death-grip-feat-haffway/1884053772</v>
       </c>
       <c r="D53" t="str">
         <v>2026-04-21</v>
@@ -2389,36 +2389,36 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
+        <v>Death Grip (feat. HAFFWAY) - Single</v>
       </c>
       <c r="G53" t="str">
-        <v>5:21</v>
+        <v>2:57</v>
       </c>
       <c r="H53" t="str">
-        <v>This Is Lorelei</v>
+        <v>Trousdale</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J53" t="str">
-        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K53" t="str">
-        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
+        <v>https://music.apple.com/us/album/death-grip-feat-haffway/1884053771</v>
       </c>
       <c r="L53" t="str">
-        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
+        <v>Death Grip (feat. HAFFWAY) - Trousdale</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Rodeo Clowns (4-track)</v>
+        <v>Where’s Your Love Now (Waxahatchee Version)</v>
       </c>
       <c r="B54" t="str">
         <v/>
       </c>
       <c r="C54" t="str">
-        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
+        <v>https://music.apple.com/us/song/wheres-your-love-now-waxahatchee-version/1877035405</v>
       </c>
       <c r="D54" t="str">
         <v>2026-04-21</v>
@@ -2427,36 +2427,36 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
+        <v>Box for Buddy, Box for Star (Super Deluxe)</v>
       </c>
       <c r="G54" t="str">
-        <v>2:49</v>
+        <v>5:21</v>
       </c>
       <c r="H54" t="str">
-        <v>Jack Johnson</v>
+        <v>This Is Lorelei</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J54" t="str">
-        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
+        <v>https://music.apple.com/us/artist/this-is-lorelei/1249727049</v>
       </c>
       <c r="K54" t="str">
-        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
+        <v>https://music.apple.com/us/album/wheres-your-love-now-waxahatchee-version/1877035065</v>
       </c>
       <c r="L54" t="str">
-        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
+        <v>Where’s Your Love Now (Waxahatchee Version) - This Is Lorelei</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>We'd Make A Good Movie</v>
+        <v>Rodeo Clowns (4-track)</v>
       </c>
       <c r="B55" t="str">
         <v/>
       </c>
       <c r="C55" t="str">
-        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
+        <v>https://music.apple.com/us/song/rodeo-clowns-4-track/1883173169</v>
       </c>
       <c r="D55" t="str">
         <v>2026-04-21</v>
@@ -2465,36 +2465,36 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>Dream Chaser</v>
+        <v>SURFILMUSIC (Soundtrack &amp; 4-Tracks)</v>
       </c>
       <c r="G55" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H55" t="str">
-        <v>Willie Nelson</v>
+        <v>Jack Johnson</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J55" t="str">
-        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
+        <v>https://music.apple.com/us/artist/jack-johnson/909253</v>
       </c>
       <c r="K55" t="str">
-        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
+        <v>https://music.apple.com/us/album/rodeo-clowns-4-track/1883172879</v>
       </c>
       <c r="L55" t="str">
-        <v>We'd Make A Good Movie - Willie Nelson</v>
+        <v>Rodeo Clowns (4-track) - Jack Johnson</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>I DRINK THE LIGHT</v>
+        <v>We'd Make A Good Movie</v>
       </c>
       <c r="B56" t="str">
         <v/>
       </c>
       <c r="C56" t="str">
-        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
+        <v>https://music.apple.com/us/song/wed-make-a-good-movie/1884219680</v>
       </c>
       <c r="D56" t="str">
         <v>2026-04-21</v>
@@ -2503,36 +2503,36 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>COME CLOSER</v>
+        <v>Dream Chaser</v>
       </c>
       <c r="G56" t="str">
-        <v>7:56</v>
+        <v>3:32</v>
       </c>
       <c r="H56" t="str">
-        <v>TOMORA</v>
+        <v>Willie Nelson</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J56" t="str">
-        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
+        <v>https://music.apple.com/us/artist/willie-nelson/71676</v>
       </c>
       <c r="K56" t="str">
-        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
+        <v>https://music.apple.com/us/album/wed-make-a-good-movie/1884219677</v>
       </c>
       <c r="L56" t="str">
-        <v>I DRINK THE LIGHT - TOMORA</v>
+        <v>We'd Make A Good Movie - Willie Nelson</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Everything U</v>
+        <v>I DRINK THE LIGHT</v>
       </c>
       <c r="B57" t="str">
         <v/>
       </c>
       <c r="C57" t="str">
-        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
+        <v>https://music.apple.com/us/song/i-drink-the-light/1871185071</v>
       </c>
       <c r="D57" t="str">
         <v>2026-04-21</v>
@@ -2541,36 +2541,36 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>If This Is It</v>
+        <v>COME CLOSER</v>
       </c>
       <c r="G57" t="str">
-        <v>3:30</v>
+        <v>7:56</v>
       </c>
       <c r="H57" t="str">
-        <v>DJ Seinfeld</v>
+        <v>TOMORA</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J57" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/tomora/1852575872</v>
       </c>
       <c r="K57" t="str">
-        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
+        <v>https://music.apple.com/us/album/i-drink-the-light/1871184398</v>
       </c>
       <c r="L57" t="str">
-        <v>Everything U - DJ Seinfeld</v>
+        <v>I DRINK THE LIGHT - TOMORA</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>If It's Not Love</v>
+        <v>Everything U</v>
       </c>
       <c r="B58" t="str">
         <v/>
       </c>
       <c r="C58" t="str">
-        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
+        <v>https://music.apple.com/us/song/everything-u/1871227339</v>
       </c>
       <c r="D58" t="str">
         <v>2026-04-21</v>
@@ -2579,36 +2579,36 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>If It's Not Love - Single</v>
+        <v>If This Is It</v>
       </c>
       <c r="G58" t="str">
-        <v>4:21</v>
+        <v>3:30</v>
       </c>
       <c r="H58" t="str">
-        <v>ZERB</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J58" t="str">
-        <v>https://music.apple.com/us/artist/zerb/275494817</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K58" t="str">
-        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
+        <v>https://music.apple.com/us/album/everything-u/1871227330</v>
       </c>
       <c r="L58" t="str">
-        <v>If It's Not Love - ZERB</v>
+        <v>Everything U - DJ Seinfeld</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Our Last Fight</v>
+        <v>If It's Not Love</v>
       </c>
       <c r="B59" t="str">
         <v/>
       </c>
       <c r="C59" t="str">
-        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
+        <v>https://music.apple.com/us/song/if-its-not-love/1886411536</v>
       </c>
       <c r="D59" t="str">
         <v>2026-04-21</v>
@@ -2617,36 +2617,36 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>soft pop</v>
+        <v>If It's Not Love - Single</v>
       </c>
       <c r="G59" t="str">
-        <v>3:02</v>
+        <v>4:21</v>
       </c>
       <c r="H59" t="str">
-        <v>Amy Shark</v>
+        <v>ZERB</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J59" t="str">
-        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
+        <v>https://music.apple.com/us/artist/zerb/275494817</v>
       </c>
       <c r="K59" t="str">
-        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
+        <v>https://music.apple.com/us/album/if-its-not-love/1886411535</v>
       </c>
       <c r="L59" t="str">
-        <v>Our Last Fight - Amy Shark</v>
+        <v>If It's Not Love - ZERB</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Eyes Cut Deeper</v>
+        <v>Our Last Fight</v>
       </c>
       <c r="B60" t="str">
         <v/>
       </c>
       <c r="C60" t="str">
-        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
+        <v>https://music.apple.com/us/song/our-last-fight/1880496747</v>
       </c>
       <c r="D60" t="str">
         <v>2026-04-21</v>
@@ -2655,36 +2655,36 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>Eyes Cut Deeper - Single</v>
+        <v>soft pop</v>
       </c>
       <c r="G60" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H60" t="str">
-        <v>Subtronics</v>
+        <v>Amy Shark</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J60" t="str">
-        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
+        <v>https://music.apple.com/us/artist/amy-shark/1083179259</v>
       </c>
       <c r="K60" t="str">
-        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
+        <v>https://music.apple.com/us/album/our-last-fight/1880496743</v>
       </c>
       <c r="L60" t="str">
-        <v>Eyes Cut Deeper - Subtronics</v>
+        <v>Our Last Fight - Amy Shark</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Perfect One</v>
+        <v>Eyes Cut Deeper</v>
       </c>
       <c r="B61" t="str">
         <v/>
       </c>
       <c r="C61" t="str">
-        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
+        <v>https://music.apple.com/us/song/eyes-cut-deeper/1890056754</v>
       </c>
       <c r="D61" t="str">
         <v>2026-04-21</v>
@@ -2693,36 +2693,36 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>At Least She's Beautiful</v>
+        <v>Eyes Cut Deeper - Single</v>
       </c>
       <c r="G61" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H61" t="str">
-        <v>rjtheweirdo</v>
+        <v>Subtronics</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J61" t="str">
-        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
+        <v>https://music.apple.com/us/artist/subtronics/576543499</v>
       </c>
       <c r="K61" t="str">
-        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
+        <v>https://music.apple.com/us/album/eyes-cut-deeper/1890056751</v>
       </c>
       <c r="L61" t="str">
-        <v>The Perfect One - rjtheweirdo</v>
+        <v>Eyes Cut Deeper - Subtronics</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Outside</v>
+        <v>The Perfect One</v>
       </c>
       <c r="B62" t="str">
         <v/>
       </c>
       <c r="C62" t="str">
-        <v>https://music.apple.com/us/song/outside/1889990724</v>
+        <v>https://music.apple.com/us/song/the-perfect-one/1889992071</v>
       </c>
       <c r="D62" t="str">
         <v>2026-04-21</v>
@@ -2731,36 +2731,36 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>Outside - Single</v>
+        <v>At Least She's Beautiful</v>
       </c>
       <c r="G62" t="str">
-        <v>3:15</v>
+        <v>2:56</v>
       </c>
       <c r="H62" t="str">
-        <v>Inayah</v>
+        <v>rjtheweirdo</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J62" t="str">
-        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
+        <v>https://music.apple.com/us/artist/rjtheweirdo/1705150968</v>
       </c>
       <c r="K62" t="str">
-        <v>https://music.apple.com/us/album/outside/1889990714</v>
+        <v>https://music.apple.com/us/album/the-perfect-one/1889992065</v>
       </c>
       <c r="L62" t="str">
-        <v>Outside - Inayah</v>
+        <v>The Perfect One - rjtheweirdo</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>N.Y.F.F.</v>
+        <v>Outside</v>
       </c>
       <c r="B63" t="str">
         <v/>
       </c>
       <c r="C63" t="str">
-        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
+        <v>https://music.apple.com/us/song/outside/1889990724</v>
       </c>
       <c r="D63" t="str">
         <v>2026-04-21</v>
@@ -2769,36 +2769,36 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>N.Y.F.F. - Single</v>
+        <v>Outside - Single</v>
       </c>
       <c r="G63" t="str">
-        <v>2:25</v>
+        <v>3:15</v>
       </c>
       <c r="H63" t="str">
-        <v>Jessie Reyez</v>
+        <v>Inayah</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J63" t="str">
-        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
+        <v>https://music.apple.com/us/artist/inayah/1488027733</v>
       </c>
       <c r="K63" t="str">
-        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
+        <v>https://music.apple.com/us/album/outside/1889990714</v>
       </c>
       <c r="L63" t="str">
-        <v>N.Y.F.F. - Jessie Reyez</v>
+        <v>Outside - Inayah</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Heart You Didn't Break</v>
+        <v>N.Y.F.F.</v>
       </c>
       <c r="B64" t="str">
         <v/>
       </c>
       <c r="C64" t="str">
-        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
+        <v>https://music.apple.com/us/song/n-y-f-f/1891454055</v>
       </c>
       <c r="D64" t="str">
         <v>2026-04-21</v>
@@ -2807,36 +2807,36 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>Heart You Didn't Break - Single</v>
+        <v>N.Y.F.F. - Single</v>
       </c>
       <c r="G64" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H64" t="str">
-        <v>Max McNown</v>
+        <v>Jessie Reyez</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J64" t="str">
-        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
+        <v>https://music.apple.com/us/artist/jessie-reyez/1043591612</v>
       </c>
       <c r="K64" t="str">
-        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
+        <v>https://music.apple.com/us/album/n-y-f-f/1891454049</v>
       </c>
       <c r="L64" t="str">
-        <v>Heart You Didn't Break - Max McNown</v>
+        <v>N.Y.F.F. - Jessie Reyez</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Heart Stop</v>
+        <v>Heart You Didn't Break</v>
       </c>
       <c r="B65" t="str">
         <v/>
       </c>
       <c r="C65" t="str">
-        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
+        <v>https://music.apple.com/us/song/heart-you-didnt-break/1886546615</v>
       </c>
       <c r="D65" t="str">
         <v>2026-04-21</v>
@@ -2845,36 +2845,36 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>Get It Honest</v>
+        <v>Heart You Didn't Break - Single</v>
       </c>
       <c r="G65" t="str">
-        <v>4:19</v>
+        <v>3:12</v>
       </c>
       <c r="H65" t="str">
-        <v>The Revivalists</v>
+        <v>Max McNown</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J65" t="str">
-        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
+        <v>https://music.apple.com/us/artist/max-mcnown/1682299543</v>
       </c>
       <c r="K65" t="str">
-        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
+        <v>https://music.apple.com/us/album/heart-you-didnt-break/1886546610</v>
       </c>
       <c r="L65" t="str">
-        <v>Heart Stop - The Revivalists</v>
+        <v>Heart You Didn't Break - Max McNown</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Don't Ask Me</v>
+        <v>Heart Stop</v>
       </c>
       <c r="B66" t="str">
         <v/>
       </c>
       <c r="C66" t="str">
-        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
+        <v>https://music.apple.com/us/song/heart-stop/1888004803</v>
       </c>
       <c r="D66" t="str">
         <v>2026-04-21</v>
@@ -2883,36 +2883,36 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>Don't Ask Me - Single</v>
+        <v>Get It Honest</v>
       </c>
       <c r="G66" t="str">
-        <v>3:14</v>
+        <v>4:19</v>
       </c>
       <c r="H66" t="str">
-        <v>Vincent Mason</v>
+        <v>The Revivalists</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J66" t="str">
-        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
+        <v>https://music.apple.com/us/artist/the-revivalists/288615324</v>
       </c>
       <c r="K66" t="str">
-        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
+        <v>https://music.apple.com/us/album/heart-stop/1888004802</v>
       </c>
       <c r="L66" t="str">
-        <v>Don't Ask Me - Vincent Mason</v>
+        <v>Heart Stop - The Revivalists</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>OSADÍA</v>
+        <v>Don't Ask Me</v>
       </c>
       <c r="B67" t="str">
         <v/>
       </c>
       <c r="C67" t="str">
-        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
+        <v>https://music.apple.com/us/song/dont-ask-me/1888369837</v>
       </c>
       <c r="D67" t="str">
         <v>2026-04-21</v>
@@ -2921,36 +2921,36 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>OSADÍA - Single</v>
+        <v>Don't Ask Me - Single</v>
       </c>
       <c r="G67" t="str">
-        <v>3:26</v>
+        <v>3:14</v>
       </c>
       <c r="H67" t="str">
-        <v>Eden Muñoz</v>
+        <v>Vincent Mason</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J67" t="str">
-        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
+        <v>https://music.apple.com/us/artist/vincent-mason/1602781449</v>
       </c>
       <c r="K67" t="str">
-        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
+        <v>https://music.apple.com/us/album/dont-ask-me/1888369828</v>
       </c>
       <c r="L67" t="str">
-        <v>OSADÍA - Eden Muñoz</v>
+        <v>Don't Ask Me - Vincent Mason</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Deep Water</v>
+        <v>OSADÍA</v>
       </c>
       <c r="B68" t="str">
         <v/>
       </c>
       <c r="C68" t="str">
-        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
+        <v>https://music.apple.com/us/song/osad%C3%ADa/1889956789</v>
       </c>
       <c r="D68" t="str">
         <v>2026-04-21</v>
@@ -2959,36 +2959,36 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>Deep Water - EP</v>
+        <v>OSADÍA - Single</v>
       </c>
       <c r="G68" t="str">
-        <v>2:33</v>
+        <v>3:26</v>
       </c>
       <c r="H68" t="str">
-        <v>Cameron Whitcomb</v>
+        <v>Eden Muñoz</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J68" t="str">
-        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
+        <v>https://music.apple.com/us/artist/eden-mu%C3%B1oz/383984059</v>
       </c>
       <c r="K68" t="str">
-        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
+        <v>https://music.apple.com/us/album/osad%C3%ADa/1889956788</v>
       </c>
       <c r="L68" t="str">
-        <v>Deep Water - Cameron Whitcomb</v>
+        <v>OSADÍA - Eden Muñoz</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Time Is A Thief</v>
+        <v>Deep Water</v>
       </c>
       <c r="B69" t="str">
         <v/>
       </c>
       <c r="C69" t="str">
-        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
+        <v>https://music.apple.com/us/song/deep-water/1887606219</v>
       </c>
       <c r="D69" t="str">
         <v>2026-04-21</v>
@@ -2997,36 +2997,36 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>Deep Blue</v>
+        <v>Deep Water - EP</v>
       </c>
       <c r="G69" t="str">
-        <v>3:13</v>
+        <v>2:33</v>
       </c>
       <c r="H69" t="str">
-        <v>ERNEST</v>
+        <v>Cameron Whitcomb</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J69" t="str">
-        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
+        <v>https://music.apple.com/us/artist/cameron-whitcomb/1542957700</v>
       </c>
       <c r="K69" t="str">
-        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
+        <v>https://music.apple.com/us/album/deep-water/1887606218</v>
       </c>
       <c r="L69" t="str">
-        <v>Time Is A Thief - ERNEST</v>
+        <v>Deep Water - Cameron Whitcomb</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>No Pierdo El Tiempo</v>
+        <v>Time Is A Thief</v>
       </c>
       <c r="B70" t="str">
         <v/>
       </c>
       <c r="C70" t="str">
-        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
+        <v>https://music.apple.com/us/song/time-is-a-thief/1885061430</v>
       </c>
       <c r="D70" t="str">
         <v>2026-04-21</v>
@@ -3035,36 +3035,36 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>No Pierdo El Tiempo - Single</v>
+        <v>Deep Blue</v>
       </c>
       <c r="G70" t="str">
-        <v>1:58</v>
+        <v>3:13</v>
       </c>
       <c r="H70" t="str">
-        <v>Marca MP</v>
+        <v>ERNEST</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J70" t="str">
-        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
+        <v>https://music.apple.com/us/artist/ernest/1450042443</v>
       </c>
       <c r="K70" t="str">
-        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
+        <v>https://music.apple.com/us/album/time-is-a-thief/1885061168</v>
       </c>
       <c r="L70" t="str">
-        <v>No Pierdo El Tiempo - Marca MP</v>
+        <v>Time Is A Thief - ERNEST</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Price of Love</v>
+        <v>No Pierdo El Tiempo</v>
       </c>
       <c r="B71" t="str">
         <v/>
       </c>
       <c r="C71" t="str">
-        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
+        <v>https://music.apple.com/us/song/no-pierdo-el-tiempo/1890328522</v>
       </c>
       <c r="D71" t="str">
         <v>2026-04-21</v>
@@ -3073,36 +3073,36 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>When You Know You Know - EP</v>
+        <v>No Pierdo El Tiempo - Single</v>
       </c>
       <c r="G71" t="str">
-        <v>3:29</v>
+        <v>1:58</v>
       </c>
       <c r="H71" t="str">
-        <v>Benny G</v>
+        <v>Marca MP</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J71" t="str">
-        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
+        <v>https://music.apple.com/us/artist/marca-mp/1493050737</v>
       </c>
       <c r="K71" t="str">
-        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
+        <v>https://music.apple.com/us/album/no-pierdo-el-tiempo/1890328521</v>
       </c>
       <c r="L71" t="str">
-        <v>Price of Love - Benny G</v>
+        <v>No Pierdo El Tiempo - Marca MP</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Las Flores</v>
+        <v>Price of Love</v>
       </c>
       <c r="B72" t="str">
         <v/>
       </c>
       <c r="C72" t="str">
-        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
+        <v>https://music.apple.com/us/song/price-of-love/1885677047</v>
       </c>
       <c r="D72" t="str">
         <v>2026-04-21</v>
@@ -3111,36 +3111,36 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>Las Flores - Single</v>
+        <v>When You Know You Know - EP</v>
       </c>
       <c r="G72" t="str">
-        <v>2:59</v>
+        <v>3:29</v>
       </c>
       <c r="H72" t="str">
-        <v>Mau y Ricky</v>
+        <v>Benny G</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J72" t="str">
-        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
+        <v>https://music.apple.com/us/artist/benny-g/1831835318</v>
       </c>
       <c r="K72" t="str">
-        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
+        <v>https://music.apple.com/us/album/price-of-love/1885677041</v>
       </c>
       <c r="L72" t="str">
-        <v>Las Flores - Mau y Ricky</v>
+        <v>Price of Love - Benny G</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>To The Moon</v>
+        <v>Las Flores</v>
       </c>
       <c r="B73" t="str">
         <v/>
       </c>
       <c r="C73" t="str">
-        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
+        <v>https://music.apple.com/us/song/las-flores/1889618220</v>
       </c>
       <c r="D73" t="str">
         <v>2026-04-21</v>
@@ -3149,36 +3149,36 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>BABY JAKE - Single</v>
+        <v>Las Flores - Single</v>
       </c>
       <c r="G73" t="str">
-        <v>3:42</v>
+        <v>2:59</v>
       </c>
       <c r="H73" t="str">
-        <v>Fancy Hagood</v>
+        <v>Mau y Ricky</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J73" t="str">
-        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
+        <v>https://music.apple.com/us/artist/mau-y-ricky/1096068683</v>
       </c>
       <c r="K73" t="str">
-        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
+        <v>https://music.apple.com/us/album/las-flores/1889618218</v>
       </c>
       <c r="L73" t="str">
-        <v>To The Moon - Fancy Hagood</v>
+        <v>Las Flores - Mau y Ricky</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>MATCHA</v>
+        <v>To The Moon</v>
       </c>
       <c r="B74" t="str">
         <v/>
       </c>
       <c r="C74" t="str">
-        <v>https://music.apple.com/us/song/matcha/1891443064</v>
+        <v>https://music.apple.com/us/song/to-the-moon/1886518037</v>
       </c>
       <c r="D74" t="str">
         <v>2026-04-21</v>
@@ -3187,36 +3187,36 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>SABIA</v>
+        <v>BABY JAKE - Single</v>
       </c>
       <c r="G74" t="str">
-        <v>2:36</v>
+        <v>3:42</v>
       </c>
       <c r="H74" t="str">
-        <v>Los Dareyes De La Sierra</v>
+        <v>Fancy Hagood</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J74" t="str">
-        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
+        <v>https://music.apple.com/us/artist/fancy-hagood/859825960</v>
       </c>
       <c r="K74" t="str">
-        <v>https://music.apple.com/us/album/matcha/1891442873</v>
+        <v>https://music.apple.com/us/album/to-the-moon/1886518034</v>
       </c>
       <c r="L74" t="str">
-        <v>MATCHA - Los Dareyes De La Sierra</v>
+        <v>To The Moon - Fancy Hagood</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>PROWLER</v>
+        <v>MATCHA</v>
       </c>
       <c r="B75" t="str">
         <v/>
       </c>
       <c r="C75" t="str">
-        <v>https://music.apple.com/us/song/prowler/1891120710</v>
+        <v>https://music.apple.com/us/song/matcha/1891443064</v>
       </c>
       <c r="D75" t="str">
         <v>2026-04-21</v>
@@ -3225,36 +3225,36 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>PROWLER - Single</v>
+        <v>SABIA</v>
       </c>
       <c r="G75" t="str">
-        <v>2:45</v>
+        <v>2:36</v>
       </c>
       <c r="H75" t="str">
-        <v>Waterparks</v>
+        <v>Los Dareyes De La Sierra</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J75" t="str">
-        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
+        <v>https://music.apple.com/us/artist/los-dareyes-de-la-sierra/1475990231</v>
       </c>
       <c r="K75" t="str">
-        <v>https://music.apple.com/us/album/prowler/1891120709</v>
+        <v>https://music.apple.com/us/album/matcha/1891442873</v>
       </c>
       <c r="L75" t="str">
-        <v>PROWLER - Waterparks</v>
+        <v>MATCHA - Los Dareyes De La Sierra</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>BLINDFOLD</v>
+        <v>PROWLER</v>
       </c>
       <c r="B76" t="str">
         <v/>
       </c>
       <c r="C76" t="str">
-        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
+        <v>https://music.apple.com/us/song/prowler/1891120710</v>
       </c>
       <c r="D76" t="str">
         <v>2026-04-21</v>
@@ -3263,36 +3263,36 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>IT CALLS ME BY NAME - EP</v>
+        <v>PROWLER - Single</v>
       </c>
       <c r="G76" t="str">
-        <v>3:14</v>
+        <v>2:45</v>
       </c>
       <c r="H76" t="str">
-        <v>Wage War</v>
+        <v>Waterparks</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J76" t="str">
-        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
+        <v>https://music.apple.com/us/artist/waterparks/513067235</v>
       </c>
       <c r="K76" t="str">
-        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
+        <v>https://music.apple.com/us/album/prowler/1891120709</v>
       </c>
       <c r="L76" t="str">
-        <v>BLINDFOLD - Wage War</v>
+        <v>PROWLER - Waterparks</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>how far down</v>
+        <v>BLINDFOLD</v>
       </c>
       <c r="B77" t="str">
         <v/>
       </c>
       <c r="C77" t="str">
-        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
+        <v>https://music.apple.com/us/song/blindfold/1876593211</v>
       </c>
       <c r="D77" t="str">
         <v>2026-04-21</v>
@@ -3301,36 +3301,36 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>Take My Bones</v>
+        <v>IT CALLS ME BY NAME - EP</v>
       </c>
       <c r="G77" t="str">
-        <v>2:59</v>
+        <v>3:14</v>
       </c>
       <c r="H77" t="str">
-        <v>Camylio</v>
+        <v>Wage War</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J77" t="str">
-        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
+        <v>https://music.apple.com/us/artist/wage-war/1000847729</v>
       </c>
       <c r="K77" t="str">
-        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
+        <v>https://music.apple.com/us/album/blindfold/1876593203</v>
       </c>
       <c r="L77" t="str">
-        <v>how far down - Camylio</v>
+        <v>BLINDFOLD - Wage War</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Tell Me Why</v>
+        <v>how far down</v>
       </c>
       <c r="B78" t="str">
         <v/>
       </c>
       <c r="C78" t="str">
-        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
+        <v>https://music.apple.com/us/song/how-far-down/1890397336</v>
       </c>
       <c r="D78" t="str">
         <v>2026-04-21</v>
@@ -3339,36 +3339,36 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>Tell Me Why - Single</v>
+        <v>Take My Bones</v>
       </c>
       <c r="G78" t="str">
-        <v>2:26</v>
+        <v>2:59</v>
       </c>
       <c r="H78" t="str">
-        <v>Trap Dickey</v>
+        <v>Camylio</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J78" t="str">
-        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
+        <v>https://music.apple.com/us/artist/camylio/1459768105</v>
       </c>
       <c r="K78" t="str">
-        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
+        <v>https://music.apple.com/us/album/how-far-down/1890396884</v>
       </c>
       <c r="L78" t="str">
-        <v>Tell Me Why - Trap Dickey</v>
+        <v>how far down - Camylio</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Spin</v>
+        <v>Tell Me Why</v>
       </c>
       <c r="B79" t="str">
         <v/>
       </c>
       <c r="C79" t="str">
-        <v>https://music.apple.com/us/song/spin/1893085872</v>
+        <v>https://music.apple.com/us/song/tell-me-why/1890385785</v>
       </c>
       <c r="D79" t="str">
         <v>2026-04-21</v>
@@ -3377,36 +3377,36 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>Spin - Single</v>
+        <v>Tell Me Why - Single</v>
       </c>
       <c r="G79" t="str">
-        <v>4:15</v>
+        <v>2:26</v>
       </c>
       <c r="H79" t="str">
-        <v>21 Lil Harold</v>
+        <v>Trap Dickey</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J79" t="str">
-        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
+        <v>https://music.apple.com/us/artist/trap-dickey/1351019310</v>
       </c>
       <c r="K79" t="str">
-        <v>https://music.apple.com/us/album/spin/1893085869</v>
+        <v>https://music.apple.com/us/album/tell-me-why/1890385783</v>
       </c>
       <c r="L79" t="str">
-        <v>Spin - 21 Lil Harold</v>
+        <v>Tell Me Why - Trap Dickey</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>MILAN</v>
+        <v>Spin</v>
       </c>
       <c r="B80" t="str">
         <v/>
       </c>
       <c r="C80" t="str">
-        <v>https://music.apple.com/us/song/milan/1886158838</v>
+        <v>https://music.apple.com/us/song/spin/1893085872</v>
       </c>
       <c r="D80" t="str">
         <v>2026-04-21</v>
@@ -3415,36 +3415,36 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>MILAN - Single</v>
+        <v>Spin - Single</v>
       </c>
       <c r="G80" t="str">
-        <v>2:16</v>
+        <v>4:15</v>
       </c>
       <c r="H80" t="str">
-        <v>ERISTHEPLANET</v>
+        <v>21 Lil Harold</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J80" t="str">
-        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
+        <v>https://music.apple.com/us/artist/21-lil-harold/1514241738</v>
       </c>
       <c r="K80" t="str">
-        <v>https://music.apple.com/us/album/milan/1886158825</v>
+        <v>https://music.apple.com/us/album/spin/1893085869</v>
       </c>
       <c r="L80" t="str">
-        <v>MILAN - ERISTHEPLANET</v>
+        <v>Spin - 21 Lil Harold</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SHABA</v>
+        <v>MILAN</v>
       </c>
       <c r="B81" t="str">
         <v/>
       </c>
       <c r="C81" t="str">
-        <v>https://music.apple.com/us/song/shaba/1893186287</v>
+        <v>https://music.apple.com/us/song/milan/1886158838</v>
       </c>
       <c r="D81" t="str">
         <v>2026-04-21</v>
@@ -3453,36 +3453,36 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>SHABA - Single</v>
+        <v>MILAN - Single</v>
       </c>
       <c r="G81" t="str">
-        <v>2:01</v>
+        <v>2:16</v>
       </c>
       <c r="H81" t="str">
-        <v>SPINALL</v>
+        <v>ERISTHEPLANET</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J81" t="str">
-        <v>https://music.apple.com/us/artist/spinall/813737832</v>
+        <v>https://music.apple.com/us/artist/eristheplanet/1737346894</v>
       </c>
       <c r="K81" t="str">
-        <v>https://music.apple.com/us/album/shaba/1893186284</v>
+        <v>https://music.apple.com/us/album/milan/1886158825</v>
       </c>
       <c r="L81" t="str">
-        <v>SHABA - SPINALL</v>
+        <v>MILAN - ERISTHEPLANET</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Forever</v>
+        <v>SHABA</v>
       </c>
       <c r="B82" t="str">
         <v/>
       </c>
       <c r="C82" t="str">
-        <v>https://music.apple.com/us/song/forever/1860126454</v>
+        <v>https://music.apple.com/us/song/shaba/1893186287</v>
       </c>
       <c r="D82" t="str">
         <v>2026-04-21</v>
@@ -3491,36 +3491,36 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>Reflections</v>
+        <v>SHABA - Single</v>
       </c>
       <c r="G82" t="str">
-        <v>3:38</v>
+        <v>2:01</v>
       </c>
       <c r="H82" t="str">
-        <v>From Ashes to New</v>
+        <v>SPINALL</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J82" t="str">
-        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
+        <v>https://music.apple.com/us/artist/spinall/813737832</v>
       </c>
       <c r="K82" t="str">
-        <v>https://music.apple.com/us/album/forever/1860126452</v>
+        <v>https://music.apple.com/us/album/shaba/1893186284</v>
       </c>
       <c r="L82" t="str">
-        <v>Forever - From Ashes to New</v>
+        <v>SHABA - SPINALL</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>STRONGER THAN MACHINES</v>
+        <v>Forever</v>
       </c>
       <c r="B83" t="str">
         <v/>
       </c>
       <c r="C83" t="str">
-        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
+        <v>https://music.apple.com/us/song/forever/1860126454</v>
       </c>
       <c r="D83" t="str">
         <v>2026-04-21</v>
@@ -3529,36 +3529,36 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>STRONGER THAN MACHINES - Single</v>
+        <v>Reflections</v>
       </c>
       <c r="G83" t="str">
-        <v>2:46</v>
+        <v>3:38</v>
       </c>
       <c r="H83" t="str">
-        <v>Kaleena Zanders</v>
+        <v>From Ashes to New</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J83" t="str">
-        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
+        <v>https://music.apple.com/us/artist/from-ashes-to-new/688645097</v>
       </c>
       <c r="K83" t="str">
-        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
+        <v>https://music.apple.com/us/album/forever/1860126452</v>
       </c>
       <c r="L83" t="str">
-        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
+        <v>Forever - From Ashes to New</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Fear The Panic (feat. Hot Water Music)</v>
+        <v>STRONGER THAN MACHINES</v>
       </c>
       <c r="B84" t="str">
         <v/>
       </c>
       <c r="C84" t="str">
-        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
+        <v>https://music.apple.com/us/song/stronger-than-machines/1890296500</v>
       </c>
       <c r="D84" t="str">
         <v>2026-04-21</v>
@@ -3567,36 +3567,36 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>Still Suffer</v>
+        <v>STRONGER THAN MACHINES - Single</v>
       </c>
       <c r="G84" t="str">
-        <v>2:57</v>
+        <v>2:46</v>
       </c>
       <c r="H84" t="str">
-        <v>Terror</v>
+        <v>Kaleena Zanders</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J84" t="str">
-        <v>https://music.apple.com/us/artist/terror/19123484</v>
+        <v>https://music.apple.com/us/artist/kaleena-zanders/438767588</v>
       </c>
       <c r="K84" t="str">
-        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
+        <v>https://music.apple.com/us/album/stronger-than-machines/1890296499</v>
       </c>
       <c r="L84" t="str">
-        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
+        <v>STRONGER THAN MACHINES - Kaleena Zanders</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Confused</v>
+        <v>Fear The Panic (feat. Hot Water Music)</v>
       </c>
       <c r="B85" t="str">
         <v/>
       </c>
       <c r="C85" t="str">
-        <v>https://music.apple.com/us/song/confused/1889252290</v>
+        <v>https://music.apple.com/us/song/fear-the-panic-feat-hot-water-music/1872200608</v>
       </c>
       <c r="D85" t="str">
         <v>2026-04-21</v>
@@ -3605,36 +3605,36 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>For What It's Worth</v>
+        <v>Still Suffer</v>
       </c>
       <c r="G85" t="str">
-        <v>2:56</v>
+        <v>2:57</v>
       </c>
       <c r="H85" t="str">
-        <v>cortex</v>
+        <v>Terror</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J85" t="str">
-        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
+        <v>https://music.apple.com/us/artist/terror/19123484</v>
       </c>
       <c r="K85" t="str">
-        <v>https://music.apple.com/us/album/confused/1889252285</v>
+        <v>https://music.apple.com/us/album/fear-the-panic-feat-hot-water-music/1872200024</v>
       </c>
       <c r="L85" t="str">
-        <v>Confused - cortex</v>
+        <v>Fear The Panic (feat. Hot Water Music) - Terror</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>On The Low</v>
+        <v>Confused</v>
       </c>
       <c r="B86" t="str">
         <v/>
       </c>
       <c r="C86" t="str">
-        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
+        <v>https://music.apple.com/us/song/confused/1889252290</v>
       </c>
       <c r="D86" t="str">
         <v>2026-04-21</v>
@@ -3643,36 +3643,36 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>On The Low - Single</v>
+        <v>For What It's Worth</v>
       </c>
       <c r="G86" t="str">
-        <v>3:29</v>
+        <v>2:56</v>
       </c>
       <c r="H86" t="str">
-        <v>Rene Bonét</v>
+        <v>cortex</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J86" t="str">
-        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
+        <v>https://music.apple.com/us/artist/cortex/1762682501</v>
       </c>
       <c r="K86" t="str">
-        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
+        <v>https://music.apple.com/us/album/confused/1889252285</v>
       </c>
       <c r="L86" t="str">
-        <v>On The Low - Rene Bonét</v>
+        <v>Confused - cortex</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Wannabe</v>
+        <v>On The Low</v>
       </c>
       <c r="B87" t="str">
         <v/>
       </c>
       <c r="C87" t="str">
-        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
+        <v>https://music.apple.com/us/song/on-the-low/1885895848</v>
       </c>
       <c r="D87" t="str">
         <v>2026-04-21</v>
@@ -3681,36 +3681,36 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>Wannabe - Single</v>
+        <v>On The Low - Single</v>
       </c>
       <c r="G87" t="str">
-        <v>2:30</v>
+        <v>3:29</v>
       </c>
       <c r="H87" t="str">
-        <v>Corey Kent</v>
+        <v>Rene Bonét</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J87" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/rene-bon%C3%A9t/1459423803</v>
       </c>
       <c r="K87" t="str">
-        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
+        <v>https://music.apple.com/us/album/on-the-low/1885895847</v>
       </c>
       <c r="L87" t="str">
-        <v>Wannabe - Corey Kent</v>
+        <v>On The Low - Rene Bonét</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Talking To Jesus</v>
+        <v>Wannabe</v>
       </c>
       <c r="B88" t="str">
         <v/>
       </c>
       <c r="C88" t="str">
-        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
+        <v>https://music.apple.com/us/song/wannabe/1890533850</v>
       </c>
       <c r="D88" t="str">
         <v>2026-04-21</v>
@@ -3719,36 +3719,36 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>Middle Child</v>
+        <v>Wannabe - Single</v>
       </c>
       <c r="G88" t="str">
-        <v>3:32</v>
+        <v>2:30</v>
       </c>
       <c r="H88" t="str">
-        <v>Amma</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J88" t="str">
-        <v>https://music.apple.com/us/artist/amma/1834685990</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K88" t="str">
-        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
+        <v>https://music.apple.com/us/album/wannabe/1890533842</v>
       </c>
       <c r="L88" t="str">
-        <v>Talking To Jesus - Amma</v>
+        <v>Wannabe - Corey Kent</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Kicked Outta Hell</v>
+        <v>Talking To Jesus</v>
       </c>
       <c r="B89" t="str">
         <v/>
       </c>
       <c r="C89" t="str">
-        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
+        <v>https://music.apple.com/us/song/talking-to-jesus/1891474318</v>
       </c>
       <c r="D89" t="str">
         <v>2026-04-21</v>
@@ -3757,36 +3757,36 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>Into Oblivion</v>
+        <v>Middle Child</v>
       </c>
       <c r="G89" t="str">
-        <v>3:24</v>
+        <v>3:32</v>
       </c>
       <c r="H89" t="str">
-        <v>Venom</v>
+        <v>Amma</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J89" t="str">
-        <v>https://music.apple.com/us/artist/venom/3222127</v>
+        <v>https://music.apple.com/us/artist/amma/1834685990</v>
       </c>
       <c r="K89" t="str">
-        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
+        <v>https://music.apple.com/us/album/talking-to-jesus/1891473908</v>
       </c>
       <c r="L89" t="str">
-        <v>Kicked Outta Hell - Venom</v>
+        <v>Talking To Jesus - Amma</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>breakups with best friends</v>
+        <v>Kicked Outta Hell</v>
       </c>
       <c r="B90" t="str">
         <v/>
       </c>
       <c r="C90" t="str">
-        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
+        <v>https://music.apple.com/us/song/kicked-outta-hell/1872651423</v>
       </c>
       <c r="D90" t="str">
         <v>2026-04-21</v>
@@ -3795,36 +3795,36 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>breakups with best friends - Single</v>
+        <v>Into Oblivion</v>
       </c>
       <c r="G90" t="str">
-        <v>3:22</v>
+        <v>3:24</v>
       </c>
       <c r="H90" t="str">
-        <v>Zoe Levert</v>
+        <v>Venom</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J90" t="str">
-        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
+        <v>https://music.apple.com/us/artist/venom/3222127</v>
       </c>
       <c r="K90" t="str">
-        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
+        <v>https://music.apple.com/us/album/kicked-outta-hell/1872651243</v>
       </c>
       <c r="L90" t="str">
-        <v>breakups with best friends - Zoe Levert</v>
+        <v>Kicked Outta Hell - Venom</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Taylor</v>
+        <v>breakups with best friends</v>
       </c>
       <c r="B91" t="str">
         <v/>
       </c>
       <c r="C91" t="str">
-        <v>https://music.apple.com/us/song/taylor/1871219896</v>
+        <v>https://music.apple.com/us/song/breakups-with-best-friends/1890003291</v>
       </c>
       <c r="D91" t="str">
         <v>2026-04-21</v>
@@ -3833,36 +3833,36 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>So The Sun Can Pour</v>
+        <v>breakups with best friends - Single</v>
       </c>
       <c r="G91" t="str">
-        <v>4:15</v>
+        <v>3:22</v>
       </c>
       <c r="H91" t="str">
-        <v>Hayden Everett</v>
+        <v>Zoe Levert</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J91" t="str">
-        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
+        <v>https://music.apple.com/us/artist/zoe-levert/1845343641</v>
       </c>
       <c r="K91" t="str">
-        <v>https://music.apple.com/us/album/taylor/1871219587</v>
+        <v>https://music.apple.com/us/album/breakups-with-best-friends/1890003290</v>
       </c>
       <c r="L91" t="str">
-        <v>Taylor - Hayden Everett</v>
+        <v>breakups with best friends - Zoe Levert</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Yours</v>
+        <v>Taylor</v>
       </c>
       <c r="B92" t="str">
         <v/>
       </c>
       <c r="C92" t="str">
-        <v>https://music.apple.com/us/song/yours/1877995590</v>
+        <v>https://music.apple.com/us/song/taylor/1871219896</v>
       </c>
       <c r="D92" t="str">
         <v>2026-04-21</v>
@@ -3871,36 +3871,36 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>Yours - Single</v>
+        <v>So The Sun Can Pour</v>
       </c>
       <c r="G92" t="str">
-        <v>4:26</v>
+        <v>4:15</v>
       </c>
       <c r="H92" t="str">
-        <v>Luca Fogale</v>
+        <v>Hayden Everett</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J92" t="str">
-        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
+        <v>https://music.apple.com/us/artist/hayden-everett/1465086443</v>
       </c>
       <c r="K92" t="str">
-        <v>https://music.apple.com/us/album/yours/1877995586</v>
+        <v>https://music.apple.com/us/album/taylor/1871219587</v>
       </c>
       <c r="L92" t="str">
-        <v>Yours - Luca Fogale</v>
+        <v>Taylor - Hayden Everett</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Pepper</v>
+        <v>Yours</v>
       </c>
       <c r="B93" t="str">
         <v/>
       </c>
       <c r="C93" t="str">
-        <v>https://music.apple.com/us/song/pepper/1888590563</v>
+        <v>https://music.apple.com/us/song/yours/1877995590</v>
       </c>
       <c r="D93" t="str">
         <v>2026-04-21</v>
@@ -3909,36 +3909,36 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>Pepper - Single</v>
+        <v>Yours - Single</v>
       </c>
       <c r="G93" t="str">
-        <v>4:54</v>
+        <v>4:26</v>
       </c>
       <c r="H93" t="str">
-        <v>S.G. Goodman</v>
+        <v>Luca Fogale</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J93" t="str">
-        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
+        <v>https://music.apple.com/us/artist/luca-fogale/868038740</v>
       </c>
       <c r="K93" t="str">
-        <v>https://music.apple.com/us/album/pepper/1888590562</v>
+        <v>https://music.apple.com/us/album/yours/1877995586</v>
       </c>
       <c r="L93" t="str">
-        <v>Pepper - S.G. Goodman</v>
+        <v>Yours - Luca Fogale</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>No Driver</v>
+        <v>Pepper</v>
       </c>
       <c r="B94" t="str">
         <v/>
       </c>
       <c r="C94" t="str">
-        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
+        <v>https://music.apple.com/us/song/pepper/1888590563</v>
       </c>
       <c r="D94" t="str">
         <v>2026-04-21</v>
@@ -3947,36 +3947,36 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>Roses</v>
+        <v>Pepper - Single</v>
       </c>
       <c r="G94" t="str">
-        <v>3:48</v>
+        <v>4:54</v>
       </c>
       <c r="H94" t="str">
-        <v>Widowspeak</v>
+        <v>S.G. Goodman</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J94" t="str">
-        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
+        <v>https://music.apple.com/us/artist/s-g-goodman/1450439730</v>
       </c>
       <c r="K94" t="str">
-        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
+        <v>https://music.apple.com/us/album/pepper/1888590562</v>
       </c>
       <c r="L94" t="str">
-        <v>No Driver - Widowspeak</v>
+        <v>Pepper - S.G. Goodman</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Catch A Fire</v>
+        <v>No Driver</v>
       </c>
       <c r="B95" t="str">
         <v/>
       </c>
       <c r="C95" t="str">
-        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
+        <v>https://music.apple.com/us/song/no-driver/1880416147</v>
       </c>
       <c r="D95" t="str">
         <v>2026-04-21</v>
@@ -3985,36 +3985,36 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>Catch A Fire - Single</v>
+        <v>Roses</v>
       </c>
       <c r="G95" t="str">
-        <v>3:13</v>
+        <v>3:48</v>
       </c>
       <c r="H95" t="str">
-        <v>Mat Kearney</v>
+        <v>Widowspeak</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J95" t="str">
-        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
+        <v>https://music.apple.com/us/artist/widowspeak/420935735</v>
       </c>
       <c r="K95" t="str">
-        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
+        <v>https://music.apple.com/us/album/no-driver/1880416141</v>
       </c>
       <c r="L95" t="str">
-        <v>Catch A Fire - Mat Kearney</v>
+        <v>No Driver - Widowspeak</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>GUERILLAZ</v>
+        <v>Catch A Fire</v>
       </c>
       <c r="B96" t="str">
         <v/>
       </c>
       <c r="C96" t="str">
-        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
+        <v>https://music.apple.com/us/song/catch-a-fire/1886524275</v>
       </c>
       <c r="D96" t="str">
         <v>2026-04-21</v>
@@ -4023,36 +4023,36 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>GUERILLAZ - Single</v>
+        <v>Catch A Fire - Single</v>
       </c>
       <c r="G96" t="str">
-        <v>2:18</v>
+        <v>3:13</v>
       </c>
       <c r="H96" t="str">
-        <v>H.LLS</v>
+        <v>Mat Kearney</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J96" t="str">
-        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
+        <v>https://music.apple.com/us/artist/mat-kearney/27491554</v>
       </c>
       <c r="K96" t="str">
-        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
+        <v>https://music.apple.com/us/album/catch-a-fire/1886524274</v>
       </c>
       <c r="L96" t="str">
-        <v>GUERILLAZ - H.LLS</v>
+        <v>Catch A Fire - Mat Kearney</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ</v>
       </c>
       <c r="B97" t="str">
         <v/>
       </c>
       <c r="C97" t="str">
-        <v>https://music.apple.com/us/song/powder/1876915920</v>
+        <v>https://music.apple.com/us/song/guerillaz/1886836560</v>
       </c>
       <c r="D97" t="str">
         <v>2026-04-21</v>
@@ -4061,36 +4061,36 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>Powder</v>
+        <v>GUERILLAZ - Single</v>
       </c>
       <c r="G97" t="str">
-        <v>4:41</v>
+        <v>2:18</v>
       </c>
       <c r="H97" t="str">
-        <v>Nathanial Young</v>
+        <v>H.LLS</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J97" t="str">
-        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
+        <v>https://music.apple.com/us/artist/h-lls/1751287958</v>
       </c>
       <c r="K97" t="str">
-        <v>https://music.apple.com/us/album/powder/1876915916</v>
+        <v>https://music.apple.com/us/album/guerillaz/1886836559</v>
       </c>
       <c r="L97" t="str">
-        <v>Powder - Nathanial Young</v>
+        <v>GUERILLAZ - H.LLS</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Knuckle</v>
+        <v>Powder</v>
       </c>
       <c r="B98" t="str">
         <v/>
       </c>
       <c r="C98" t="str">
-        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
+        <v>https://music.apple.com/us/song/powder/1876915920</v>
       </c>
       <c r="D98" t="str">
         <v>2026-04-21</v>
@@ -4099,36 +4099,36 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>Knuckle - Single</v>
+        <v>Powder</v>
       </c>
       <c r="G98" t="str">
-        <v>2:20</v>
+        <v>4:41</v>
       </c>
       <c r="H98" t="str">
-        <v>MexikoDro</v>
+        <v>Nathanial Young</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J98" t="str">
-        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
+        <v>https://music.apple.com/us/artist/nathanial-young/1434895154</v>
       </c>
       <c r="K98" t="str">
-        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
+        <v>https://music.apple.com/us/album/powder/1876915916</v>
       </c>
       <c r="L98" t="str">
-        <v>Knuckle - MexikoDro</v>
+        <v>Powder - Nathanial Young</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>For The Ride</v>
+        <v>Knuckle</v>
       </c>
       <c r="B99" t="str">
         <v/>
       </c>
       <c r="C99" t="str">
-        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
+        <v>https://music.apple.com/us/song/knuckle/1891862173</v>
       </c>
       <c r="D99" t="str">
         <v>2026-04-21</v>
@@ -4137,36 +4137,36 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>For The Ride - Single</v>
+        <v>Knuckle - Single</v>
       </c>
       <c r="G99" t="str">
-        <v>2:43</v>
+        <v>2:20</v>
       </c>
       <c r="H99" t="str">
-        <v>Snakehips</v>
+        <v>MexikoDro</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J99" t="str">
-        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
+        <v>https://music.apple.com/us/artist/mexikodro/1092836688</v>
       </c>
       <c r="K99" t="str">
-        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
+        <v>https://music.apple.com/us/album/knuckle/1891862169</v>
       </c>
       <c r="L99" t="str">
-        <v>For The Ride - Snakehips</v>
+        <v>Knuckle - MexikoDro</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>I Expect Better</v>
+        <v>For The Ride</v>
       </c>
       <c r="B100" t="str">
         <v/>
       </c>
       <c r="C100" t="str">
-        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
+        <v>https://music.apple.com/us/song/for-the-ride/1890544557</v>
       </c>
       <c r="D100" t="str">
         <v>2026-04-21</v>
@@ -4175,36 +4175,36 @@
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>I Expect Better - Single</v>
+        <v>For The Ride - Single</v>
       </c>
       <c r="G100" t="str">
-        <v>2:19</v>
+        <v>2:43</v>
       </c>
       <c r="H100" t="str">
-        <v>daydreamers</v>
+        <v>Snakehips</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J100" t="str">
-        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
+        <v>https://music.apple.com/us/artist/snakehips/974255216</v>
       </c>
       <c r="K100" t="str">
-        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
+        <v>https://music.apple.com/us/album/for-the-ride/1890544556</v>
       </c>
       <c r="L100" t="str">
-        <v>I Expect Better - daydreamers</v>
+        <v>For The Ride - Snakehips</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>WYD</v>
+        <v>I Expect Better</v>
       </c>
       <c r="B101" t="str">
         <v/>
       </c>
       <c r="C101" t="str">
-        <v>https://music.apple.com/us/song/wyd/1889295508</v>
+        <v>https://music.apple.com/us/song/i-expect-better/1888185858</v>
       </c>
       <c r="D101" t="str">
         <v>2026-04-21</v>
@@ -4213,36 +4213,36 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>WYD - Single</v>
+        <v>I Expect Better - Single</v>
       </c>
       <c r="G101" t="str">
-        <v>2:36</v>
+        <v>2:19</v>
       </c>
       <c r="H101" t="str">
-        <v>KARRAHBOOO</v>
+        <v>daydreamers</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J101" t="str">
-        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
+        <v>https://music.apple.com/us/artist/daydreamers/1736977711</v>
       </c>
       <c r="K101" t="str">
-        <v>https://music.apple.com/us/album/wyd/1889295507</v>
+        <v>https://music.apple.com/us/album/i-expect-better/1888185856</v>
       </c>
       <c r="L101" t="str">
-        <v>WYD - KARRAHBOOO</v>
+        <v>I Expect Better - daydreamers</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Dig Your Own Grave</v>
+        <v>WYD</v>
       </c>
       <c r="B102" t="str">
         <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+        <v>https://music.apple.com/us/song/wyd/1889295508</v>
       </c>
       <c r="D102" t="str">
         <v>2026-04-21</v>
@@ -4251,68 +4251,106 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Strike and Kill</v>
+        <v>WYD - Single</v>
       </c>
       <c r="G102" t="str">
-        <v>4:29</v>
+        <v>2:36</v>
       </c>
       <c r="H102" t="str">
-        <v>DevilDriver</v>
+        <v>KARRAHBOOO</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+        <v>https://music.apple.com/us/artist/karrahbooo/1653276309</v>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+        <v>https://music.apple.com/us/album/wyd/1889295507</v>
       </c>
       <c r="L102" t="str">
-        <v>Dig Your Own Grave - DevilDriver</v>
+        <v>WYD - KARRAHBOOO</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>Dig Your Own Grave</v>
+      </c>
+      <c r="B103" t="str">
+        <v/>
+      </c>
+      <c r="C103" t="str">
+        <v>https://music.apple.com/us/song/dig-your-own-grave/1886763096</v>
+      </c>
+      <c r="D103" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v>Strike and Kill</v>
+      </c>
+      <c r="G103" t="str">
+        <v>4:29</v>
+      </c>
+      <c r="H103" t="str">
+        <v>DevilDriver</v>
+      </c>
+      <c r="I103" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J103" t="str">
+        <v>https://music.apple.com/us/artist/devildriver/17407176</v>
+      </c>
+      <c r="K103" t="str">
+        <v>https://music.apple.com/us/album/dig-your-own-grave/1886763087</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Dig Your Own Grave - DevilDriver</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>Rat Trap (feat. Nate Johnson)</v>
       </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
+      <c r="B104" t="str">
+        <v/>
+      </c>
+      <c r="C104" t="str">
         <v>https://music.apple.com/us/song/rat-trap-feat-nate-johnson/1854239130</v>
       </c>
-      <c r="D103" t="str">
-        <v>2026-04-21</v>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
+      <c r="D104" t="str">
+        <v>2026-04-21</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
         <v>The Dead Ones</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G104" t="str">
         <v>3:32</v>
       </c>
-      <c r="H103" t="str">
+      <c r="H104" t="str">
         <v>The Last Ten Seconds of Life</v>
       </c>
-      <c r="I103" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J103" t="str">
+      <c r="I104" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J104" t="str">
         <v>https://music.apple.com/us/artist/the-last-ten-seconds-of-life/459333090</v>
       </c>
-      <c r="K103" t="str">
+      <c r="K104" t="str">
         <v>https://music.apple.com/us/album/rat-trap-feat-nate-johnson/1854239127</v>
       </c>
-      <c r="L103" t="str">
+      <c r="L104" t="str">
         <v>Rat Trap (feat. Nate Johnson) - The Last Ten Seconds of Life</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L104"/>
   </ignoredErrors>
 </worksheet>
 </file>